--- a/품목마스터/마감작업자별 생산가능품목_코드목록_v2.xlsx
+++ b/품목마스터/마감작업자별 생산가능품목_코드목록_v2.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FURSYS\Desktop\코드추출\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FURSYS\Desktop\계획및분배\품목마스터\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,16 +14,16 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="품목군별코드" sheetId="4" r:id="rId4"/>
-    <sheet name="품목군코드상세" sheetId="5" r:id="rId5"/>
+    <sheet name="품목군별코드" sheetId="4" r:id="rId3"/>
+    <sheet name="품목군코드상세" sheetId="5" r:id="rId4"/>
+    <sheet name="특정라인 지정" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2770" uniqueCount="1095">
   <si>
     <t>마감작업자 생산가능품목</t>
   </si>
@@ -1124,6 +1124,2190 @@
   </si>
   <si>
     <t>IXY2412001</t>
+  </si>
+  <si>
+    <t>품목코드</t>
+  </si>
+  <si>
+    <t>단품명칭▼</t>
+  </si>
+  <si>
+    <t>CSXX2604308</t>
+  </si>
+  <si>
+    <t>(알로소)베르디 1인 수출 박스 포장사양</t>
+  </si>
+  <si>
+    <t>CSXX2604309</t>
+  </si>
+  <si>
+    <t>FACSB1161BN</t>
+  </si>
+  <si>
+    <t>(알로소)베르디 1인_프리미엄 레더</t>
+  </si>
+  <si>
+    <t>FACSB1161HN</t>
+  </si>
+  <si>
+    <t>(알로소)베르디 1인_하이엔드 레더</t>
+  </si>
+  <si>
+    <t>FACSL003</t>
+  </si>
+  <si>
+    <t>(알로소)베이스 타입 003 (4EA)</t>
+  </si>
+  <si>
+    <t>FACSL006</t>
+  </si>
+  <si>
+    <t>(알로소)베이스 타입 006 (4EA)</t>
+  </si>
+  <si>
+    <t>ZSL7101N</t>
+  </si>
+  <si>
+    <t>1인 소파</t>
+  </si>
+  <si>
+    <t>CS6201A</t>
+  </si>
+  <si>
+    <t>1인용 소파 몸통 (NO ARM)+쿠션(1EA)</t>
+  </si>
+  <si>
+    <t>CS6201</t>
+  </si>
+  <si>
+    <t>1인용 소파 몸통+쿠션(1EA)</t>
+  </si>
+  <si>
+    <t>CS6201B</t>
+  </si>
+  <si>
+    <t>1인용 소파-등받이 무</t>
+  </si>
+  <si>
+    <t>CS6202A</t>
+  </si>
+  <si>
+    <t>2인용 소파 몸통 (NO ARM)+쿠션(2EA)</t>
+  </si>
+  <si>
+    <t>CS6202</t>
+  </si>
+  <si>
+    <t>2인용 소파 몸통+쿠션(2EA)</t>
+  </si>
+  <si>
+    <t>CS6202B</t>
+  </si>
+  <si>
+    <t>2인용 소파-등받이 무</t>
+  </si>
+  <si>
+    <t>ZSL7103N</t>
+  </si>
+  <si>
+    <t>3인용 소파</t>
+  </si>
+  <si>
+    <t>WDWW134016-R000</t>
+  </si>
+  <si>
+    <t>ACSB3704 바드 오토만 좌판쿠션 마감_GN</t>
+  </si>
+  <si>
+    <t>FBFP040404-R000</t>
+  </si>
+  <si>
+    <t>ACSB3704 바드 오토만 좌판쿠션 미싱_GN</t>
+  </si>
+  <si>
+    <t>FBFP040362-R000</t>
+  </si>
+  <si>
+    <t>ACSB3771 바드 와이드 1인 좌판쿠션 미싱_GN</t>
+  </si>
+  <si>
+    <t>WDWW166042-R000</t>
+  </si>
+  <si>
+    <t>ACSB3773 바드 데이베드 좌 좌판쿠션 마감 (구스사양)</t>
+  </si>
+  <si>
+    <t>WDWW133988-R000</t>
+  </si>
+  <si>
+    <t>ACSB3773 바드 데이베드 좌 좌판쿠션 마감_GN</t>
+  </si>
+  <si>
+    <t>WDWW134002-R000</t>
+  </si>
+  <si>
+    <t>ACSB3774 바드 데이베드 우 좌판쿠션 마감_GN</t>
+  </si>
+  <si>
+    <t>WDWW134004-R000</t>
+  </si>
+  <si>
+    <t>ACSB3774 바드 데이베드 우 좌판쿠션 마감_JN</t>
+  </si>
+  <si>
+    <t>WDWW133676-R000</t>
+  </si>
+  <si>
+    <t>ACSB377X 바드 데이베드 좌판쿠션 본딩</t>
+  </si>
+  <si>
+    <t>WDWW133953-R000</t>
+  </si>
+  <si>
+    <t>ACSB377X 바드 와이드 1인 (공용) 좌판쿠션 마감_GN</t>
+  </si>
+  <si>
+    <t>WDWW133974-R000</t>
+  </si>
+  <si>
+    <t>ACSB37XX 바드 등판쿠션(공용) 마감_GN</t>
+  </si>
+  <si>
+    <t>WDWW140015-R000</t>
+  </si>
+  <si>
+    <t>ACSB37XX 바드 등판쿠션(공용) 마감_V2</t>
+  </si>
+  <si>
+    <t>WDWW133598-R000</t>
+  </si>
+  <si>
+    <t>ACSB37XX 바드 플랫쿠션(공용) 마감_GN</t>
+  </si>
+  <si>
+    <t>WDWW135278-R000</t>
+  </si>
+  <si>
+    <t>ACSB38 홀리데이 와이드 2인 공용 좌방석 마감</t>
+  </si>
+  <si>
+    <t>FBFP042729-R000</t>
+  </si>
+  <si>
+    <t>ACSB38 홀리데이 와이드 2인 공용 좌방석 미싱</t>
+  </si>
+  <si>
+    <t>WDWW135299-R000</t>
+  </si>
+  <si>
+    <t>ACSB3827 홀리데이 터미널 좌 좌방석 마감</t>
+  </si>
+  <si>
+    <t>WDWW134133-R000</t>
+  </si>
+  <si>
+    <t>ACSF24XX 카포네 그랑 공용(우) 등판 마감</t>
+  </si>
+  <si>
+    <t>FBFP046465-R000</t>
+  </si>
+  <si>
+    <t>AS HCS8812L 밴쿠버 3인 좌 암리스 좌방석 커버</t>
+  </si>
+  <si>
+    <t>OPFW004159-R000</t>
+  </si>
+  <si>
+    <t>AS HCS8812LF 밴쿠버 1.5인 좌 좌방석</t>
+  </si>
+  <si>
+    <t>OPFW004160-R000</t>
+  </si>
+  <si>
+    <t>AS HCS8812RF 밴쿠버 1.5인 우 좌방석</t>
+  </si>
+  <si>
+    <t>WDWW162380-R000</t>
+  </si>
+  <si>
+    <t>AS 개별 접수코드</t>
+  </si>
+  <si>
+    <t>ETEP000402-R000</t>
+  </si>
+  <si>
+    <t>AS 로바 1인 좌 스위치 변경</t>
+  </si>
+  <si>
+    <t>WDWW138104-R000</t>
+  </si>
+  <si>
+    <t>AS 로바 4인(좌,우,암리스) 스크래치 리터치 및 열처리 수리</t>
+  </si>
+  <si>
+    <t>WDWW138394-R000</t>
+  </si>
+  <si>
+    <t>AS 밴쿠버 4인 스프링 및 고리 수리</t>
+  </si>
+  <si>
+    <t>FBFP046435-R000</t>
+  </si>
+  <si>
+    <t>AS, HEL3206A 천갈이</t>
+  </si>
+  <si>
+    <t>STSW000831-R000</t>
+  </si>
+  <si>
+    <t>AS, 밴쿠버 1.5인 단품 철제 다리</t>
+  </si>
+  <si>
+    <t>FBFP046318-R000</t>
+  </si>
+  <si>
+    <t>AS, 밴쿠버 1.5인 우 등판쿠션 (박스포장)</t>
+  </si>
+  <si>
+    <t>ETPJ013474-R000</t>
+  </si>
+  <si>
+    <t>AS, 밴쿠버 1인 우 철제다리</t>
+  </si>
+  <si>
+    <t>FBFP047332-R000</t>
+  </si>
+  <si>
+    <t>AS, 밴쿠버 3인좌 등쿠션 커버 교체</t>
+  </si>
+  <si>
+    <t>FBFP046661-R000</t>
+  </si>
+  <si>
+    <t>AS, 코티 CS6202B 좌판 천갈이</t>
+  </si>
+  <si>
+    <t>WDWW159411-R000</t>
+  </si>
+  <si>
+    <t>AS,마감 밀로(ACSB30) 공용 등판쿠션(대) 봉제+내장재</t>
+  </si>
+  <si>
+    <t>WDWW159415-R000</t>
+  </si>
+  <si>
+    <t>AS,마감 밀로(ACSB30) 공용 등판쿠션(소) 봉제+내장재</t>
+  </si>
+  <si>
+    <t>CL3207P</t>
+  </si>
+  <si>
+    <t>CL320 - 인조가죽부</t>
+  </si>
+  <si>
+    <t>CL3207PZ</t>
+  </si>
+  <si>
+    <t>WDWW138089-R000</t>
+  </si>
+  <si>
+    <t>CS6201B 코티 1인 벤치형 좌판 본딩</t>
+  </si>
+  <si>
+    <t>WDWW138093-R000</t>
+  </si>
+  <si>
+    <t>CS6202B 코티 2인 벤치형 좌판 본딩</t>
+  </si>
+  <si>
+    <t>CSXX2603012</t>
+  </si>
+  <si>
+    <t>CS6401RM 색비 수출 5V8</t>
+  </si>
+  <si>
+    <t>CSXX2604307</t>
+  </si>
+  <si>
+    <t>CS6411SM 색비 5V5A</t>
+  </si>
+  <si>
+    <t>CSXX2603013</t>
+  </si>
+  <si>
+    <t>CS6411SM 색비 수출 5M0</t>
+  </si>
+  <si>
+    <t>WDWW161766-R000</t>
+  </si>
+  <si>
+    <t>CS6411SM_5M1 스툴,(본사 전달건)</t>
+  </si>
+  <si>
+    <t>WDWW140655-R000</t>
+  </si>
+  <si>
+    <t>HCS8101 헤드 마감</t>
+  </si>
+  <si>
+    <t>OPFW004881-R000</t>
+  </si>
+  <si>
+    <t>HCS8800 좌판 쿠션 마감</t>
+  </si>
+  <si>
+    <t>WDWW132161-R000</t>
+  </si>
+  <si>
+    <t>HCS8800N 몸통 마감</t>
+  </si>
+  <si>
+    <t>WDWW132162-R000</t>
+  </si>
+  <si>
+    <t>HCS8800NF 몸통 마감</t>
+  </si>
+  <si>
+    <t>WDWW132163-R000</t>
+  </si>
+  <si>
+    <t>HCS8800NFA 몸통 마감</t>
+  </si>
+  <si>
+    <t>FBFP039443-R000</t>
+  </si>
+  <si>
+    <t>HCS8800NFA 미싱</t>
+  </si>
+  <si>
+    <t>OPFW004799-R000</t>
+  </si>
+  <si>
+    <t>HCS8812L 등판 쿠션 마감</t>
+  </si>
+  <si>
+    <t>OPFW004785-R000</t>
+  </si>
+  <si>
+    <t>OPFW004801-R000</t>
+  </si>
+  <si>
+    <t>HCS8812L 좌판 쿠션 마감</t>
+  </si>
+  <si>
+    <t>OPFW004789-R000</t>
+  </si>
+  <si>
+    <t>OPFW004808-R000</t>
+  </si>
+  <si>
+    <t>HCS8812R 등판 쿠션 마감</t>
+  </si>
+  <si>
+    <t>OPFW004802-R000</t>
+  </si>
+  <si>
+    <t>OPFW004810-R000</t>
+  </si>
+  <si>
+    <t>HCS8812R 좌판 쿠션 마감</t>
+  </si>
+  <si>
+    <t>OPFW004806-R000</t>
+  </si>
+  <si>
+    <t>OPFW004877-R000</t>
+  </si>
+  <si>
+    <t>HCS8813L 등판 쿠션(중) 가죽 마감</t>
+  </si>
+  <si>
+    <t>OPFW004878-R000</t>
+  </si>
+  <si>
+    <t>HCS8813L 좌판 쿠션(중) 가죽 마감</t>
+  </si>
+  <si>
+    <t>FBFP035719-R000</t>
+  </si>
+  <si>
+    <t>HCS8813L 좌판 쿠션(중) 가죽 미싱</t>
+  </si>
+  <si>
+    <t>OPFW004873-R000</t>
+  </si>
+  <si>
+    <t>HCS8813LF 등판 쿠션(중) 패브릭 마감</t>
+  </si>
+  <si>
+    <t>OPFW004874-R000</t>
+  </si>
+  <si>
+    <t>HCS8813LF 좌판 쿠션(중) 패브릭 마감</t>
+  </si>
+  <si>
+    <t>OPFW004876-R000</t>
+  </si>
+  <si>
+    <t>HCS8813LFA 좌판 쿠션(중) 패브릭 마감</t>
+  </si>
+  <si>
+    <t>OPFW004845-R000</t>
+  </si>
+  <si>
+    <t>HCS88XX 공용 등판(1인 우) 쿠션 마감</t>
+  </si>
+  <si>
+    <t>OPFW004848-R000</t>
+  </si>
+  <si>
+    <t>FBFP039465-R000</t>
+  </si>
+  <si>
+    <t>HCS88XX 공용 등판(1인 우) 쿠션 미싱</t>
+  </si>
+  <si>
+    <t>OPFW004857-R000</t>
+  </si>
+  <si>
+    <t>HCS88XX 공용 등판(1인 좌) 쿠션 마감</t>
+  </si>
+  <si>
+    <t>OPFW004860-R000</t>
+  </si>
+  <si>
+    <t>FBFP039504-R000</t>
+  </si>
+  <si>
+    <t>HCS88XX 공용 등판(1인 좌) 쿠션 미싱</t>
+  </si>
+  <si>
+    <t>OPFW004850-R000</t>
+  </si>
+  <si>
+    <t>HCS88XX 공용 좌판(1인 우) 쿠션 마감</t>
+  </si>
+  <si>
+    <t>OPFW004847-R000</t>
+  </si>
+  <si>
+    <t>FBFP039459-R000</t>
+  </si>
+  <si>
+    <t>HCS88XX 공용 좌판(1인 우) 쿠션 미싱</t>
+  </si>
+  <si>
+    <t>FBFP039479-R000</t>
+  </si>
+  <si>
+    <t>OPFW004862-R000</t>
+  </si>
+  <si>
+    <t>HCS88XX 공용 좌판(1인 좌) 쿠션 마감</t>
+  </si>
+  <si>
+    <t>OPFW004856-R000</t>
+  </si>
+  <si>
+    <t>OPFW004859-R000</t>
+  </si>
+  <si>
+    <t>FBFP039518-R000</t>
+  </si>
+  <si>
+    <t>HCS88XX 공용 좌판(1인 좌) 쿠션 미싱</t>
+  </si>
+  <si>
+    <t>OPFW004849-R000</t>
+  </si>
+  <si>
+    <t>HCS88XX 공용 팔걸이(우) 쿠션 마감</t>
+  </si>
+  <si>
+    <t>OPFW004846-R000</t>
+  </si>
+  <si>
+    <t>FBFP039467-R000</t>
+  </si>
+  <si>
+    <t>HCS88XX 공용 팔걸이(우) 쿠션 미싱</t>
+  </si>
+  <si>
+    <t>OPFW004800-R000</t>
+  </si>
+  <si>
+    <t>HCS88XX 공용 팔걸이(좌) 쿠션 마감</t>
+  </si>
+  <si>
+    <t>OPFW004787-R000</t>
+  </si>
+  <si>
+    <t>OPFW004858-R000</t>
+  </si>
+  <si>
+    <t>FBFP039506-R000</t>
+  </si>
+  <si>
+    <t>HCS88XX 공용 팔걸이(좌) 쿠션 미싱</t>
+  </si>
+  <si>
+    <t>FBFP039421-R000</t>
+  </si>
+  <si>
+    <t>HCS88XX_공용_연결 직물_가죽</t>
+  </si>
+  <si>
+    <t>FBFP039423-R000</t>
+  </si>
+  <si>
+    <t>HCS88XX_공용_연결 직물_패브릭</t>
+  </si>
+  <si>
+    <t>NGCSP3813</t>
+  </si>
+  <si>
+    <t>Holiday mini Basic body (L)</t>
+  </si>
+  <si>
+    <t>NGCSP3814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holiday mini Basic body (R) </t>
+  </si>
+  <si>
+    <t>NGCSB3891</t>
+  </si>
+  <si>
+    <t>Holiday mini Large Cushion</t>
+  </si>
+  <si>
+    <t>NGCSB3892</t>
+  </si>
+  <si>
+    <t>Holiday mini Lumbar Cushion</t>
+  </si>
+  <si>
+    <t>NGCSP3827</t>
+  </si>
+  <si>
+    <t>Holiday mini Terminal (L)</t>
+  </si>
+  <si>
+    <t>NGCSP3828</t>
+  </si>
+  <si>
+    <t>Holiday mini Terminal (R)</t>
+  </si>
+  <si>
+    <t>DSSCAY0701</t>
+  </si>
+  <si>
+    <t>S02 베이스 등받이 타입</t>
+  </si>
+  <si>
+    <t>DSSCAY0700</t>
+  </si>
+  <si>
+    <t>S02 베이스 스툴 타입</t>
+  </si>
+  <si>
+    <t>DSSCAY0702</t>
+  </si>
+  <si>
+    <t>S02 베이스 코너 타입</t>
+  </si>
+  <si>
+    <t>NGCS8800NF</t>
+  </si>
+  <si>
+    <t>Vancouver headrest (fabric)</t>
+  </si>
+  <si>
+    <t>NGCS8800NFA</t>
+  </si>
+  <si>
+    <t>NGCS8800N</t>
+  </si>
+  <si>
+    <t>Vancouver headrest (leather)</t>
+  </si>
+  <si>
+    <t>FBFP047334-R000</t>
+  </si>
+  <si>
+    <t>VN 수리, 벤쿠버 1.5인 (우) 등쿠션 커버</t>
+  </si>
+  <si>
+    <t>FBFP047333-R000</t>
+  </si>
+  <si>
+    <t>VN 수리, 벤쿠버 1.5인 (좌) 등쿠션 커버</t>
+  </si>
+  <si>
+    <t>FBFP047338-R000</t>
+  </si>
+  <si>
+    <t>VN 수리, 벤쿠버 1인 (우) 등쿠션</t>
+  </si>
+  <si>
+    <t>FBFP047337-R000</t>
+  </si>
+  <si>
+    <t>VN 수리, 벤쿠버 1인 (우) 좌방석 커버</t>
+  </si>
+  <si>
+    <t>FBFP047339-R000</t>
+  </si>
+  <si>
+    <t>VN 수리, 벤쿠버 1인 (우) 팔걸이</t>
+  </si>
+  <si>
+    <t>FBFP047341-R000</t>
+  </si>
+  <si>
+    <t>VN 수리, 벤쿠버 3인 (좌) 등쿠션</t>
+  </si>
+  <si>
+    <t>FBFP047340-P000</t>
+  </si>
+  <si>
+    <t>VN 수리, 벤쿠버 3인 (좌) 좌방석 커버 set</t>
+  </si>
+  <si>
+    <t>FBFP047342-R000</t>
+  </si>
+  <si>
+    <t>VN 수리, 벤쿠버 3인 (좌) 팔걸이</t>
+  </si>
+  <si>
+    <t>FBFP047336-R000</t>
+  </si>
+  <si>
+    <t>VN 수리, 벤쿠버 3인 등쿠션 (우)</t>
+  </si>
+  <si>
+    <t>FBFP047335-R000</t>
+  </si>
+  <si>
+    <t>VN 수리, 벤쿠버 3인 등쿠션 (좌)</t>
+  </si>
+  <si>
+    <t>WDWW154842-R000</t>
+  </si>
+  <si>
+    <t>VN 수리, 오브 1.5인 (우) 다리set</t>
+  </si>
+  <si>
+    <t>WDWW154843-R000</t>
+  </si>
+  <si>
+    <t>VN 수리, 오브 1.5인 (좌) 다리set</t>
+  </si>
+  <si>
+    <t>CA0001</t>
+  </si>
+  <si>
+    <t>가죽 관리 키트</t>
+  </si>
+  <si>
+    <t>HCS0001</t>
+  </si>
+  <si>
+    <t>가죽 케어 키트</t>
+  </si>
+  <si>
+    <t>ILC00AA00A</t>
+  </si>
+  <si>
+    <t>공용 가죽 쿠션 (마스트로또)</t>
+  </si>
+  <si>
+    <t>ILC00AA01A</t>
+  </si>
+  <si>
+    <t>공용 가죽 쿠션 (모아브)</t>
+  </si>
+  <si>
+    <t>ISC00DA00A</t>
+  </si>
+  <si>
+    <t>닛 데이베드 등쿠션(패브릭)</t>
+  </si>
+  <si>
+    <t>ISC00DA01A</t>
+  </si>
+  <si>
+    <t>ISM18DA01A</t>
+  </si>
+  <si>
+    <t>닛 데이베드 매트(패브릭)</t>
+  </si>
+  <si>
+    <t>ISM18DA00A</t>
+  </si>
+  <si>
+    <t>WDWW136484-R000</t>
+  </si>
+  <si>
+    <t>대체소파, 카포네 그랑 2인 좌 ACSF2443BN</t>
+  </si>
+  <si>
+    <t>WDWW113538-R000</t>
+  </si>
+  <si>
+    <t>등쿠션(공용) ASS'Y, 클렉트2.0</t>
+  </si>
+  <si>
+    <t>OPFW004095-R000</t>
+  </si>
+  <si>
+    <t>등판쿠션 ASS'Y, 밴쿠버 1.5인_우</t>
+  </si>
+  <si>
+    <t>OPFW004032-R000</t>
+  </si>
+  <si>
+    <t>등판쿠션 ASS'Y, 밴쿠버 1.5인_좌</t>
+  </si>
+  <si>
+    <t>WDWW122152-R000</t>
+  </si>
+  <si>
+    <t>등프레임 ASS'Y, 밴쿠버 1.5인_우</t>
+  </si>
+  <si>
+    <t>ACSB4591S1</t>
+  </si>
+  <si>
+    <t>디딤 라지 쿠션_디자인 패브릭ㅣ부클레 위브_번트 베</t>
+  </si>
+  <si>
+    <t>디딤 라지 쿠션_디자인 패브릭ㅣ부클레 위브_클레어</t>
+  </si>
+  <si>
+    <t>ACSB4591K</t>
+  </si>
+  <si>
+    <t>디딤 라지 쿠션_디자인 패브릭ㅣ크바드라트_순타 라임</t>
+  </si>
+  <si>
+    <t>ACSB4591X2</t>
+  </si>
+  <si>
+    <t>디딤 라지 쿠션_에센셜 패브릭ㅣ솔라_웜 브리즈</t>
+  </si>
+  <si>
+    <t>ACSB4591BN</t>
+  </si>
+  <si>
+    <t>디딤 라지 쿠션_프리미엄 레더ㅣ드리밍 헤비_뮤트 블</t>
+  </si>
+  <si>
+    <t>디딤 라지 쿠션_프리미엄 레더ㅣ드리밍 헤비_파우더</t>
+  </si>
+  <si>
+    <t>ACSB4591GN</t>
+  </si>
+  <si>
+    <t>디딤 라지 쿠션_프리미엄 레더ㅣ르아테_버번</t>
+  </si>
+  <si>
+    <t>ACSB4591R</t>
+  </si>
+  <si>
+    <t>디딤 라지 쿠션_프리미엄 패브릭ㅣ루소_뮤티드 핑크</t>
+  </si>
+  <si>
+    <t>디딤 라지 쿠션_프리미엄 패브릭ㅣ루소_아이린</t>
+  </si>
+  <si>
+    <t>ACSB4591V2</t>
+  </si>
+  <si>
+    <t>디딤 라지 쿠션_프리미엄 패브릭ㅣ스칼렛_머스탱</t>
+  </si>
+  <si>
+    <t>ACSB4594K1</t>
+  </si>
+  <si>
+    <t>디딤 서포트 쿠션_디자인 패브릭ㅣ릴레이트_번트 엄버</t>
+  </si>
+  <si>
+    <t>ACSB4594S1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">디딤 서포트 쿠션_디자인 패브릭ㅣ부클레 위브_번트 </t>
+  </si>
+  <si>
+    <t>ACSB4594K</t>
+  </si>
+  <si>
+    <t>디딤 서포트 쿠션_디자인 패브릭ㅣ크바드라트_순타 라</t>
+  </si>
+  <si>
+    <t>ACSB4594X1</t>
+  </si>
+  <si>
+    <t>디딤 서포트 쿠션_에센셜 패브릭ㅣ노르딕_멜로우 크림</t>
+  </si>
+  <si>
+    <t>ACSB4594X2</t>
+  </si>
+  <si>
+    <t>디딤 서포트 쿠션_에센셜 패브릭ㅣ솔라_웜 브리즈</t>
+  </si>
+  <si>
+    <t>ACSB4594GN</t>
+  </si>
+  <si>
+    <t>디딤 서포트 쿠션_프리미엄 레더ㅣ르아테_버번</t>
+  </si>
+  <si>
+    <t>ACSB4594R</t>
+  </si>
+  <si>
+    <t>디딤 서포트 쿠션_프리미엄 패브릭ㅣ루소_뮤티드 핑크</t>
+  </si>
+  <si>
+    <t>디딤 서포트 쿠션_프리미엄 패브릭ㅣ루소_아이린</t>
+  </si>
+  <si>
+    <t>ACSB4594V2</t>
+  </si>
+  <si>
+    <t>디딤 서포트 쿠션_프리미엄 패브릭ㅣ스칼렛_머스탱</t>
+  </si>
+  <si>
+    <t>ACSB45C1</t>
+  </si>
+  <si>
+    <t>WDWW123059-R000</t>
+  </si>
+  <si>
+    <t>마감, 레지나 리뉴얼 공용 좌판 쿠션</t>
+  </si>
+  <si>
+    <t>ACSP0704K1</t>
+  </si>
+  <si>
+    <t>모브 푸프_디자인 패브릭ㅣ릴레이트_마누카</t>
+  </si>
+  <si>
+    <t>모브 푸프_디자인 패브릭ㅣ릴레이트_모스</t>
+  </si>
+  <si>
+    <t>모브 푸프_디자인 패브릭ㅣ릴레이트_미모사</t>
+  </si>
+  <si>
+    <t>모브 푸프_디자인 패브릭ㅣ릴레이트_민트 밤</t>
+  </si>
+  <si>
+    <t>모브 푸프_디자인 패브릭ㅣ릴레이트_번트 엄버</t>
+  </si>
+  <si>
+    <t>ACSP0704S1</t>
+  </si>
+  <si>
+    <t>모브 푸프_디자인 패브릭ㅣ부클레 위브_번트 베이지</t>
+  </si>
+  <si>
+    <t>모브 푸프_디자인 패브릭ㅣ부클레 위브_클레어</t>
+  </si>
+  <si>
+    <t>ACSP0704S</t>
+  </si>
+  <si>
+    <t>모브 푸프_디자인 패브릭ㅣ부클레_아이스 블루</t>
+  </si>
+  <si>
+    <t>모브 푸프_디자인 패브릭ㅣ부클레_카놀리 크림</t>
+  </si>
+  <si>
+    <t>모브 푸프_디자인 패브릭ㅣ부클레_허니콤</t>
+  </si>
+  <si>
+    <t>ACSP0704JN</t>
+  </si>
+  <si>
+    <t>모브 푸프_에센셜 레더ㅣ소프트 프리모_카멜</t>
+  </si>
+  <si>
+    <t>모브 푸프_에센셜 레더ㅣ소프트 프리모_클라우드</t>
+  </si>
+  <si>
+    <t>모브 푸프_에센셜 레더ㅣ소프트 프리모_피오니</t>
+  </si>
+  <si>
+    <t>ACSP0704X1</t>
+  </si>
+  <si>
+    <t>모브 푸프_에센셜 패브릭ㅣ노르딕_딥 올리브</t>
+  </si>
+  <si>
+    <t>모브 푸프_에센셜 패브릭ㅣ노르딕_멜로우 크림</t>
+  </si>
+  <si>
+    <t>모브 푸프_에센셜 패브릭ㅣ노르딕_핑크 블리스</t>
+  </si>
+  <si>
+    <t>ACSP0704X2</t>
+  </si>
+  <si>
+    <t>모브 푸프_에센셜 패브릭ㅣ솔라_이브닝 허쉬</t>
+  </si>
+  <si>
+    <t>ACSP0704BN</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 레더ㅣ드리밍 헤비_노체</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 레더ㅣ드리밍 헤비_뮤트 블랙</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 레더ㅣ드리밍 헤비_세이지</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 레더ㅣ드리밍 헤비_조이풀 옐로우</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 레더ㅣ드리밍 헤비_카도 마리노</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 레더ㅣ드리밍 헤비_테라 코타</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 레더ㅣ드리밍 헤비_템즈 그레이</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 레더ㅣ드리밍 헤비_파나마</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 레더ㅣ드리밍 헤비_파우더</t>
+  </si>
+  <si>
+    <t>ACSP0704GN</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 레더ㅣ르아테_모빅</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 레더ㅣ르아테_모튼</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 레더ㅣ르아테_버번</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 레더ㅣ르아테_셔우드 탠</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 레더ㅣ르아테_오비드</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 레더ㅣ르아테_온드</t>
+  </si>
+  <si>
+    <t>ACSP0704R</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 패브릭ㅣ루소_아이린</t>
+  </si>
+  <si>
+    <t>ACSP0704V2</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 패브릭ㅣ스칼렛_마리골드</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 패브릭ㅣ스칼렛_머스탱</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 패브릭ㅣ스칼렛_쉘</t>
+  </si>
+  <si>
+    <t>ACSP0704T</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 패브릭ㅣ아크레_몬드</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 패브릭ㅣ아크레_블러쉬</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 패브릭ㅣ아크레_블루 베이</t>
+  </si>
+  <si>
+    <t>모브 푸프_프리미엄 패브릭ㅣ아크레_샤모아</t>
+  </si>
+  <si>
+    <t>ACSP0704HN</t>
+  </si>
+  <si>
+    <t>모브 푸프_하이엔드 레더ㅣ단테_마쉬</t>
+  </si>
+  <si>
+    <t>WDWW122977-R000</t>
+  </si>
+  <si>
+    <t>밀로 공용 등판(소)/팔걸이 가드 ASS'Y</t>
+  </si>
+  <si>
+    <t>OPFW004242-R000</t>
+  </si>
+  <si>
+    <t>밀로 공용 좌판쿠션(대) ASS'Y</t>
+  </si>
+  <si>
+    <t>OPFW004258-R000</t>
+  </si>
+  <si>
+    <t>밀로 공용 좌판쿠션(소) ASS'Y</t>
+  </si>
+  <si>
+    <t>ACSB3091BN</t>
+  </si>
+  <si>
+    <t>밀로 라지 쿠션_프리미엄 레더ㅣ드리밍 헤비_노체</t>
+  </si>
+  <si>
+    <t>밀로 라지 쿠션_프리미엄 레더ㅣ드리밍 헤비_템즈 그</t>
+  </si>
+  <si>
+    <t>밀로 라지 쿠션_프리미엄 레더ㅣ드리밍 헤비_파우더</t>
+  </si>
+  <si>
+    <t>ACSB3091GN</t>
+  </si>
+  <si>
+    <t>밀로 라지 쿠션_프리미엄 레더ㅣ르아테_모빅</t>
+  </si>
+  <si>
+    <t>밀로 라지 쿠션_프리미엄 레더ㅣ르아테_버번</t>
+  </si>
+  <si>
+    <t>밀로 라지 쿠션_프리미엄 레더ㅣ르아테_셔우드 탠</t>
+  </si>
+  <si>
+    <t>밀로 라지 쿠션_프리미엄 레더ㅣ르아테_오비드</t>
+  </si>
+  <si>
+    <t>밀로 라지 쿠션_프리미엄 레더ㅣ르아테_온드</t>
+  </si>
+  <si>
+    <t>ACSB3091R</t>
+  </si>
+  <si>
+    <t>밀로 라지 쿠션_프리미엄 패브릭ㅣ루소_뮤티드 핑크</t>
+  </si>
+  <si>
+    <t>밀로 라지 쿠션_프리미엄 패브릭ㅣ루소_아이린</t>
+  </si>
+  <si>
+    <t>ACSB3091T</t>
+  </si>
+  <si>
+    <t>밀로 라지 쿠션_프리미엄 패브릭ㅣ아크레_몬드</t>
+  </si>
+  <si>
+    <t>밀로 라지 쿠션_프리미엄 패브릭ㅣ아크레_블러쉬</t>
+  </si>
+  <si>
+    <t>밀로 라지 쿠션_프리미엄 패브릭ㅣ아크레_샤모아</t>
+  </si>
+  <si>
+    <t>ACSB3091HN</t>
+  </si>
+  <si>
+    <t>밀로 라지 쿠션_하이엔드 레더ㅣ단테_마쉬</t>
+  </si>
+  <si>
+    <t>밀로 라지 쿠션_하이엔드 레더ㅣ단테_머스키 블랙</t>
+  </si>
+  <si>
+    <t>밀로 라지 쿠션_하이엔드 레더ㅣ단테_토프</t>
+  </si>
+  <si>
+    <t>ACSB3091CN</t>
+  </si>
+  <si>
+    <t>밀로 라지 쿠션_하이엔드 레더ㅣ베지탄_쿠오이오</t>
+  </si>
+  <si>
+    <t>ACSB3092BN</t>
+  </si>
+  <si>
+    <t>밀로 럼버 쿠션_프리미엄 레더ㅣ드리밍 헤비_뮤트 블</t>
+  </si>
+  <si>
+    <t>밀로 럼버 쿠션_프리미엄 레더ㅣ드리밍 헤비_파우더</t>
+  </si>
+  <si>
+    <t>ACSB3092GN</t>
+  </si>
+  <si>
+    <t>밀로 럼버 쿠션_프리미엄 레더ㅣ르아테_모빅</t>
+  </si>
+  <si>
+    <t>ACSB3092HN</t>
+  </si>
+  <si>
+    <t>밀로 럼버 쿠션_하이엔드 레더ㅣ단테_마쉬</t>
+  </si>
+  <si>
+    <t>ACSB3093GN</t>
+  </si>
+  <si>
+    <t>밀로 사이드 쿠션_프리미엄 레더ㅣ르아테_모빅</t>
+  </si>
+  <si>
+    <t>밀로 사이드 쿠션_프리미엄 레더ㅣ르아테_버번</t>
+  </si>
+  <si>
+    <t>ACSB3093R</t>
+  </si>
+  <si>
+    <t>밀로 사이드 쿠션_프리미엄 패브릭ㅣ루소_셀릭</t>
+  </si>
+  <si>
+    <t>FBFP036263-R000</t>
+  </si>
+  <si>
+    <t>밀로(ACSB30) 럼버쿠션 ASSY</t>
+  </si>
+  <si>
+    <t>FBFP036264-R000</t>
+  </si>
+  <si>
+    <t>밀로(ACSB30) 사이드쿠션 ASSY</t>
+  </si>
+  <si>
+    <t>ACSB3794X1</t>
+  </si>
+  <si>
+    <t>바드 플랫 쿠션_에센셜 패브릭ㅣ노르딕_딥 올리브</t>
+  </si>
+  <si>
+    <t>ACSB3794X2</t>
+  </si>
+  <si>
+    <t>바드 플랫 쿠션_에센셜 패브릭ㅣ솔라_그레이 아울</t>
+  </si>
+  <si>
+    <t>ACSB3794BN</t>
+  </si>
+  <si>
+    <t>바드 플랫 쿠션_프리미엄 레더ㅣ드리밍 헤비_뮤트 블</t>
+  </si>
+  <si>
+    <t>바드 플랫 쿠션_프리미엄 레더ㅣ드리밍 헤비_파우더</t>
+  </si>
+  <si>
+    <t>ACSB3794GN</t>
+  </si>
+  <si>
+    <t>바드 플랫 쿠션_프리미엄 레더ㅣ르아테_모빅</t>
+  </si>
+  <si>
+    <t>바드 플랫 쿠션_프리미엄 레더ㅣ르아테_모튼</t>
+  </si>
+  <si>
+    <t>바드 플랫 쿠션_프리미엄 레더ㅣ르아테_버번</t>
+  </si>
+  <si>
+    <t>바드 플랫 쿠션_프리미엄 레더ㅣ르아테_오비드</t>
+  </si>
+  <si>
+    <t>바드 플랫 쿠션_프리미엄 레더ㅣ르아테_온드</t>
+  </si>
+  <si>
+    <t>ACSB3794V2</t>
+  </si>
+  <si>
+    <t>바드 플랫 쿠션_프리미엄 패브릭ㅣ스칼렛_쉘</t>
+  </si>
+  <si>
+    <t>HCS8818U</t>
+  </si>
+  <si>
+    <t>HCS8813U</t>
+  </si>
+  <si>
+    <t>밴쿠버 3인 철제다리</t>
+  </si>
+  <si>
+    <t>HCS8814U</t>
+  </si>
+  <si>
+    <t>HCS8800U</t>
+  </si>
+  <si>
+    <t>밴쿠버 스툴 철제다리</t>
+  </si>
+  <si>
+    <t>밴쿠버 스툴(가죽)_엘지앤솔</t>
+  </si>
+  <si>
+    <t>HCS8800FA</t>
+  </si>
+  <si>
+    <t>밴쿠버 스툴(패브릭)</t>
+  </si>
+  <si>
+    <t>HCS8800F</t>
+  </si>
+  <si>
+    <t>HCS8800N</t>
+  </si>
+  <si>
+    <t>밴쿠버 헤드레스트(가죽)_엘지앤솔</t>
+  </si>
+  <si>
+    <t>HCS8800NF</t>
+  </si>
+  <si>
+    <t>밴쿠버 헤드레스트(패브릭)</t>
+  </si>
+  <si>
+    <t>HCS8800NFA</t>
+  </si>
+  <si>
+    <t>WDWW151508-R000</t>
+  </si>
+  <si>
+    <t>밴쿠버 헤드레스트(패브릭) (프레임 제외)</t>
+  </si>
+  <si>
+    <t>ACSB1161JN</t>
+  </si>
+  <si>
+    <t>베르디 1인_에센셜 레더ㅣ소프트 프리모_카멜</t>
+  </si>
+  <si>
+    <t>ACSB1161BN</t>
+  </si>
+  <si>
+    <t>베르디 1인_프리미엄 레더ㅣ드리밍 헤비_카도 마리노</t>
+  </si>
+  <si>
+    <t>ACSB1161GN</t>
+  </si>
+  <si>
+    <t>베르디 1인_프리미엄 레더ㅣ르아테_모빅</t>
+  </si>
+  <si>
+    <t>베르디 1인_프리미엄 레더ㅣ르아테_버번</t>
+  </si>
+  <si>
+    <t>WDWW164072-R000</t>
+  </si>
+  <si>
+    <t>베르디 조립&amp;포장 진행 FACSB1161BN</t>
+  </si>
+  <si>
+    <t>WDWW164071-R000</t>
+  </si>
+  <si>
+    <t>WDWW164069-R000</t>
+  </si>
+  <si>
+    <t>WDWW164070-R000</t>
+  </si>
+  <si>
+    <t>베르디 조립&amp;포장 진행 FACSB1161GN</t>
+  </si>
+  <si>
+    <t>WDWW122154-R000</t>
+  </si>
+  <si>
+    <t>베이스 ASS'Y, 밴쿠버 1.5인_우</t>
+  </si>
+  <si>
+    <t>ACSL001</t>
+  </si>
+  <si>
+    <t>베이스 타입 001 (2EA)</t>
+  </si>
+  <si>
+    <t>ACSL002</t>
+  </si>
+  <si>
+    <t>베이스 타입 002 (2EA)</t>
+  </si>
+  <si>
+    <t>ACSL003</t>
+  </si>
+  <si>
+    <t>베이스 타입 003 (4EA)</t>
+  </si>
+  <si>
+    <t>ACSL006</t>
+  </si>
+  <si>
+    <t>베이스 타입 006 (4EA)</t>
+  </si>
+  <si>
+    <t>ACSL007</t>
+  </si>
+  <si>
+    <t>베이스 타입 007 (4EA)</t>
+  </si>
+  <si>
+    <t>CS6402B</t>
+  </si>
+  <si>
+    <t>벤치형 스툴</t>
+  </si>
+  <si>
+    <t>WDWW164956-R000</t>
+  </si>
+  <si>
+    <t>벤쿠버 헤드레스트 지퍼방식 개선사양</t>
+  </si>
+  <si>
+    <t>WDWW164957-R000</t>
+  </si>
+  <si>
+    <t>HCS8101N</t>
+  </si>
+  <si>
+    <t>볼케S(P가죽,전동)</t>
+  </si>
+  <si>
+    <t>볼케S(가죽,전동)</t>
+  </si>
+  <si>
+    <t>OPFW005622-R000</t>
+  </si>
+  <si>
+    <t>샘플, 코펜하겐 1인 좌 스펀지 본딩</t>
+  </si>
+  <si>
+    <t>OPFW005623-R000</t>
+  </si>
+  <si>
+    <t>샘플, 코펜하겐 카우치 우 스펀지 본딩</t>
+  </si>
+  <si>
+    <t>OPFW005624-R000</t>
+  </si>
+  <si>
+    <t>샘플, 코펜하겐 코너 스펀지 본딩</t>
+  </si>
+  <si>
+    <t>ITHCS8813U</t>
+  </si>
+  <si>
+    <t>수출용코드-밴쿠버 3인 철제다리</t>
+  </si>
+  <si>
+    <t>ITHCS8811R</t>
+  </si>
+  <si>
+    <t>수출용코드-벤쿠버 1인 몸통 우(가죽)</t>
+  </si>
+  <si>
+    <t>ITHCS8818U</t>
+  </si>
+  <si>
+    <t>수출용코드-벤쿠버 3.5인 다리</t>
+  </si>
+  <si>
+    <t>ITHCS8813L</t>
+  </si>
+  <si>
+    <t>수출용코드-벤쿠버 3인 몸통 좌(가죽)</t>
+  </si>
+  <si>
+    <t>ITHCS8814U</t>
+  </si>
+  <si>
+    <t>수출용코드-벤쿠버 4인 다리</t>
+  </si>
+  <si>
+    <t>ACSB3392GN</t>
+  </si>
+  <si>
+    <t>스탠 럼버 쿠션_프리미엄 레더ㅣ르아테_온드</t>
+  </si>
+  <si>
+    <t>CS6401SM</t>
+  </si>
+  <si>
+    <t>스툴</t>
+  </si>
+  <si>
+    <t>CS6411RM</t>
+  </si>
+  <si>
+    <t>CS6401PM</t>
+  </si>
+  <si>
+    <t>CS6411SM</t>
+  </si>
+  <si>
+    <t>CS6401RM</t>
+  </si>
+  <si>
+    <t>CHXZ603003</t>
+  </si>
+  <si>
+    <t>시팅 패드 - 이지클린</t>
+  </si>
+  <si>
+    <t>AXXZ405001</t>
+  </si>
+  <si>
+    <t>알로소 판촉용 쿠션 M_4S7</t>
+  </si>
+  <si>
+    <t>알로소 판촉용 쿠션 M_L817</t>
+  </si>
+  <si>
+    <t>ACSP0594X1</t>
+  </si>
+  <si>
+    <t>알로소 펫 스텝_에센셜 패브릭ㅣ노르딕_딥 올리브</t>
+  </si>
+  <si>
+    <t>알로소 펫 스텝_에센셜 패브릭ㅣ노르딕_멜로우 크림</t>
+  </si>
+  <si>
+    <t>알로소 펫 스텝_에센셜 패브릭ㅣ노르딕_핑크 블리스</t>
+  </si>
+  <si>
+    <t>ACSP0594X2</t>
+  </si>
+  <si>
+    <t>알로소 펫 스텝_에센셜 패브릭ㅣ솔라_그레이 아울</t>
+  </si>
+  <si>
+    <t>알로소 펫 스텝_에센셜 패브릭ㅣ솔라_웜 브리즈</t>
+  </si>
+  <si>
+    <t>알로소 펫 스텝_에센셜 패브릭ㅣ솔라_이브닝 허쉬</t>
+  </si>
+  <si>
+    <t>ACSP0594R</t>
+  </si>
+  <si>
+    <t>알로소 펫 스텝_프리미엄 패브릭ㅣ루소_뮤티드 핑크</t>
+  </si>
+  <si>
+    <t>알로소 펫 스텝_프리미엄 패브릭ㅣ루소_아이린</t>
+  </si>
+  <si>
+    <t>ACSP0594V2</t>
+  </si>
+  <si>
+    <t>알로소 펫 스텝_프리미엄 패브릭ㅣ스칼렛_마리골드</t>
+  </si>
+  <si>
+    <t>알로소 펫 스텝_프리미엄 패브릭ㅣ스칼렛_머스탱</t>
+  </si>
+  <si>
+    <t>알로소 펫 스텝_프리미엄 패브릭ㅣ스칼렛_쉘</t>
+  </si>
+  <si>
+    <t>ACSP0594T</t>
+  </si>
+  <si>
+    <t>알로소 펫 스텝_프리미엄 패브릭ㅣ아크레_달리아</t>
+  </si>
+  <si>
+    <t>알로소 펫 스텝_프리미엄 패브릭ㅣ아크레_몬드</t>
+  </si>
+  <si>
+    <t>알로소 펫 스텝_프리미엄 패브릭ㅣ아크레_블러쉬</t>
+  </si>
+  <si>
+    <t>알로소 펫 스텝_프리미엄 패브릭ㅣ아크레_블루 베이</t>
+  </si>
+  <si>
+    <t>알로소 펫 스텝_프리미엄 패브릭ㅣ아크레_샤모아</t>
+  </si>
+  <si>
+    <t>ACSB2598BN</t>
+  </si>
+  <si>
+    <t>엘머 롱삭스_프리미엄 레더ㅣ드리밍 헤비_파우더</t>
+  </si>
+  <si>
+    <t>ACSB2599BN</t>
+  </si>
+  <si>
+    <t>엘머 숏삭스_프리미엄 레더ㅣ드리밍 헤비_파우더</t>
+  </si>
+  <si>
+    <t>ISC00CX01A</t>
+  </si>
+  <si>
+    <t>오브 플레인 헤드레스트(패브릭)</t>
+  </si>
+  <si>
+    <t>ISC00CX02A</t>
+  </si>
+  <si>
+    <t>오브 헤드레스트(부클)</t>
+  </si>
+  <si>
+    <t>ISC00CX00A</t>
+  </si>
+  <si>
+    <t>오브 헤드레스트(패브릭)</t>
+  </si>
+  <si>
+    <t>CS6403P</t>
+  </si>
+  <si>
+    <t>오토만</t>
+  </si>
+  <si>
+    <t>CS6403S</t>
+  </si>
+  <si>
+    <t>CS6403R</t>
+  </si>
+  <si>
+    <t>WDWW128784-R000</t>
+  </si>
+  <si>
+    <t>좌방석 ASS'Y, 홀리데이 미니(ACSP38) 2인</t>
+  </si>
+  <si>
+    <t>WDWW113537-R000</t>
+  </si>
+  <si>
+    <t>좌방석(공용) ASS'Y, 클렉트2.0</t>
+  </si>
+  <si>
+    <t>OPFW004035-R000</t>
+  </si>
+  <si>
+    <t>좌판쿠션 ASS'Y, 밴쿠버 1.5인_좌</t>
+  </si>
+  <si>
+    <t>OPFW004162-R000</t>
+  </si>
+  <si>
+    <t>좌판쿠션 ASS'Y, 밴쿠버 1인_좌</t>
+  </si>
+  <si>
+    <t>WAE0190</t>
+  </si>
+  <si>
+    <t>진찰대 매트리스</t>
+  </si>
+  <si>
+    <t>HPEA9001F</t>
+  </si>
+  <si>
+    <t>캐스터네츠 펫스텝 (패브릭)</t>
+  </si>
+  <si>
+    <t>FBFP036186-R000</t>
+  </si>
+  <si>
+    <t>커버, 밀로(ACSB30) 공용 등판(소)/팔걸이_GN</t>
+  </si>
+  <si>
+    <t>FBFP036163-R000</t>
+  </si>
+  <si>
+    <t>커버, 밀로(ACSB30) 공용 럼버쿠션_BN</t>
+  </si>
+  <si>
+    <t>FBFP036199-R000</t>
+  </si>
+  <si>
+    <t>커버, 밀로(ACSB30) 공용 럼버쿠션_HN</t>
+  </si>
+  <si>
+    <t>FBFP036164-R000</t>
+  </si>
+  <si>
+    <t>커버, 밀로(ACSB30) 공용 사이드쿠션_BN</t>
+  </si>
+  <si>
+    <t>FBFP036162-R000</t>
+  </si>
+  <si>
+    <t>커버, 밀로(ACSB30) 공용 좌판쿠션(대)_BN</t>
+  </si>
+  <si>
+    <t>FBFP036189-R000</t>
+  </si>
+  <si>
+    <t>커버, 밀로(ACSB30) 공용 좌판쿠션(대)_GN</t>
+  </si>
+  <si>
+    <t>FBFP036213-R000</t>
+  </si>
+  <si>
+    <t>커버, 밀로(ACSB30) 공용 좌판쿠션(소)_GN</t>
+  </si>
+  <si>
+    <t>FBFP035464-R000</t>
+  </si>
+  <si>
+    <t>커버, 밴쿠버 1.5인 우(HCS8812)_등판쿠션_패브릭</t>
+  </si>
+  <si>
+    <t>FBFP035465-R000</t>
+  </si>
+  <si>
+    <t>커버, 밴쿠버 1.5인 우(HCS8812)_몸통_패브릭</t>
+  </si>
+  <si>
+    <t>FBFP035391-R000</t>
+  </si>
+  <si>
+    <t>커버, 밴쿠버 1.5인 좌(HCS8812)_등판쿠션_패브릭</t>
+  </si>
+  <si>
+    <t>FBFP035389-R000</t>
+  </si>
+  <si>
+    <t>커버, 밴쿠버 1.5인 좌(HCS8812)_좌판쿠션_패브릭</t>
+  </si>
+  <si>
+    <t>FBFP035711-R000</t>
+  </si>
+  <si>
+    <t>커버, 밴쿠버(HCS88) 1인 좌_좌판쿠션_가죽</t>
+  </si>
+  <si>
+    <t>FBFP035409-R000</t>
+  </si>
+  <si>
+    <t>커버, 밴쿠버(HCS88)_공용_연결직물_패브릭</t>
+  </si>
+  <si>
+    <t>FBFP033161-R000</t>
+  </si>
+  <si>
+    <t>커버, 클렉트2.0 공용_등쿠션_BN</t>
+  </si>
+  <si>
+    <t>FBFP033160-R000</t>
+  </si>
+  <si>
+    <t>커버, 클렉트2.0 공용_좌방석_BN</t>
+  </si>
+  <si>
+    <t>FBFP043605-R000</t>
+  </si>
+  <si>
+    <t>커버, 홀리데이 미니(ACSP38) 2인_좌/우 좌방석_X2</t>
+  </si>
+  <si>
+    <t>FBFP039083-R000</t>
+  </si>
+  <si>
+    <t>커버, 홀리데이(ACSB38) 공용 럼버쿠션</t>
+  </si>
+  <si>
+    <t>ACSB2391JN</t>
+  </si>
+  <si>
+    <t>케렌시아 럼버 쿠션_에센셜 레더ㅣ소프트 프리모_카멜</t>
+  </si>
+  <si>
+    <t>케렌시아 럼버 쿠션_에센셜 레더ㅣ소프트 프리모_피오</t>
+  </si>
+  <si>
+    <t>ACSB2391X1</t>
+  </si>
+  <si>
+    <t>케렌시아 럼버 쿠션_에센셜 패브릭ㅣ노르딕_핑크 블리</t>
+  </si>
+  <si>
+    <t>ACSB2391BN</t>
+  </si>
+  <si>
+    <t>케렌시아 럼버 쿠션_프리미엄 레더ㅣ드리밍 헤비_노체</t>
+  </si>
+  <si>
+    <t>ACSB2391GN</t>
+  </si>
+  <si>
+    <t>케렌시아 럼버 쿠션_프리미엄 레더ㅣ르아테_모빅</t>
+  </si>
+  <si>
+    <t>케렌시아 럼버 쿠션_프리미엄 레더ㅣ르아테_버번</t>
+  </si>
+  <si>
+    <t>케렌시아 럼버 쿠션_프리미엄 레더ㅣ르아테_오비드</t>
+  </si>
+  <si>
+    <t>ACSB2391V2</t>
+  </si>
+  <si>
+    <t>케렌시아 럼버 쿠션_프리미엄 패브릭ㅣ스칼렛_머스탱</t>
+  </si>
+  <si>
+    <t>케렌시아 럼버 쿠션_프리미엄 패브릭ㅣ스칼렛_쉘</t>
+  </si>
+  <si>
+    <t>ACSB2391T</t>
+  </si>
+  <si>
+    <t>케렌시아 럼버 쿠션_프리미엄 패브릭ㅣ아크레_샤모아</t>
+  </si>
+  <si>
+    <t>ACSB2390JN</t>
+  </si>
+  <si>
+    <t>케렌시아 사이드 쿠션_에센셜 레더ㅣ소프트 프리모_피</t>
+  </si>
+  <si>
+    <t>ACSB2390X1</t>
+  </si>
+  <si>
+    <t>케렌시아 사이드 쿠션_에센셜 패브릭ㅣ노르딕_핑크 블</t>
+  </si>
+  <si>
+    <t>ACSB2390BN</t>
+  </si>
+  <si>
+    <t>케렌시아 사이드 쿠션_프리미엄 레더ㅣ드리밍 헤비_노</t>
+  </si>
+  <si>
+    <t>케렌시아 사이드 쿠션_프리미엄 레더ㅣ드리밍 헤비_올</t>
+  </si>
+  <si>
+    <t>케렌시아 사이드 쿠션_프리미엄 레더ㅣ드리밍 헤비_파</t>
+  </si>
+  <si>
+    <t>ACSB2390GN</t>
+  </si>
+  <si>
+    <t>케렌시아 사이드 쿠션_프리미엄 레더ㅣ르아테_모빅</t>
+  </si>
+  <si>
+    <t>케렌시아 사이드 쿠션_프리미엄 레더ㅣ르아테_버번</t>
+  </si>
+  <si>
+    <t>케렌시아 사이드 쿠션_프리미엄 레더ㅣ르아테_오비드</t>
+  </si>
+  <si>
+    <t>ACSB2390V2</t>
+  </si>
+  <si>
+    <t>케렌시아 사이드 쿠션_프리미엄 패브릭ㅣ스칼렛_머스</t>
+  </si>
+  <si>
+    <t>케렌시아 사이드 쿠션_프리미엄 패브릭ㅣ스칼렛_쉘</t>
+  </si>
+  <si>
+    <t>ACSB2390T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">케렌시아 사이드 쿠션_프리미엄 패브릭ㅣ아크레_블루 </t>
+  </si>
+  <si>
+    <t>ACSB2394V1</t>
+  </si>
+  <si>
+    <t>케렌시아 페이브 쿠션_디자인 패브릭ㅣ라리오_시나몬</t>
+  </si>
+  <si>
+    <t>ACSB2394S1</t>
+  </si>
+  <si>
+    <t>케렌시아 페이브 쿠션_디자인 패브릭ㅣ부클레 위브_번</t>
+  </si>
+  <si>
+    <t>케렌시아 페이브 쿠션_디자인 패브릭ㅣ부클레 위브_클</t>
+  </si>
+  <si>
+    <t>ACSB2394S</t>
+  </si>
+  <si>
+    <t>케렌시아 페이브 쿠션_디자인 패브릭ㅣ부클레_올리바</t>
+  </si>
+  <si>
+    <t>케렌시아 페이브 쿠션_디자인 패브릭ㅣ부클레_카놀리</t>
+  </si>
+  <si>
+    <t>ACSB2394X1</t>
+  </si>
+  <si>
+    <t>케렌시아 페이브 쿠션_에센셜 패브릭ㅣ노르딕_멜로우</t>
+  </si>
+  <si>
+    <t>케렌시아 페이브 쿠션_에센셜 패브릭ㅣ노르딕_핑크블</t>
+  </si>
+  <si>
+    <t>ACSB2394T</t>
+  </si>
+  <si>
+    <t>케렌시아 페이브 쿠션_에센셜 패브릭ㅣ아크레_블러쉬</t>
+  </si>
+  <si>
+    <t>케렌시아 페이브 쿠션_에센셜 패브릭ㅣ아크레_샤모아</t>
+  </si>
+  <si>
+    <t>ACSB2394BN</t>
+  </si>
+  <si>
+    <t>케렌시아 페이브 쿠션_프리미엄 레더ㅣ드리밍 헤비_파</t>
+  </si>
+  <si>
+    <t>ACSB2394GN</t>
+  </si>
+  <si>
+    <t>케렌시아 페이브 쿠션_프리미엄 레더ㅣ르아테_모빅</t>
+  </si>
+  <si>
+    <t>케렌시아 페이브 쿠션_프리미엄 레더ㅣ르아테_버번</t>
+  </si>
+  <si>
+    <t>ACSB2394R</t>
+  </si>
+  <si>
+    <t>케렌시아 페이브 쿠션_프리미엄 패브릭ㅣ루소_뮤티드</t>
+  </si>
+  <si>
+    <t>케렌시아 페이브 쿠션_프리미엄 패브릭ㅣ루소_아이린</t>
+  </si>
+  <si>
+    <t>ACSB2394V2</t>
+  </si>
+  <si>
+    <t>케렌시아 페이브 쿠션_프리미엄 패브릭ㅣ스칼렛_머스</t>
+  </si>
+  <si>
+    <t>케렌시아 페이브 쿠션_프리미엄 패브릭ㅣ스칼렛_쉘</t>
+  </si>
+  <si>
+    <t>WDWW126795-R000</t>
+  </si>
+  <si>
+    <t>쿠션 ASS'Y, 홀리데이(ACSB38) 럼버쿠션</t>
+  </si>
+  <si>
+    <t>ACSB3691BN</t>
+  </si>
+  <si>
+    <t>클렉트 하이백 쿠션_프리미엄 레더ㅣ드리밍 헤비_파우</t>
+  </si>
+  <si>
+    <t>ACSB3491BN</t>
+  </si>
+  <si>
+    <t>테오 라지 쿠션_프리미엄 레더ㅣ드리밍 헤비_테라 코</t>
+  </si>
+  <si>
+    <t>테오 라지 쿠션_프리미엄 레더ㅣ드리밍 헤비_파우더</t>
+  </si>
+  <si>
+    <t>ACSB3491GN</t>
+  </si>
+  <si>
+    <t>테오 라지 쿠션_프리미엄 레더ㅣ르아테_모빅</t>
+  </si>
+  <si>
+    <t>테오 라지 쿠션_프리미엄 레더ㅣ르아테_셔우드 탠</t>
+  </si>
+  <si>
+    <t>테오 라지 쿠션_프리미엄 레더ㅣ르아테_오비드</t>
+  </si>
+  <si>
+    <t>테오 라지 쿠션_프리미엄 레더ㅣ르아테_온드</t>
+  </si>
+  <si>
+    <t>ACSB3491CN</t>
+  </si>
+  <si>
+    <t>테오 라지 쿠션_하이엔드 레더ㅣ베지탄_사하라</t>
+  </si>
+  <si>
+    <t>테오 라지 쿠션_하이엔드 레더ㅣ베지탄_프렌치 모이어</t>
+  </si>
+  <si>
+    <t>ACSB3494T</t>
+  </si>
+  <si>
+    <t>테오 플랫 쿠션_프리미엄 패브릭ㅣ아크레_샤모아</t>
+  </si>
+  <si>
+    <t>ETPJ006377-R000</t>
+  </si>
+  <si>
+    <t>포장 철물, 카포네 그랑 1인 (좌/우)</t>
+  </si>
+  <si>
+    <t>ETFS002365-R000</t>
+  </si>
+  <si>
+    <t>포장 철물, 클렉트2.0 2인(좌/우)_ACSB3613/ACSB3614</t>
+  </si>
+  <si>
+    <t>WDWW164075-R000</t>
+  </si>
+  <si>
+    <t>폴디 민자 직사각 (2인) CS6402B</t>
+  </si>
+  <si>
+    <t>WDWW164078-R000</t>
+  </si>
+  <si>
+    <t>폴디 사각절개형 이동형 CS6401SM</t>
+  </si>
+  <si>
+    <t>WDWW164077-R000</t>
+  </si>
+  <si>
+    <t>WDWW164076-R000</t>
+  </si>
+  <si>
+    <t>폴디 절개 사각 CS6401SM</t>
+  </si>
+  <si>
+    <t>WDWW164073-R000</t>
+  </si>
+  <si>
+    <t>폴디 절개 오각 포장 CS6401PM</t>
+  </si>
+  <si>
+    <t>WDWW164074-R000</t>
+  </si>
+  <si>
+    <t>폴디 절개 원형 CS6401RM</t>
+  </si>
+  <si>
+    <t>ISC00DB00A</t>
+  </si>
+  <si>
+    <t>플로코 2-WAY 등받이 쿠션</t>
+  </si>
+  <si>
+    <t>ISC00DB01A</t>
+  </si>
+  <si>
+    <t>ISC00DB02A</t>
+  </si>
+  <si>
+    <t>플로코 2-WAY 등받이 쿠션 커버</t>
+  </si>
+  <si>
+    <t>ISC00DB03A</t>
+  </si>
+  <si>
+    <t>ISY10DB01A</t>
+  </si>
+  <si>
+    <t>플로코 낮은 팔걸이 모듈 (패브릭,와이드)</t>
+  </si>
+  <si>
+    <t>ISY10DB04A</t>
+  </si>
+  <si>
+    <t>ISC10DB01A</t>
+  </si>
+  <si>
+    <t>플로코 낮은 팔걸이 모듈 커버 (패브릭,와이드)</t>
+  </si>
+  <si>
+    <t>ISC10DB04A</t>
+  </si>
+  <si>
+    <t>ISY07DB00A</t>
+  </si>
+  <si>
+    <t>플로코 등판 모듈 (패브릭,베이직)</t>
+  </si>
+  <si>
+    <t>ISY07DB02A</t>
+  </si>
+  <si>
+    <t>ISC07DB00A</t>
+  </si>
+  <si>
+    <t>플로코 등판 모듈 커버 (패브릭,베이직)</t>
+  </si>
+  <si>
+    <t>ISC07DB02A</t>
+  </si>
+  <si>
+    <t>플로코 등판 모듈 커버(패브릭,베이직)</t>
+  </si>
+  <si>
+    <t>ISY10DB00A</t>
+  </si>
+  <si>
+    <t>플로코 등판,팔걸이 모듈 (패브릭,와이드)</t>
+  </si>
+  <si>
+    <t>ISY10DB03A</t>
+  </si>
+  <si>
+    <t>ISC10DB00A</t>
+  </si>
+  <si>
+    <t>플로코 등판,팔걸이 모듈 커버 (패브릭,와이드)</t>
+  </si>
+  <si>
+    <t>ISC10DB03A</t>
+  </si>
+  <si>
+    <t>플로코 등판,팔걸이 모듈 커버(패브릭,와이드)</t>
+  </si>
+  <si>
+    <t>ISY07DB01A</t>
+  </si>
+  <si>
+    <t>플로코 좌판 모듈 (패브릭,베이직)</t>
+  </si>
+  <si>
+    <t>ISY07DB03A</t>
+  </si>
+  <si>
+    <t>ISY10DB05A</t>
+  </si>
+  <si>
+    <t>플로코 좌판 모듈 (패브릭,와이드)</t>
+  </si>
+  <si>
+    <t>ISY10DB02A</t>
+  </si>
+  <si>
+    <t>ISC07DB01A</t>
+  </si>
+  <si>
+    <t>플로코 좌판 모듈 커버 (패브릭,베이직)</t>
+  </si>
+  <si>
+    <t>ISC10DB02A</t>
+  </si>
+  <si>
+    <t>플로코 좌판 모듈 커버 (패브릭,와이드)</t>
+  </si>
+  <si>
+    <t>ISC07DB03A</t>
+  </si>
+  <si>
+    <t>플로코 좌판 모듈 커버(패브릭,베이직)</t>
+  </si>
+  <si>
+    <t>ISC10DB05A</t>
+  </si>
+  <si>
+    <t>플로코 좌판 모듈 커버(패브릭,와이드)</t>
+  </si>
+  <si>
+    <t>ACSB3891S1</t>
+  </si>
+  <si>
+    <t>홀리데이 라지 쿠션_디자인 패브릭ㅣ부클레 위브_클레</t>
+  </si>
+  <si>
+    <t>ACSB3891X1</t>
+  </si>
+  <si>
+    <t>홀리데이 라지 쿠션_에센셜 패브릭ㅣ노르딕_딥 올리브</t>
+  </si>
+  <si>
+    <t>홀리데이 라지 쿠션_에센셜 패브릭ㅣ노르딕_멜로우 크</t>
+  </si>
+  <si>
+    <t>홀리데이 라지 쿠션_에센셜 패브릭ㅣ노르딕_핑크 블리</t>
+  </si>
+  <si>
+    <t>ACSB3891X2</t>
+  </si>
+  <si>
+    <t>홀리데이 라지 쿠션_에센셜 패브릭ㅣ솔라_그레이 아울</t>
+  </si>
+  <si>
+    <t>홀리데이 라지 쿠션_에센셜 패브릭ㅣ솔라_웜 브리즈</t>
+  </si>
+  <si>
+    <t>ACSB3891R</t>
+  </si>
+  <si>
+    <t>홀리데이 라지 쿠션_프리미엄 패브릭ㅣ루소_아이린</t>
+  </si>
+  <si>
+    <t>ACSB3891V2</t>
+  </si>
+  <si>
+    <t>홀리데이 라지 쿠션_프리미엄 패브릭ㅣ스칼렛_마리골</t>
+  </si>
+  <si>
+    <t>홀리데이 라지 쿠션_프리미엄 패브릭ㅣ스칼렛_쉘</t>
+  </si>
+  <si>
+    <t>홀리데이 라지 쿠션_프리미엄 패브릭ㅣ스칼렛_클레이</t>
+  </si>
+  <si>
+    <t>ACSB3891T</t>
+  </si>
+  <si>
+    <t>홀리데이 라지 쿠션_프리미엄 패브릭ㅣ아크레_블루 베</t>
+  </si>
+  <si>
+    <t>홀리데이 라지 쿠션_프리미엄 패브릭ㅣ아크레_샤모아</t>
+  </si>
+  <si>
+    <t>ACSB3892X1</t>
+  </si>
+  <si>
+    <t>홀리데이 럼버 쿠션_에센셜 패브릭ㅣ노르딕_멜로우 크</t>
+  </si>
+  <si>
+    <t>홀리데이 럼버 쿠션_에센셜 패브릭ㅣ노르딕_핑크 블리</t>
+  </si>
+  <si>
+    <t>ACSB3892X2</t>
+  </si>
+  <si>
+    <t>홀리데이 럼버 쿠션_에센셜 패브릭ㅣ솔라_그레이 아울</t>
+  </si>
+  <si>
+    <t>홀리데이 럼버 쿠션_에센셜 패브릭ㅣ솔라_웜 브리즈</t>
+  </si>
+  <si>
+    <t>ACSB3892R</t>
+  </si>
+  <si>
+    <t>홀리데이 럼버 쿠션_프리미엄 패브릭ㅣ루소_뮤티드 핑</t>
+  </si>
+  <si>
+    <t>홀리데이 럼버 쿠션_프리미엄 패브릭ㅣ루소_아이린</t>
+  </si>
+  <si>
+    <t>ACSB3892V2</t>
+  </si>
+  <si>
+    <t>홀리데이 럼버 쿠션_프리미엄 패브릭ㅣ스칼렛_마리골</t>
+  </si>
+  <si>
+    <t>홀리데이 럼버 쿠션_프리미엄 패브릭ㅣ스칼렛_쉘</t>
+  </si>
+  <si>
+    <t>홀리데이 럼버 쿠션_프리미엄 패브릭ㅣ스칼렛_클레이</t>
+  </si>
+  <si>
+    <t>ACSB3892T</t>
+  </si>
+  <si>
+    <t>홀리데이 럼버 쿠션_프리미엄 패브릭ㅣ아크레_블루 베</t>
+  </si>
+  <si>
+    <t>홀리데이 럼버 쿠션_프리미엄 패브릭ㅣ아크레_샤모아</t>
+  </si>
+  <si>
+    <t>WDWW165987-R000</t>
+  </si>
+  <si>
+    <t>홀리데이 미니 2인 (우) 커버+내장재 ASSY</t>
+  </si>
+  <si>
+    <t>WDWW165988-R000</t>
+  </si>
+  <si>
+    <t>홀리데이 미니 터미널 (좌) 커버+내장재 ASSY</t>
   </si>
 </sst>
 </file>
@@ -3229,16 +5413,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4357,7 +6531,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N155"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -10222,4 +12396,3523 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B438"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>372</v>
+      </c>
+      <c r="B4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B5" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>376</v>
+      </c>
+      <c r="B6" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>378</v>
+      </c>
+      <c r="B7" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>380</v>
+      </c>
+      <c r="B8" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>382</v>
+      </c>
+      <c r="B9" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>384</v>
+      </c>
+      <c r="B10" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>386</v>
+      </c>
+      <c r="B11" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>388</v>
+      </c>
+      <c r="B12" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>390</v>
+      </c>
+      <c r="B13" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>392</v>
+      </c>
+      <c r="B14" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>394</v>
+      </c>
+      <c r="B15" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>396</v>
+      </c>
+      <c r="B16" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>398</v>
+      </c>
+      <c r="B17" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>400</v>
+      </c>
+      <c r="B18" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>402</v>
+      </c>
+      <c r="B19" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>404</v>
+      </c>
+      <c r="B20" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>406</v>
+      </c>
+      <c r="B21" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>408</v>
+      </c>
+      <c r="B22" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>410</v>
+      </c>
+      <c r="B23" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>412</v>
+      </c>
+      <c r="B24" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>414</v>
+      </c>
+      <c r="B25" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>416</v>
+      </c>
+      <c r="B26" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>418</v>
+      </c>
+      <c r="B27" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>420</v>
+      </c>
+      <c r="B28" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>422</v>
+      </c>
+      <c r="B29" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>424</v>
+      </c>
+      <c r="B30" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>426</v>
+      </c>
+      <c r="B31" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>428</v>
+      </c>
+      <c r="B32" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>430</v>
+      </c>
+      <c r="B33" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>432</v>
+      </c>
+      <c r="B34" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>434</v>
+      </c>
+      <c r="B35" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>436</v>
+      </c>
+      <c r="B36" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>438</v>
+      </c>
+      <c r="B37" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>440</v>
+      </c>
+      <c r="B38" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>442</v>
+      </c>
+      <c r="B39" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>444</v>
+      </c>
+      <c r="B40" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>446</v>
+      </c>
+      <c r="B41" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>448</v>
+      </c>
+      <c r="B42" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>450</v>
+      </c>
+      <c r="B43" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>452</v>
+      </c>
+      <c r="B44" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>454</v>
+      </c>
+      <c r="B45" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>456</v>
+      </c>
+      <c r="B46" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>458</v>
+      </c>
+      <c r="B47" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>460</v>
+      </c>
+      <c r="B48" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>461</v>
+      </c>
+      <c r="B49" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>463</v>
+      </c>
+      <c r="B50" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>465</v>
+      </c>
+      <c r="B51" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>467</v>
+      </c>
+      <c r="B52" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>469</v>
+      </c>
+      <c r="B53" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>471</v>
+      </c>
+      <c r="B54" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>473</v>
+      </c>
+      <c r="B55" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>475</v>
+      </c>
+      <c r="B56" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>477</v>
+      </c>
+      <c r="B57" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>479</v>
+      </c>
+      <c r="B58" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>481</v>
+      </c>
+      <c r="B59" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>483</v>
+      </c>
+      <c r="B60" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>485</v>
+      </c>
+      <c r="B61" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>487</v>
+      </c>
+      <c r="B62" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>488</v>
+      </c>
+      <c r="B63" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>490</v>
+      </c>
+      <c r="B64" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>491</v>
+      </c>
+      <c r="B65" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>493</v>
+      </c>
+      <c r="B66" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>494</v>
+      </c>
+      <c r="B67" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>496</v>
+      </c>
+      <c r="B68" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>497</v>
+      </c>
+      <c r="B69" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>499</v>
+      </c>
+      <c r="B70" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>501</v>
+      </c>
+      <c r="B71" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>503</v>
+      </c>
+      <c r="B72" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>505</v>
+      </c>
+      <c r="B73" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>507</v>
+      </c>
+      <c r="B74" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>509</v>
+      </c>
+      <c r="B75" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>511</v>
+      </c>
+      <c r="B76" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>512</v>
+      </c>
+      <c r="B77" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>514</v>
+      </c>
+      <c r="B78" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>516</v>
+      </c>
+      <c r="B79" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>517</v>
+      </c>
+      <c r="B80" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>519</v>
+      </c>
+      <c r="B81" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>521</v>
+      </c>
+      <c r="B82" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>522</v>
+      </c>
+      <c r="B83" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>524</v>
+      </c>
+      <c r="B84" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>525</v>
+      </c>
+      <c r="B85" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>527</v>
+      </c>
+      <c r="B86" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>528</v>
+      </c>
+      <c r="B87" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>529</v>
+      </c>
+      <c r="B88" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>531</v>
+      </c>
+      <c r="B89" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>533</v>
+      </c>
+      <c r="B90" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>534</v>
+      </c>
+      <c r="B91" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>536</v>
+      </c>
+      <c r="B92" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>538</v>
+      </c>
+      <c r="B93" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>539</v>
+      </c>
+      <c r="B94" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>540</v>
+      </c>
+      <c r="B95" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>542</v>
+      </c>
+      <c r="B96" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>544</v>
+      </c>
+      <c r="B97" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>546</v>
+      </c>
+      <c r="B98" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>548</v>
+      </c>
+      <c r="B99" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>550</v>
+      </c>
+      <c r="B100" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>552</v>
+      </c>
+      <c r="B101" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>554</v>
+      </c>
+      <c r="B102" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>556</v>
+      </c>
+      <c r="B103" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>558</v>
+      </c>
+      <c r="B104" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>560</v>
+      </c>
+      <c r="B105" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>562</v>
+      </c>
+      <c r="B106" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>564</v>
+      </c>
+      <c r="B107" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>566</v>
+      </c>
+      <c r="B108" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>567</v>
+      </c>
+      <c r="B109" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>569</v>
+      </c>
+      <c r="B110" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>571</v>
+      </c>
+      <c r="B111" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>573</v>
+      </c>
+      <c r="B112" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>575</v>
+      </c>
+      <c r="B113" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>577</v>
+      </c>
+      <c r="B114" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>579</v>
+      </c>
+      <c r="B115" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>581</v>
+      </c>
+      <c r="B116" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>583</v>
+      </c>
+      <c r="B117" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>585</v>
+      </c>
+      <c r="B118" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>587</v>
+      </c>
+      <c r="B119" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>589</v>
+      </c>
+      <c r="B120" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>591</v>
+      </c>
+      <c r="B121" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>593</v>
+      </c>
+      <c r="B122" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>595</v>
+      </c>
+      <c r="B123" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>597</v>
+      </c>
+      <c r="B124" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>599</v>
+      </c>
+      <c r="B125" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>601</v>
+      </c>
+      <c r="B126" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>603</v>
+      </c>
+      <c r="B127" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>604</v>
+      </c>
+      <c r="B128" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>606</v>
+      </c>
+      <c r="B129" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>607</v>
+      </c>
+      <c r="B130" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>609</v>
+      </c>
+      <c r="B131" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>611</v>
+      </c>
+      <c r="B132" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>613</v>
+      </c>
+      <c r="B133" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>615</v>
+      </c>
+      <c r="B134" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>617</v>
+      </c>
+      <c r="B135" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>617</v>
+      </c>
+      <c r="B136" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>620</v>
+      </c>
+      <c r="B137" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>622</v>
+      </c>
+      <c r="B138" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>624</v>
+      </c>
+      <c r="B139" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>624</v>
+      </c>
+      <c r="B140" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>627</v>
+      </c>
+      <c r="B141" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>629</v>
+      </c>
+      <c r="B142" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>629</v>
+      </c>
+      <c r="B143" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>632</v>
+      </c>
+      <c r="B144" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>634</v>
+      </c>
+      <c r="B145" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>636</v>
+      </c>
+      <c r="B146" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>638</v>
+      </c>
+      <c r="B147" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>640</v>
+      </c>
+      <c r="B148" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>642</v>
+      </c>
+      <c r="B149" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>644</v>
+      </c>
+      <c r="B150" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>646</v>
+      </c>
+      <c r="B151" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>646</v>
+      </c>
+      <c r="B152" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>649</v>
+      </c>
+      <c r="B153" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>651</v>
+      </c>
+      <c r="B154" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>652</v>
+      </c>
+      <c r="B155" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>654</v>
+      </c>
+      <c r="B156" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>654</v>
+      </c>
+      <c r="B157" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>654</v>
+      </c>
+      <c r="B158" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>654</v>
+      </c>
+      <c r="B159" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>654</v>
+      </c>
+      <c r="B160" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>660</v>
+      </c>
+      <c r="B161" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>660</v>
+      </c>
+      <c r="B162" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>663</v>
+      </c>
+      <c r="B163" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>663</v>
+      </c>
+      <c r="B164" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>663</v>
+      </c>
+      <c r="B165" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>667</v>
+      </c>
+      <c r="B166" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>667</v>
+      </c>
+      <c r="B167" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>667</v>
+      </c>
+      <c r="B168" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>671</v>
+      </c>
+      <c r="B169" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>671</v>
+      </c>
+      <c r="B170" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>671</v>
+      </c>
+      <c r="B171" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>675</v>
+      </c>
+      <c r="B172" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>677</v>
+      </c>
+      <c r="B173" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>677</v>
+      </c>
+      <c r="B174" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>677</v>
+      </c>
+      <c r="B175" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>677</v>
+      </c>
+      <c r="B176" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>677</v>
+      </c>
+      <c r="B177" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>677</v>
+      </c>
+      <c r="B178" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>677</v>
+      </c>
+      <c r="B179" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>677</v>
+      </c>
+      <c r="B180" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>677</v>
+      </c>
+      <c r="B181" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>687</v>
+      </c>
+      <c r="B182" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>687</v>
+      </c>
+      <c r="B183" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>687</v>
+      </c>
+      <c r="B184" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>687</v>
+      </c>
+      <c r="B185" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>687</v>
+      </c>
+      <c r="B186" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>687</v>
+      </c>
+      <c r="B187" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>694</v>
+      </c>
+      <c r="B188" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>696</v>
+      </c>
+      <c r="B189" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>696</v>
+      </c>
+      <c r="B190" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>696</v>
+      </c>
+      <c r="B191" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>700</v>
+      </c>
+      <c r="B192" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>700</v>
+      </c>
+      <c r="B193" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>700</v>
+      </c>
+      <c r="B194" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>700</v>
+      </c>
+      <c r="B195" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>705</v>
+      </c>
+      <c r="B196" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>707</v>
+      </c>
+      <c r="B197" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>709</v>
+      </c>
+      <c r="B198" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>711</v>
+      </c>
+      <c r="B199" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>713</v>
+      </c>
+      <c r="B200" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>713</v>
+      </c>
+      <c r="B201" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>713</v>
+      </c>
+      <c r="B202" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>717</v>
+      </c>
+      <c r="B203" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>717</v>
+      </c>
+      <c r="B204" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>717</v>
+      </c>
+      <c r="B205" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>717</v>
+      </c>
+      <c r="B206" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>717</v>
+      </c>
+      <c r="B207" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>723</v>
+      </c>
+      <c r="B208" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>723</v>
+      </c>
+      <c r="B209" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>726</v>
+      </c>
+      <c r="B210" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>726</v>
+      </c>
+      <c r="B211" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>726</v>
+      </c>
+      <c r="B212" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>730</v>
+      </c>
+      <c r="B213" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>730</v>
+      </c>
+      <c r="B214" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>730</v>
+      </c>
+      <c r="B215" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>734</v>
+      </c>
+      <c r="B216" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>736</v>
+      </c>
+      <c r="B217" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>736</v>
+      </c>
+      <c r="B218" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>739</v>
+      </c>
+      <c r="B219" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>741</v>
+      </c>
+      <c r="B220" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>743</v>
+      </c>
+      <c r="B221" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>743</v>
+      </c>
+      <c r="B222" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>746</v>
+      </c>
+      <c r="B223" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>748</v>
+      </c>
+      <c r="B224" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>750</v>
+      </c>
+      <c r="B225" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>752</v>
+      </c>
+      <c r="B226" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>754</v>
+      </c>
+      <c r="B227" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>756</v>
+      </c>
+      <c r="B228" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>756</v>
+      </c>
+      <c r="B229" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>759</v>
+      </c>
+      <c r="B230" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>759</v>
+      </c>
+      <c r="B231" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>759</v>
+      </c>
+      <c r="B232" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>759</v>
+      </c>
+      <c r="B233" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>759</v>
+      </c>
+      <c r="B234" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>765</v>
+      </c>
+      <c r="B235" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>767</v>
+      </c>
+      <c r="B236" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>768</v>
+      </c>
+      <c r="B237" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>770</v>
+      </c>
+      <c r="B238" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>771</v>
+      </c>
+      <c r="B239" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>342</v>
+      </c>
+      <c r="B240" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>362</v>
+      </c>
+      <c r="B241" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>774</v>
+      </c>
+      <c r="B242" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>776</v>
+      </c>
+      <c r="B243" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>777</v>
+      </c>
+      <c r="B244" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>366</v>
+      </c>
+      <c r="B245" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>364</v>
+      </c>
+      <c r="B246" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>779</v>
+      </c>
+      <c r="B247" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>781</v>
+      </c>
+      <c r="B248" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>782</v>
+      </c>
+      <c r="B249" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>784</v>
+      </c>
+      <c r="B250" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>786</v>
+      </c>
+      <c r="B251" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>788</v>
+      </c>
+      <c r="B252" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>788</v>
+      </c>
+      <c r="B253" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>791</v>
+      </c>
+      <c r="B254" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>793</v>
+      </c>
+      <c r="B255" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>794</v>
+      </c>
+      <c r="B256" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>795</v>
+      </c>
+      <c r="B257" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>797</v>
+      </c>
+      <c r="B258" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>799</v>
+      </c>
+      <c r="B259" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>801</v>
+      </c>
+      <c r="B260" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>803</v>
+      </c>
+      <c r="B261" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>805</v>
+      </c>
+      <c r="B262" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>807</v>
+      </c>
+      <c r="B263" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>809</v>
+      </c>
+      <c r="B264" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>811</v>
+      </c>
+      <c r="B265" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>813</v>
+      </c>
+      <c r="B266" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>814</v>
+      </c>
+      <c r="B267" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>299</v>
+      </c>
+      <c r="B268" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>817</v>
+      </c>
+      <c r="B269" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>819</v>
+      </c>
+      <c r="B270" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>821</v>
+      </c>
+      <c r="B271" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>823</v>
+      </c>
+      <c r="B272" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>825</v>
+      </c>
+      <c r="B273" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>827</v>
+      </c>
+      <c r="B274" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>829</v>
+      </c>
+      <c r="B275" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>831</v>
+      </c>
+      <c r="B276" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>833</v>
+      </c>
+      <c r="B277" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>835</v>
+      </c>
+      <c r="B278" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>837</v>
+      </c>
+      <c r="B279" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>838</v>
+      </c>
+      <c r="B280" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>839</v>
+      </c>
+      <c r="B281" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>840</v>
+      </c>
+      <c r="B282" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>841</v>
+      </c>
+      <c r="B283" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>843</v>
+      </c>
+      <c r="B284" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>843</v>
+      </c>
+      <c r="B285" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>846</v>
+      </c>
+      <c r="B286" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>846</v>
+      </c>
+      <c r="B287" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>846</v>
+      </c>
+      <c r="B288" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>850</v>
+      </c>
+      <c r="B289" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>850</v>
+      </c>
+      <c r="B290" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>850</v>
+      </c>
+      <c r="B291" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>854</v>
+      </c>
+      <c r="B292" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>854</v>
+      </c>
+      <c r="B293" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>857</v>
+      </c>
+      <c r="B294" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>857</v>
+      </c>
+      <c r="B295" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>857</v>
+      </c>
+      <c r="B296" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>861</v>
+      </c>
+      <c r="B297" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>861</v>
+      </c>
+      <c r="B298" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>861</v>
+      </c>
+      <c r="B299" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>861</v>
+      </c>
+      <c r="B300" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>861</v>
+      </c>
+      <c r="B301" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>867</v>
+      </c>
+      <c r="B302" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A303" t="s">
+        <v>869</v>
+      </c>
+      <c r="B303" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>871</v>
+      </c>
+      <c r="B304" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>873</v>
+      </c>
+      <c r="B305" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>875</v>
+      </c>
+      <c r="B306" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>877</v>
+      </c>
+      <c r="B307" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>879</v>
+      </c>
+      <c r="B308" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>880</v>
+      </c>
+      <c r="B309" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>881</v>
+      </c>
+      <c r="B310" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>883</v>
+      </c>
+      <c r="B311" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>885</v>
+      </c>
+      <c r="B312" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>887</v>
+      </c>
+      <c r="B313" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>889</v>
+      </c>
+      <c r="B314" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>891</v>
+      </c>
+      <c r="B315" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>893</v>
+      </c>
+      <c r="B316" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
+        <v>895</v>
+      </c>
+      <c r="B317" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A318" t="s">
+        <v>897</v>
+      </c>
+      <c r="B318" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A319" t="s">
+        <v>899</v>
+      </c>
+      <c r="B319" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>901</v>
+      </c>
+      <c r="B320" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>903</v>
+      </c>
+      <c r="B321" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A322" t="s">
+        <v>905</v>
+      </c>
+      <c r="B322" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A323" t="s">
+        <v>907</v>
+      </c>
+      <c r="B323" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A324" t="s">
+        <v>909</v>
+      </c>
+      <c r="B324" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A325" t="s">
+        <v>911</v>
+      </c>
+      <c r="B325" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A326" t="s">
+        <v>913</v>
+      </c>
+      <c r="B326" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A327" t="s">
+        <v>915</v>
+      </c>
+      <c r="B327" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A328" t="s">
+        <v>917</v>
+      </c>
+      <c r="B328" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A329" t="s">
+        <v>919</v>
+      </c>
+      <c r="B329" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A330" t="s">
+        <v>921</v>
+      </c>
+      <c r="B330" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A331" t="s">
+        <v>923</v>
+      </c>
+      <c r="B331" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A332" t="s">
+        <v>925</v>
+      </c>
+      <c r="B332" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A333" t="s">
+        <v>927</v>
+      </c>
+      <c r="B333" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A334" t="s">
+        <v>927</v>
+      </c>
+      <c r="B334" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A335" t="s">
+        <v>930</v>
+      </c>
+      <c r="B335" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A336" t="s">
+        <v>932</v>
+      </c>
+      <c r="B336" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A337" t="s">
+        <v>934</v>
+      </c>
+      <c r="B337" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A338" t="s">
+        <v>934</v>
+      </c>
+      <c r="B338" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A339" t="s">
+        <v>934</v>
+      </c>
+      <c r="B339" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A340" t="s">
+        <v>938</v>
+      </c>
+      <c r="B340" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A341" t="s">
+        <v>938</v>
+      </c>
+      <c r="B341" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A342" t="s">
+        <v>941</v>
+      </c>
+      <c r="B342" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A343" t="s">
+        <v>943</v>
+      </c>
+      <c r="B343" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A344" t="s">
+        <v>945</v>
+      </c>
+      <c r="B344" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A345" t="s">
+        <v>947</v>
+      </c>
+      <c r="B345" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A346" t="s">
+        <v>947</v>
+      </c>
+      <c r="B346" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A347" t="s">
+        <v>947</v>
+      </c>
+      <c r="B347" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A348" t="s">
+        <v>951</v>
+      </c>
+      <c r="B348" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A349" t="s">
+        <v>951</v>
+      </c>
+      <c r="B349" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A350" t="s">
+        <v>951</v>
+      </c>
+      <c r="B350" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A351" t="s">
+        <v>955</v>
+      </c>
+      <c r="B351" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A352" t="s">
+        <v>955</v>
+      </c>
+      <c r="B352" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A353" t="s">
+        <v>958</v>
+      </c>
+      <c r="B353" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A354" t="s">
+        <v>960</v>
+      </c>
+      <c r="B354" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A355" t="s">
+        <v>962</v>
+      </c>
+      <c r="B355" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A356" t="s">
+        <v>962</v>
+      </c>
+      <c r="B356" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A357" t="s">
+        <v>965</v>
+      </c>
+      <c r="B357" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A358" t="s">
+        <v>965</v>
+      </c>
+      <c r="B358" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A359" t="s">
+        <v>968</v>
+      </c>
+      <c r="B359" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A360" t="s">
+        <v>968</v>
+      </c>
+      <c r="B360" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A361" t="s">
+        <v>971</v>
+      </c>
+      <c r="B361" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A362" t="s">
+        <v>971</v>
+      </c>
+      <c r="B362" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A363" t="s">
+        <v>974</v>
+      </c>
+      <c r="B363" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A364" t="s">
+        <v>976</v>
+      </c>
+      <c r="B364" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A365" t="s">
+        <v>976</v>
+      </c>
+      <c r="B365" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A366" t="s">
+        <v>979</v>
+      </c>
+      <c r="B366" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A367" t="s">
+        <v>979</v>
+      </c>
+      <c r="B367" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A368" t="s">
+        <v>982</v>
+      </c>
+      <c r="B368" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A369" t="s">
+        <v>982</v>
+      </c>
+      <c r="B369" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A370" t="s">
+        <v>985</v>
+      </c>
+      <c r="B370" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A371" t="s">
+        <v>987</v>
+      </c>
+      <c r="B371" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A372" t="s">
+        <v>989</v>
+      </c>
+      <c r="B372" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A373" t="s">
+        <v>989</v>
+      </c>
+      <c r="B373" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A374" t="s">
+        <v>992</v>
+      </c>
+      <c r="B374" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A375" t="s">
+        <v>992</v>
+      </c>
+      <c r="B375" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A376" t="s">
+        <v>992</v>
+      </c>
+      <c r="B376" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A377" t="s">
+        <v>992</v>
+      </c>
+      <c r="B377" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A378" t="s">
+        <v>997</v>
+      </c>
+      <c r="B378" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A379" t="s">
+        <v>997</v>
+      </c>
+      <c r="B379" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A380" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B380" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A381" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B381" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A382" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B382" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A383" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B383" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A384" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B384" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A385" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B385" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A386" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B386" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A387" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B387" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A388" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B388" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A389" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B389" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A390" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B390" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A391" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B391" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A392" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B392" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A393" t="s">
+        <v>339</v>
+      </c>
+      <c r="B393" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A394" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B394" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A395" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B395" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A396" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B396" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A397" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B397" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A398" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B398" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A399" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B399" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A400" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B400" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A401" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B401" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A402" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B402" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A403" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B403" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A404" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B404" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A405" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B405" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A406" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B406" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A407" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B407" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A408" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B408" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A409" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B409" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A410" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B410" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A411" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B411" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A412" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B412" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A413" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B413" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A414" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B414" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A415" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B415" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A416" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B416" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A417" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B417" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A418" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B418" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A419" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B419" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A420" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B420" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A421" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B421" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A422" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B422" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A423" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B423" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A424" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B424" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A425" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B425" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A426" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B426" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A427" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B427" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A428" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B428" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A429" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B429" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A430" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B430" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A431" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B431" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A432" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B432" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A433" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B433" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A434" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B434" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A435" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B435" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A436" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B436" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A437" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B437" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A438" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B438" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/품목마스터/마감작업자별 생산가능품목_코드목록_v2.xlsx
+++ b/품목마스터/마감작업자별 생산가능품목_코드목록_v2.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16440" windowHeight="8655" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16440" windowHeight="8655" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,13 +17,14 @@
     <sheet name="품목군별코드" sheetId="4" r:id="rId3"/>
     <sheet name="품목군코드상세" sheetId="5" r:id="rId4"/>
     <sheet name="특정라인 지정" sheetId="6" r:id="rId5"/>
+    <sheet name="셋트구분" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2770" uniqueCount="1095">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2837" uniqueCount="1108">
   <si>
     <t>마감작업자 생산가능품목</t>
   </si>
@@ -3308,6 +3309,49 @@
   </si>
   <si>
     <t>홀리데이 미니 터미널 (좌) 커버+내장재 ASSY</t>
+  </si>
+  <si>
+    <t>L849L</t>
+  </si>
+  <si>
+    <t>HCS8812R</t>
+  </si>
+  <si>
+    <t>HCS8812L</t>
+  </si>
+  <si>
+    <t>L846</t>
+  </si>
+  <si>
+    <t>L841L</t>
+  </si>
+  <si>
+    <t>L845</t>
+  </si>
+  <si>
+    <t>밴쿠버 3인 몸통(가죽)</t>
+  </si>
+  <si>
+    <t>HCS8813L</t>
+  </si>
+  <si>
+    <t>HCS8811R</t>
+  </si>
+  <si>
+    <t>품목명칭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>색상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>품목코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>셋트 구분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3435,7 +3479,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3469,6 +3513,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -15915,4 +15962,330 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="13"/>
+    <col min="2" max="2" width="18.125" style="13" customWidth="1"/>
+    <col min="3" max="3" width="12" style="13" customWidth="1"/>
+    <col min="4" max="4" width="25.375" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="13">
+        <v>1</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="13">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="13">
+        <v>2</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="13">
+        <v>2</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
+        <v>3</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
+        <v>3</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
+        <v>4</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
+        <v>5</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
+        <v>6</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
+        <v>7</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
+        <v>8</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="13">
+        <v>9</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="13">
+        <v>10</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="13">
+        <v>11</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="13">
+        <v>12</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="13">
+        <v>12</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
+        <v>13</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
+        <v>13</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="13">
+        <v>14</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="13">
+        <v>14</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>357</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/품목마스터/마감작업자별 생산가능품목_코드목록_v2.xlsx
+++ b/품목마스터/마감작업자별 생산가능품목_코드목록_v2.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16440" windowHeight="8655" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16440" windowHeight="8655" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,16 @@
     <sheet name="특정라인 지정" sheetId="6" r:id="rId5"/>
     <sheet name="셋트구분" sheetId="7" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'특정라인 지정'!$A$1:$B$438</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">품목군코드상세!$A$1:$N$127</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2837" uniqueCount="1108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2564" uniqueCount="1068">
   <si>
     <t>마감작업자 생산가능품목</t>
   </si>
@@ -389,36 +393,6 @@
     <t>ACSB2324</t>
   </si>
   <si>
-    <t>ACSB2390</t>
-  </si>
-  <si>
-    <t>케렌시아 사이드 쿠션</t>
-  </si>
-  <si>
-    <t>ACSB2391</t>
-  </si>
-  <si>
-    <t>케렌시아 럼버 쿠션</t>
-  </si>
-  <si>
-    <t>ACSB2394</t>
-  </si>
-  <si>
-    <t>케렌시아 페이브 쿠션</t>
-  </si>
-  <si>
-    <t>ACSB2398</t>
-  </si>
-  <si>
-    <t>케렌시아 다리 11cm</t>
-  </si>
-  <si>
-    <t>ACSB2399</t>
-  </si>
-  <si>
-    <t>케렌시아 다리 15cm (비규격)</t>
-  </si>
-  <si>
     <t>ACSB23</t>
   </si>
   <si>
@@ -515,24 +489,6 @@
     <t>밀로 2인 (우)</t>
   </si>
   <si>
-    <t>ACSB3091</t>
-  </si>
-  <si>
-    <t>밀로 라지 쿠션</t>
-  </si>
-  <si>
-    <t>ACSB3092</t>
-  </si>
-  <si>
-    <t>밀로 럼버 쿠션</t>
-  </si>
-  <si>
-    <t>ACSB3093</t>
-  </si>
-  <si>
-    <t>밀로 사이드 쿠션</t>
-  </si>
-  <si>
     <t>ACSB2403</t>
   </si>
   <si>
@@ -653,12 +609,6 @@
     <t>클렉트 2인 (우)</t>
   </si>
   <si>
-    <t>ACSB3691</t>
-  </si>
-  <si>
-    <t>클렉트 하이백 쿠션</t>
-  </si>
-  <si>
     <t>ACSB3400</t>
   </si>
   <si>
@@ -719,30 +669,6 @@
     <t>테오 1인 라운지 (우)</t>
   </si>
   <si>
-    <t>ACSB3491</t>
-  </si>
-  <si>
-    <t>테오 라지 쿠션</t>
-  </si>
-  <si>
-    <t>ACSB3492</t>
-  </si>
-  <si>
-    <t>테오 럼버 쿠션</t>
-  </si>
-  <si>
-    <t>ACSB3494</t>
-  </si>
-  <si>
-    <t>테오 플랫 쿠션</t>
-  </si>
-  <si>
-    <t>ACSB2291</t>
-  </si>
-  <si>
-    <t>홀리데이 라지 쿠션</t>
-  </si>
-  <si>
     <t>ACSB3804</t>
   </si>
   <si>
@@ -785,15 +711,6 @@
     <t>홀리데이 터미널 (우)</t>
   </si>
   <si>
-    <t>ACSB3891</t>
-  </si>
-  <si>
-    <t>ACSB3892</t>
-  </si>
-  <si>
-    <t>홀리데이 럼버 쿠션</t>
-  </si>
-  <si>
     <t>ACSP2205</t>
   </si>
   <si>
@@ -869,18 +786,6 @@
     <t>바드 데이베드 (우)</t>
   </si>
   <si>
-    <t>ACSB3794</t>
-  </si>
-  <si>
-    <t>바드 플랫 쿠션</t>
-  </si>
-  <si>
-    <t>ISC00</t>
-  </si>
-  <si>
-    <t>오브 헤드레스트(패브릭) / 오브 플레인 헤드레스트(패브릭) / 오브 헤드레스트(부클)</t>
-  </si>
-  <si>
     <t>ISL15</t>
   </si>
   <si>
@@ -953,21 +858,6 @@
     <t>디딤 1인 코너</t>
   </si>
   <si>
-    <t>ACSB4591</t>
-  </si>
-  <si>
-    <t>디딤 라지 쿠션</t>
-  </si>
-  <si>
-    <t>ACSB4594</t>
-  </si>
-  <si>
-    <t>디딤 서포트 쿠션</t>
-  </si>
-  <si>
-    <t>ACSB45</t>
-  </si>
-  <si>
     <t>디딤 커넥터</t>
   </si>
   <si>
@@ -1013,15 +903,6 @@
     <t>뚜따 하이백 / 뚜따 하이백 1인</t>
   </si>
   <si>
-    <t>DXXZ001012</t>
-  </si>
-  <si>
-    <t>데스커 비규격</t>
-  </si>
-  <si>
-    <t>플로코 2-WAY 등받이 쿠션 / 플로코 2-WAY 등받이 쿠션 커버</t>
-  </si>
-  <si>
     <t>ISC07</t>
   </si>
   <si>
@@ -1049,15 +930,9 @@
     <t>플로코 2-WAY 등받이 쿠션(프로모션용)</t>
   </si>
   <si>
-    <t>(5월 데이터 없음)</t>
-  </si>
-  <si>
     <t>HCS8800</t>
   </si>
   <si>
-    <t>밴쿠버 스툴(가죽) / 밴쿠버 스툴(패브릭) / 밴쿠버 헤드레스트(가죽) / 밴쿠버 헤드레스트(패브릭) / 밴쿠버 스툴 철제다리</t>
-  </si>
-  <si>
     <t>HCS8811</t>
   </si>
   <si>
@@ -1073,16 +948,7 @@
     <t>HCS8813</t>
   </si>
   <si>
-    <t>밴쿠버 3인 몸통(가죽) / 밴쿠버 3인 몸통(패브릭) / 밴쿠버 3인 좌 몸통(가죽) / 밴쿠버 3인 좌 몸통(패브릭) / 밴쿠버 3인 철제다리</t>
-  </si>
-  <si>
-    <t>HCS8814</t>
-  </si>
-  <si>
     <t>밴쿠버 4인 철제다리</t>
-  </si>
-  <si>
-    <t>HCS8818</t>
   </si>
   <si>
     <t>밴쿠버 3.5인 철제다리</t>
@@ -3351,6 +3217,30 @@
   </si>
   <si>
     <t>셋트 구분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밴쿠버 스툴(가죽)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밴쿠버 3인 몸통(가죽)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CS62</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CS64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코티</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폴디</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6580,14 +6470,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N155"/>
+  <dimension ref="A1:N127"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" style="8" customWidth="1"/>
     <col min="2" max="2" width="5" style="8" customWidth="1"/>
     <col min="3" max="3" width="16" style="8" customWidth="1"/>
     <col min="4" max="4" width="14" style="8" customWidth="1"/>
-    <col min="5" max="5" width="42" style="8" customWidth="1"/>
+    <col min="5" max="5" width="87.75" style="8" customWidth="1"/>
     <col min="6" max="12" width="8" style="8" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7632,10 +7522,10 @@
         <v>41</v>
       </c>
       <c r="B27" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>123</v>
@@ -7643,24 +7533,18 @@
       <c r="E27" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="F27" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="F27" s="12"/>
       <c r="G27" s="11" t="s">
         <v>48</v>
       </c>
       <c r="H27" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I27" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="I27" s="12"/>
       <c r="J27" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="K27" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="K27" s="11"/>
       <c r="L27" s="11" t="s">
         <v>48</v>
       </c>
@@ -7674,10 +7558,10 @@
         <v>41</v>
       </c>
       <c r="B28" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>125</v>
@@ -7685,24 +7569,18 @@
       <c r="E28" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="F28" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="F28" s="12"/>
       <c r="G28" s="11" t="s">
         <v>48</v>
       </c>
       <c r="H28" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I28" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="I28" s="12"/>
       <c r="J28" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="K28" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="K28" s="11"/>
       <c r="L28" s="11" t="s">
         <v>48</v>
       </c>
@@ -7716,10 +7594,10 @@
         <v>41</v>
       </c>
       <c r="B29" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>127</v>
@@ -7727,27 +7605,17 @@
       <c r="E29" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="F29" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="F29" s="12"/>
       <c r="G29" s="11" t="s">
         <v>48</v>
       </c>
       <c r="H29" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I29" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J29" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K29" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L29" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
       <c r="M29" s="11" t="s">
         <v>48</v>
       </c>
@@ -7758,10 +7626,10 @@
         <v>41</v>
       </c>
       <c r="B30" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>129</v>
@@ -7769,27 +7637,17 @@
       <c r="E30" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="F30" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="F30" s="12"/>
       <c r="G30" s="11" t="s">
         <v>48</v>
       </c>
       <c r="H30" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I30" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J30" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K30" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L30" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
       <c r="M30" s="11" t="s">
         <v>48</v>
       </c>
@@ -7800,10 +7658,10 @@
         <v>41</v>
       </c>
       <c r="B31" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>131</v>
@@ -7811,27 +7669,17 @@
       <c r="E31" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="F31" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="F31" s="12"/>
       <c r="G31" s="11" t="s">
         <v>48</v>
       </c>
       <c r="H31" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I31" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J31" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K31" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L31" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
       <c r="M31" s="11" t="s">
         <v>48</v>
       </c>
@@ -7842,10 +7690,10 @@
         <v>41</v>
       </c>
       <c r="B32" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>133</v>
@@ -7861,13 +7709,9 @@
         <v>48</v>
       </c>
       <c r="I32" s="12"/>
-      <c r="J32" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
       <c r="M32" s="11" t="s">
         <v>48</v>
       </c>
@@ -7878,10 +7722,10 @@
         <v>41</v>
       </c>
       <c r="B33" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>135</v>
@@ -7897,13 +7741,9 @@
         <v>48</v>
       </c>
       <c r="I33" s="12"/>
-      <c r="J33" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
       <c r="M33" s="11" t="s">
         <v>48</v>
       </c>
@@ -7914,10 +7754,10 @@
         <v>41</v>
       </c>
       <c r="B34" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>137</v>
@@ -7926,19 +7766,19 @@
         <v>138</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H34" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
       <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="J34" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="M34" s="12"/>
       <c r="N34" s="12"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
@@ -7946,10 +7786,10 @@
         <v>41</v>
       </c>
       <c r="B35" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>139</v>
@@ -7958,19 +7798,19 @@
         <v>140</v>
       </c>
       <c r="F35" s="12"/>
-      <c r="G35" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H35" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
       <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="J35" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="M35" s="12"/>
       <c r="N35" s="12"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
@@ -7978,10 +7818,10 @@
         <v>41</v>
       </c>
       <c r="B36" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>141</v>
@@ -7990,19 +7830,19 @@
         <v>142</v>
       </c>
       <c r="F36" s="12"/>
-      <c r="G36" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H36" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
       <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
-      <c r="M36" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="J36" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="M36" s="12"/>
       <c r="N36" s="12"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
@@ -8010,10 +7850,10 @@
         <v>41</v>
       </c>
       <c r="B37" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>143</v>
@@ -8022,19 +7862,15 @@
         <v>144</v>
       </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H37" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
       <c r="I37" s="12"/>
       <c r="J37" s="12"/>
       <c r="K37" s="12"/>
-      <c r="L37" s="12"/>
-      <c r="M37" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="L37" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="M37" s="12"/>
       <c r="N37" s="12"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
@@ -8042,10 +7878,10 @@
         <v>41</v>
       </c>
       <c r="B38" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>145</v>
@@ -8054,19 +7890,15 @@
         <v>146</v>
       </c>
       <c r="F38" s="12"/>
-      <c r="G38" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H38" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
       <c r="I38" s="12"/>
       <c r="J38" s="12"/>
       <c r="K38" s="12"/>
-      <c r="L38" s="12"/>
-      <c r="M38" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="L38" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="M38" s="12"/>
       <c r="N38" s="12"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
@@ -8074,10 +7906,10 @@
         <v>41</v>
       </c>
       <c r="B39" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>147</v>
@@ -8089,12 +7921,8 @@
       <c r="G39" s="12"/>
       <c r="H39" s="12"/>
       <c r="I39" s="12"/>
-      <c r="J39" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K39" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="J39" s="12"/>
+      <c r="K39" s="12"/>
       <c r="L39" s="11" t="s">
         <v>48</v>
       </c>
@@ -8106,10 +7934,10 @@
         <v>41</v>
       </c>
       <c r="B40" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>149</v>
@@ -8121,12 +7949,8 @@
       <c r="G40" s="12"/>
       <c r="H40" s="12"/>
       <c r="I40" s="12"/>
-      <c r="J40" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K40" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
       <c r="L40" s="11" t="s">
         <v>48</v>
       </c>
@@ -8138,10 +7962,10 @@
         <v>41</v>
       </c>
       <c r="B41" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>151</v>
@@ -8153,12 +7977,8 @@
       <c r="G41" s="12"/>
       <c r="H41" s="12"/>
       <c r="I41" s="12"/>
-      <c r="J41" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K41" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="J41" s="12"/>
+      <c r="K41" s="12"/>
       <c r="L41" s="11" t="s">
         <v>48</v>
       </c>
@@ -8170,10 +7990,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>153</v>
@@ -8181,16 +8001,26 @@
       <c r="E42" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
+      <c r="F42" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="I42" s="12"/>
       <c r="J42" s="12"/>
-      <c r="K42" s="12"/>
+      <c r="K42" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="L42" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M42" s="12"/>
+      <c r="M42" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="N42" s="12"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
@@ -8198,10 +8028,10 @@
         <v>41</v>
       </c>
       <c r="B43" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D43" s="10" t="s">
         <v>155</v>
@@ -8209,16 +8039,26 @@
       <c r="E43" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
+      <c r="F43" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="I43" s="12"/>
       <c r="J43" s="12"/>
-      <c r="K43" s="12"/>
+      <c r="K43" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="L43" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M43" s="12"/>
+      <c r="M43" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="N43" s="12"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
@@ -8226,10 +8066,10 @@
         <v>41</v>
       </c>
       <c r="B44" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>157</v>
@@ -8237,16 +8077,26 @@
       <c r="E44" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
+      <c r="F44" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="I44" s="12"/>
       <c r="J44" s="12"/>
-      <c r="K44" s="12"/>
+      <c r="K44" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="L44" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M44" s="12"/>
+      <c r="M44" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="N44" s="12"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
@@ -8254,10 +8104,10 @@
         <v>41</v>
       </c>
       <c r="B45" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>159</v>
@@ -8265,16 +8115,26 @@
       <c r="E45" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
+      <c r="F45" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="I45" s="12"/>
       <c r="J45" s="12"/>
-      <c r="K45" s="12"/>
+      <c r="K45" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="L45" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M45" s="12"/>
+      <c r="M45" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="N45" s="12"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
@@ -8282,10 +8142,10 @@
         <v>41</v>
       </c>
       <c r="B46" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D46" s="10" t="s">
         <v>161</v>
@@ -8293,16 +8153,26 @@
       <c r="E46" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
+      <c r="F46" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="I46" s="12"/>
       <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
+      <c r="K46" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="L46" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M46" s="12"/>
+      <c r="M46" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="N46" s="12"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
@@ -8310,10 +8180,10 @@
         <v>41</v>
       </c>
       <c r="B47" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D47" s="10" t="s">
         <v>163</v>
@@ -8321,16 +8191,26 @@
       <c r="E47" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
+      <c r="F47" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="I47" s="12"/>
       <c r="J47" s="12"/>
-      <c r="K47" s="12"/>
+      <c r="K47" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="L47" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M47" s="12"/>
+      <c r="M47" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="N47" s="12"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
@@ -8338,10 +8218,10 @@
         <v>41</v>
       </c>
       <c r="B48" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D48" s="10" t="s">
         <v>165</v>
@@ -8349,16 +8229,26 @@
       <c r="E48" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
+      <c r="F48" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="I48" s="12"/>
       <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
+      <c r="K48" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="L48" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M48" s="12"/>
+      <c r="M48" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="N48" s="12"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
@@ -8366,10 +8256,10 @@
         <v>41</v>
       </c>
       <c r="B49" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>167</v>
@@ -8377,16 +8267,26 @@
       <c r="E49" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="12"/>
+      <c r="F49" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H49" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="I49" s="12"/>
       <c r="J49" s="12"/>
-      <c r="K49" s="12"/>
+      <c r="K49" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="L49" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M49" s="12"/>
+      <c r="M49" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="N49" s="12"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
@@ -8394,10 +8294,10 @@
         <v>41</v>
       </c>
       <c r="B50" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>169</v>
@@ -8432,10 +8332,10 @@
         <v>41</v>
       </c>
       <c r="B51" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>171</v>
@@ -8470,10 +8370,10 @@
         <v>41</v>
       </c>
       <c r="B52" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>173</v>
@@ -8508,10 +8408,10 @@
         <v>41</v>
       </c>
       <c r="B53" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D53" s="10" t="s">
         <v>175</v>
@@ -8546,10 +8446,10 @@
         <v>41</v>
       </c>
       <c r="B54" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>177</v>
@@ -8557,9 +8457,7 @@
       <c r="E54" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="F54" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="F54" s="12"/>
       <c r="G54" s="11" t="s">
         <v>48</v>
       </c>
@@ -8584,10 +8482,10 @@
         <v>41</v>
       </c>
       <c r="B55" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>179</v>
@@ -8595,9 +8493,7 @@
       <c r="E55" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="F55" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="F55" s="12"/>
       <c r="G55" s="11" t="s">
         <v>48</v>
       </c>
@@ -8622,10 +8518,10 @@
         <v>41</v>
       </c>
       <c r="B56" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D56" s="10" t="s">
         <v>181</v>
@@ -8633,9 +8529,7 @@
       <c r="E56" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="F56" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="F56" s="12"/>
       <c r="G56" s="11" t="s">
         <v>48</v>
       </c>
@@ -8660,10 +8554,10 @@
         <v>41</v>
       </c>
       <c r="B57" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>183</v>
@@ -8671,9 +8565,7 @@
       <c r="E57" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="F57" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="F57" s="12"/>
       <c r="G57" s="11" t="s">
         <v>48</v>
       </c>
@@ -8698,10 +8590,10 @@
         <v>41</v>
       </c>
       <c r="B58" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>185</v>
@@ -8709,9 +8601,7 @@
       <c r="E58" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="F58" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="F58" s="12"/>
       <c r="G58" s="11" t="s">
         <v>48</v>
       </c>
@@ -8736,10 +8626,10 @@
         <v>41</v>
       </c>
       <c r="B59" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>187</v>
@@ -8747,9 +8637,7 @@
       <c r="E59" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="F59" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="F59" s="12"/>
       <c r="G59" s="11" t="s">
         <v>48</v>
       </c>
@@ -8774,10 +8662,10 @@
         <v>41</v>
       </c>
       <c r="B60" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>189</v>
@@ -8785,9 +8673,7 @@
       <c r="E60" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="F60" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="F60" s="12"/>
       <c r="G60" s="11" t="s">
         <v>48</v>
       </c>
@@ -8812,10 +8698,10 @@
         <v>41</v>
       </c>
       <c r="B61" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D61" s="10" t="s">
         <v>191</v>
@@ -8823,9 +8709,7 @@
       <c r="E61" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="F61" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="F61" s="12"/>
       <c r="G61" s="11" t="s">
         <v>48</v>
       </c>
@@ -8850,10 +8734,10 @@
         <v>41</v>
       </c>
       <c r="B62" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>193</v>
@@ -8862,23 +8746,15 @@
         <v>194</v>
       </c>
       <c r="F62" s="12"/>
-      <c r="G62" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H62" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
       <c r="I62" s="12"/>
       <c r="J62" s="12"/>
-      <c r="K62" s="12" t="s">
-        <v>48</v>
-      </c>
+      <c r="K62" s="12"/>
       <c r="L62" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M62" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="M62" s="12"/>
       <c r="N62" s="12"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
@@ -8886,10 +8762,10 @@
         <v>41</v>
       </c>
       <c r="B63" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>195</v>
@@ -8898,23 +8774,15 @@
         <v>196</v>
       </c>
       <c r="F63" s="12"/>
-      <c r="G63" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H63" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
       <c r="I63" s="12"/>
       <c r="J63" s="12"/>
-      <c r="K63" s="12" t="s">
-        <v>48</v>
-      </c>
+      <c r="K63" s="12"/>
       <c r="L63" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M63" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="M63" s="12"/>
       <c r="N63" s="12"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
@@ -8922,10 +8790,10 @@
         <v>41</v>
       </c>
       <c r="B64" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>197</v>
@@ -8934,23 +8802,15 @@
         <v>198</v>
       </c>
       <c r="F64" s="12"/>
-      <c r="G64" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H64" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
       <c r="I64" s="12"/>
       <c r="J64" s="12"/>
-      <c r="K64" s="12" t="s">
-        <v>48</v>
-      </c>
+      <c r="K64" s="12"/>
       <c r="L64" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M64" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="M64" s="12"/>
       <c r="N64" s="12"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
@@ -8958,10 +8818,10 @@
         <v>41</v>
       </c>
       <c r="B65" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>199</v>
@@ -8970,23 +8830,15 @@
         <v>200</v>
       </c>
       <c r="F65" s="12"/>
-      <c r="G65" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H65" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="G65" s="12"/>
+      <c r="H65" s="12"/>
       <c r="I65" s="12"/>
       <c r="J65" s="12"/>
-      <c r="K65" s="12" t="s">
-        <v>48</v>
-      </c>
+      <c r="K65" s="12"/>
       <c r="L65" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M65" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="M65" s="12"/>
       <c r="N65" s="12"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
@@ -8994,10 +8846,10 @@
         <v>41</v>
       </c>
       <c r="B66" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>201</v>
@@ -9006,23 +8858,15 @@
         <v>202</v>
       </c>
       <c r="F66" s="12"/>
-      <c r="G66" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H66" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
       <c r="I66" s="12"/>
       <c r="J66" s="12"/>
-      <c r="K66" s="12" t="s">
-        <v>48</v>
-      </c>
+      <c r="K66" s="12"/>
       <c r="L66" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M66" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="M66" s="12"/>
       <c r="N66" s="12"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
@@ -9030,10 +8874,10 @@
         <v>41</v>
       </c>
       <c r="B67" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>203</v>
@@ -9042,23 +8886,15 @@
         <v>204</v>
       </c>
       <c r="F67" s="12"/>
-      <c r="G67" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H67" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12"/>
       <c r="I67" s="12"/>
       <c r="J67" s="12"/>
-      <c r="K67" s="12" t="s">
-        <v>48</v>
-      </c>
+      <c r="K67" s="12"/>
       <c r="L67" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M67" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="M67" s="12"/>
       <c r="N67" s="12"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
@@ -9066,10 +8902,10 @@
         <v>41</v>
       </c>
       <c r="B68" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>205</v>
@@ -9078,23 +8914,15 @@
         <v>206</v>
       </c>
       <c r="F68" s="12"/>
-      <c r="G68" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H68" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="G68" s="12"/>
+      <c r="H68" s="12"/>
       <c r="I68" s="12"/>
       <c r="J68" s="12"/>
-      <c r="K68" s="12" t="s">
-        <v>48</v>
-      </c>
+      <c r="K68" s="12"/>
       <c r="L68" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M68" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="M68" s="12"/>
       <c r="N68" s="12"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
@@ -9102,10 +8930,10 @@
         <v>41</v>
       </c>
       <c r="B69" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>207</v>
@@ -9114,23 +8942,15 @@
         <v>208</v>
       </c>
       <c r="F69" s="12"/>
-      <c r="G69" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H69" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12"/>
       <c r="I69" s="12"/>
       <c r="J69" s="12"/>
-      <c r="K69" s="12" t="s">
-        <v>48</v>
-      </c>
+      <c r="K69" s="12"/>
       <c r="L69" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M69" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="M69" s="12"/>
       <c r="N69" s="12"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
@@ -9138,10 +8958,10 @@
         <v>41</v>
       </c>
       <c r="B70" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>209</v>
@@ -9150,23 +8970,15 @@
         <v>210</v>
       </c>
       <c r="F70" s="12"/>
-      <c r="G70" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H70" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="G70" s="12"/>
+      <c r="H70" s="12"/>
       <c r="I70" s="12"/>
       <c r="J70" s="12"/>
-      <c r="K70" s="12" t="s">
-        <v>48</v>
-      </c>
+      <c r="K70" s="12"/>
       <c r="L70" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M70" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="M70" s="12"/>
       <c r="N70" s="12"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
@@ -9202,10 +9014,10 @@
         <v>41</v>
       </c>
       <c r="B72" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>213</v>
@@ -9213,16 +9025,30 @@
       <c r="E72" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="F72" s="12"/>
-      <c r="G72" s="12"/>
-      <c r="H72" s="12"/>
-      <c r="I72" s="12"/>
-      <c r="J72" s="12"/>
-      <c r="K72" s="12"/>
+      <c r="F72" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G72" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H72" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I72" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K72" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="L72" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M72" s="12"/>
+      <c r="M72" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="N72" s="12"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
@@ -9230,10 +9056,10 @@
         <v>41</v>
       </c>
       <c r="B73" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>215</v>
@@ -9241,16 +9067,30 @@
       <c r="E73" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="F73" s="12"/>
-      <c r="G73" s="12"/>
-      <c r="H73" s="12"/>
-      <c r="I73" s="12"/>
-      <c r="J73" s="12"/>
-      <c r="K73" s="12"/>
+      <c r="F73" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H73" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I73" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J73" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K73" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="L73" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M73" s="12"/>
+      <c r="M73" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="N73" s="12"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
@@ -9258,10 +9098,10 @@
         <v>41</v>
       </c>
       <c r="B74" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>217</v>
@@ -9269,16 +9109,30 @@
       <c r="E74" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="F74" s="12"/>
-      <c r="G74" s="12"/>
-      <c r="H74" s="12"/>
-      <c r="I74" s="12"/>
-      <c r="J74" s="12"/>
-      <c r="K74" s="12"/>
+      <c r="F74" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G74" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H74" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I74" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J74" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K74" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="L74" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M74" s="12"/>
+      <c r="M74" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="N74" s="12"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
@@ -9286,10 +9140,10 @@
         <v>41</v>
       </c>
       <c r="B75" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>219</v>
@@ -9297,16 +9151,30 @@
       <c r="E75" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="F75" s="12"/>
-      <c r="G75" s="12"/>
-      <c r="H75" s="12"/>
-      <c r="I75" s="12"/>
-      <c r="J75" s="12"/>
-      <c r="K75" s="12"/>
+      <c r="F75" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G75" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H75" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I75" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J75" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="L75" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M75" s="12"/>
+      <c r="M75" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="N75" s="12"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
@@ -9314,10 +9182,10 @@
         <v>41</v>
       </c>
       <c r="B76" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>221</v>
@@ -9325,16 +9193,30 @@
       <c r="E76" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="F76" s="12"/>
-      <c r="G76" s="12"/>
-      <c r="H76" s="12"/>
-      <c r="I76" s="12"/>
-      <c r="J76" s="12"/>
-      <c r="K76" s="12"/>
+      <c r="F76" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G76" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H76" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I76" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J76" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="L76" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M76" s="12"/>
+      <c r="M76" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="N76" s="12"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
@@ -9342,10 +9224,10 @@
         <v>41</v>
       </c>
       <c r="B77" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>223</v>
@@ -9353,16 +9235,30 @@
       <c r="E77" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="F77" s="12"/>
-      <c r="G77" s="12"/>
-      <c r="H77" s="12"/>
-      <c r="I77" s="12"/>
-      <c r="J77" s="12"/>
-      <c r="K77" s="12"/>
+      <c r="F77" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G77" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H77" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I77" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J77" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K77" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="L77" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M77" s="12"/>
+      <c r="M77" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="N77" s="12"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
@@ -9370,10 +9266,10 @@
         <v>41</v>
       </c>
       <c r="B78" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>225</v>
@@ -9381,16 +9277,30 @@
       <c r="E78" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="F78" s="12"/>
-      <c r="G78" s="12"/>
-      <c r="H78" s="12"/>
-      <c r="I78" s="12"/>
-      <c r="J78" s="12"/>
-      <c r="K78" s="12"/>
+      <c r="F78" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G78" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H78" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I78" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J78" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="L78" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M78" s="12"/>
+      <c r="M78" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="N78" s="12"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
@@ -9398,10 +9308,10 @@
         <v>41</v>
       </c>
       <c r="B79" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D79" s="10" t="s">
         <v>227</v>
@@ -9409,16 +9319,28 @@
       <c r="E79" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="F79" s="12"/>
-      <c r="G79" s="12"/>
-      <c r="H79" s="12"/>
-      <c r="I79" s="12"/>
-      <c r="J79" s="12"/>
-      <c r="K79" s="12"/>
+      <c r="F79" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G79" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H79" s="11"/>
+      <c r="I79" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J79" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="L79" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M79" s="12"/>
+      <c r="M79" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="N79" s="12"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
@@ -9426,10 +9348,10 @@
         <v>41</v>
       </c>
       <c r="B80" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D80" s="10" t="s">
         <v>229</v>
@@ -9437,16 +9359,28 @@
       <c r="E80" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="F80" s="12"/>
-      <c r="G80" s="12"/>
-      <c r="H80" s="12"/>
-      <c r="I80" s="12"/>
-      <c r="J80" s="12"/>
-      <c r="K80" s="12"/>
+      <c r="F80" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G80" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H80" s="11"/>
+      <c r="I80" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J80" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K80" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="L80" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M80" s="12"/>
+      <c r="M80" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="N80" s="12"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
@@ -9454,10 +9388,10 @@
         <v>41</v>
       </c>
       <c r="B81" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>231</v>
@@ -9465,16 +9399,28 @@
       <c r="E81" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="F81" s="12"/>
-      <c r="G81" s="12"/>
-      <c r="H81" s="12"/>
-      <c r="I81" s="12"/>
-      <c r="J81" s="12"/>
-      <c r="K81" s="12"/>
+      <c r="F81" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G81" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H81" s="11"/>
+      <c r="I81" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J81" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K81" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="L81" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M81" s="12"/>
+      <c r="M81" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="N81" s="12"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
@@ -9482,10 +9428,10 @@
         <v>41</v>
       </c>
       <c r="B82" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D82" s="10" t="s">
         <v>233</v>
@@ -9493,16 +9439,28 @@
       <c r="E82" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="F82" s="12"/>
-      <c r="G82" s="12"/>
-      <c r="H82" s="12"/>
-      <c r="I82" s="12"/>
-      <c r="J82" s="12"/>
-      <c r="K82" s="12"/>
+      <c r="F82" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G82" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H82" s="11"/>
+      <c r="I82" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J82" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K82" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="L82" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M82" s="12"/>
+      <c r="M82" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="N82" s="12"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
@@ -9510,10 +9468,10 @@
         <v>41</v>
       </c>
       <c r="B83" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D83" s="10" t="s">
         <v>235</v>
@@ -9521,16 +9479,28 @@
       <c r="E83" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="F83" s="12"/>
-      <c r="G83" s="12"/>
-      <c r="H83" s="12"/>
-      <c r="I83" s="12"/>
-      <c r="J83" s="12"/>
-      <c r="K83" s="12"/>
+      <c r="F83" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G83" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H83" s="11"/>
+      <c r="I83" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J83" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K83" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="L83" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M83" s="12"/>
+      <c r="M83" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="N83" s="12"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
@@ -9538,16 +9508,16 @@
         <v>41</v>
       </c>
       <c r="B84" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D84" s="10" t="s">
         <v>237</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="F84" s="11" t="s">
         <v>48</v>
@@ -9555,9 +9525,7 @@
       <c r="G84" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H84" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="H84" s="11"/>
       <c r="I84" s="11" t="s">
         <v>48</v>
       </c>
@@ -9580,16 +9548,16 @@
         <v>41</v>
       </c>
       <c r="B85" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="F85" s="11" t="s">
         <v>48</v>
@@ -9597,9 +9565,7 @@
       <c r="G85" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H85" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="H85" s="11"/>
       <c r="I85" s="11" t="s">
         <v>48</v>
       </c>
@@ -9622,16 +9588,16 @@
         <v>41</v>
       </c>
       <c r="B86" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="F86" s="11" t="s">
         <v>48</v>
@@ -9639,9 +9605,7 @@
       <c r="G86" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H86" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="H86" s="11"/>
       <c r="I86" s="11" t="s">
         <v>48</v>
       </c>
@@ -9664,16 +9628,16 @@
         <v>41</v>
       </c>
       <c r="B87" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="F87" s="11" t="s">
         <v>48</v>
@@ -9681,9 +9645,7 @@
       <c r="G87" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H87" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="H87" s="11"/>
       <c r="I87" s="11" t="s">
         <v>48</v>
       </c>
@@ -9706,16 +9668,16 @@
         <v>41</v>
       </c>
       <c r="B88" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="F88" s="11" t="s">
         <v>48</v>
@@ -9723,9 +9685,7 @@
       <c r="G88" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H88" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="H88" s="11"/>
       <c r="I88" s="11" t="s">
         <v>48</v>
       </c>
@@ -9748,16 +9708,16 @@
         <v>41</v>
       </c>
       <c r="B89" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="F89" s="11" t="s">
         <v>48</v>
@@ -9790,16 +9750,16 @@
         <v>41</v>
       </c>
       <c r="B90" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="F90" s="11" t="s">
         <v>48</v>
@@ -9832,16 +9792,16 @@
         <v>41</v>
       </c>
       <c r="B91" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="F91" s="11" t="s">
         <v>48</v>
@@ -9874,16 +9834,16 @@
         <v>41</v>
       </c>
       <c r="B92" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="F92" s="11" t="s">
         <v>48</v>
@@ -9916,16 +9876,16 @@
         <v>41</v>
       </c>
       <c r="B93" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F93" s="11" t="s">
         <v>48</v>
@@ -9958,16 +9918,16 @@
         <v>41</v>
       </c>
       <c r="B94" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F94" s="11" t="s">
         <v>48</v>
@@ -9975,7 +9935,9 @@
       <c r="G94" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H94" s="11"/>
+      <c r="H94" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="I94" s="11" t="s">
         <v>48</v>
       </c>
@@ -9998,16 +9960,16 @@
         <v>41</v>
       </c>
       <c r="B95" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F95" s="11" t="s">
         <v>48</v>
@@ -10015,7 +9977,9 @@
       <c r="G95" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H95" s="11"/>
+      <c r="H95" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="I95" s="11" t="s">
         <v>48</v>
       </c>
@@ -10038,16 +10002,16 @@
         <v>41</v>
       </c>
       <c r="B96" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F96" s="11" t="s">
         <v>48</v>
@@ -10055,7 +10019,9 @@
       <c r="G96" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H96" s="11"/>
+      <c r="H96" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="I96" s="11" t="s">
         <v>48</v>
       </c>
@@ -10078,16 +10044,16 @@
         <v>41</v>
       </c>
       <c r="B97" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="F97" s="11" t="s">
         <v>48</v>
@@ -10095,7 +10061,9 @@
       <c r="G97" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H97" s="11"/>
+      <c r="H97" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="I97" s="11" t="s">
         <v>48</v>
       </c>
@@ -10118,16 +10086,16 @@
         <v>41</v>
       </c>
       <c r="B98" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F98" s="11" t="s">
         <v>48</v>
@@ -10135,7 +10103,9 @@
       <c r="G98" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H98" s="11"/>
+      <c r="H98" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="I98" s="11" t="s">
         <v>48</v>
       </c>
@@ -10158,16 +10128,16 @@
         <v>41</v>
       </c>
       <c r="B99" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="F99" s="11" t="s">
         <v>48</v>
@@ -10175,7 +10145,9 @@
       <c r="G99" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H99" s="11"/>
+      <c r="H99" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="I99" s="11" t="s">
         <v>48</v>
       </c>
@@ -10198,16 +10170,16 @@
         <v>41</v>
       </c>
       <c r="B100" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="F100" s="11" t="s">
         <v>48</v>
@@ -10215,7 +10187,9 @@
       <c r="G100" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H100" s="11"/>
+      <c r="H100" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="I100" s="11" t="s">
         <v>48</v>
       </c>
@@ -10238,33 +10212,27 @@
         <v>41</v>
       </c>
       <c r="B101" s="10">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="F101" s="11" t="s">
-        <v>48</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="F101" s="12"/>
       <c r="G101" s="11" t="s">
         <v>48</v>
       </c>
       <c r="H101" s="11"/>
-      <c r="I101" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="I101" s="12"/>
       <c r="J101" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="K101" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="K101" s="11"/>
       <c r="L101" s="11" t="s">
         <v>48</v>
       </c>
@@ -10278,27 +10246,23 @@
         <v>41</v>
       </c>
       <c r="B102" s="10">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D102" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="E102" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="E102" s="10" t="s">
-        <v>263</v>
-      </c>
       <c r="F102" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G102" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H102" s="11"/>
-      <c r="I102" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="G102" s="12"/>
+      <c r="H102" s="12"/>
+      <c r="I102" s="12"/>
       <c r="J102" s="11" t="s">
         <v>48</v>
       </c>
@@ -10308,9 +10272,7 @@
       <c r="L102" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M102" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="M102" s="12"/>
       <c r="N102" s="12"/>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.3">
@@ -10318,27 +10280,23 @@
         <v>41</v>
       </c>
       <c r="B103" s="10">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D103" s="10" t="s">
         <v>270</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F103" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G103" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H103" s="11"/>
-      <c r="I103" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="G103" s="12"/>
+      <c r="H103" s="12"/>
+      <c r="I103" s="12"/>
       <c r="J103" s="11" t="s">
         <v>48</v>
       </c>
@@ -10348,9 +10306,7 @@
       <c r="L103" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M103" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="M103" s="12"/>
       <c r="N103" s="12"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.3">
@@ -10358,29 +10314,23 @@
         <v>41</v>
       </c>
       <c r="B104" s="10">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F104" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G104" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H104" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I104" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="G104" s="12"/>
+      <c r="H104" s="12"/>
+      <c r="I104" s="12"/>
       <c r="J104" s="11" t="s">
         <v>48</v>
       </c>
@@ -10390,9 +10340,7 @@
       <c r="L104" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M104" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="M104" s="12"/>
       <c r="N104" s="12"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.3">
@@ -10400,29 +10348,23 @@
         <v>41</v>
       </c>
       <c r="B105" s="10">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F105" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G105" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H105" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I105" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="G105" s="12"/>
+      <c r="H105" s="12"/>
+      <c r="I105" s="12"/>
       <c r="J105" s="11" t="s">
         <v>48</v>
       </c>
@@ -10432,9 +10374,7 @@
       <c r="L105" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M105" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="M105" s="12"/>
       <c r="N105" s="12"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
@@ -10442,16 +10382,16 @@
         <v>41</v>
       </c>
       <c r="B106" s="10">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F106" s="11" t="s">
         <v>48</v>
@@ -10484,16 +10424,16 @@
         <v>41</v>
       </c>
       <c r="B107" s="10">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F107" s="11" t="s">
         <v>48</v>
@@ -10526,16 +10466,16 @@
         <v>41</v>
       </c>
       <c r="B108" s="10">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F108" s="11" t="s">
         <v>48</v>
@@ -10568,16 +10508,16 @@
         <v>41</v>
       </c>
       <c r="B109" s="10">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F109" s="11" t="s">
         <v>48</v>
@@ -10610,80 +10550,58 @@
         <v>41</v>
       </c>
       <c r="B110" s="10">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="F110" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G110" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H110" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I110" s="11" t="s">
-        <v>48</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="F110" s="12"/>
+      <c r="G110" s="12"/>
+      <c r="H110" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I110" s="12"/>
       <c r="J110" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="K110" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L110" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="K110" s="11"/>
+      <c r="L110" s="12"/>
       <c r="M110" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="N110" s="12"/>
+      <c r="N110" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="10" t="s">
         <v>41</v>
       </c>
       <c r="B111" s="10">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="F111" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G111" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H111" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I111" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J111" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K111" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L111" s="11" t="s">
-        <v>48</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="F111" s="12"/>
+      <c r="G111" s="12"/>
+      <c r="H111" s="12"/>
+      <c r="I111" s="12"/>
+      <c r="J111" s="12"/>
+      <c r="K111" s="12"/>
+      <c r="L111" s="12"/>
       <c r="M111" s="11" t="s">
         <v>48</v>
       </c>
@@ -10694,38 +10612,24 @@
         <v>41</v>
       </c>
       <c r="B112" s="10">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="F112" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G112" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H112" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I112" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J112" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K112" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L112" s="11" t="s">
-        <v>48</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="F112" s="12"/>
+      <c r="G112" s="12"/>
+      <c r="H112" s="12"/>
+      <c r="I112" s="12"/>
+      <c r="J112" s="12"/>
+      <c r="K112" s="12"/>
+      <c r="L112" s="12"/>
       <c r="M112" s="11" t="s">
         <v>48</v>
       </c>
@@ -10733,19 +10637,19 @@
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B113" s="10">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F113" s="11" t="s">
         <v>48</v>
@@ -10771,23 +10675,25 @@
       <c r="M113" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="N113" s="12"/>
+      <c r="N113" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B114" s="10">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E114" s="10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F114" s="11" t="s">
         <v>48</v>
@@ -10813,23 +10719,25 @@
       <c r="M114" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="N114" s="12"/>
+      <c r="N114" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B115" s="10">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F115" s="11" t="s">
         <v>48</v>
@@ -10855,23 +10763,25 @@
       <c r="M115" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="N115" s="12"/>
+      <c r="N115" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B116" s="10">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>295</v>
+        <v>262</v>
       </c>
       <c r="E116" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F116" s="11" t="s">
         <v>48</v>
@@ -10897,23 +10807,25 @@
       <c r="M116" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="N116" s="12"/>
+      <c r="N116" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B117" s="10">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>297</v>
+        <v>1064</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>298</v>
+        <v>1066</v>
       </c>
       <c r="F117" s="11" t="s">
         <v>48</v>
@@ -10939,37 +10851,33 @@
       <c r="M117" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="N117" s="12"/>
+      <c r="N117" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B118" s="10">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>299</v>
+        <v>1065</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>300</v>
+        <v>1067</v>
       </c>
       <c r="F118" s="12"/>
-      <c r="G118" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H118" s="11"/>
+      <c r="G118" s="12"/>
+      <c r="H118" s="12"/>
       <c r="I118" s="12"/>
-      <c r="J118" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K118" s="11"/>
-      <c r="L118" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="J118" s="12"/>
+      <c r="K118" s="12"/>
+      <c r="L118" s="12"/>
       <c r="M118" s="11" t="s">
         <v>48</v>
       </c>
@@ -10977,26 +10885,32 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B119" s="10">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>302</v>
+        <v>1062</v>
       </c>
       <c r="F119" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G119" s="12"/>
-      <c r="H119" s="12"/>
-      <c r="I119" s="12"/>
+      <c r="G119" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H119" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I119" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="J119" s="11" t="s">
         <v>48</v>
       </c>
@@ -11006,31 +10920,41 @@
       <c r="L119" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M119" s="12"/>
-      <c r="N119" s="12"/>
+      <c r="M119" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N119" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B120" s="10">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E120" s="10" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F120" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G120" s="12"/>
-      <c r="H120" s="12"/>
-      <c r="I120" s="12"/>
+      <c r="G120" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H120" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I120" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="J120" s="11" t="s">
         <v>48</v>
       </c>
@@ -11040,31 +10964,41 @@
       <c r="L120" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M120" s="12"/>
-      <c r="N120" s="12"/>
+      <c r="M120" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N120" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B121" s="10">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F121" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G121" s="12"/>
-      <c r="H121" s="12"/>
-      <c r="I121" s="12"/>
+      <c r="G121" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H121" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I121" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="J121" s="11" t="s">
         <v>48</v>
       </c>
@@ -11074,31 +11008,41 @@
       <c r="L121" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M121" s="12"/>
-      <c r="N121" s="12"/>
+      <c r="M121" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N121" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B122" s="10">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>308</v>
+        <v>1063</v>
       </c>
       <c r="F122" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G122" s="12"/>
-      <c r="H122" s="12"/>
-      <c r="I122" s="12"/>
+      <c r="G122" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H122" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I122" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="J122" s="11" t="s">
         <v>48</v>
       </c>
@@ -11108,31 +11052,41 @@
       <c r="L122" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M122" s="12"/>
-      <c r="N122" s="12"/>
+      <c r="M122" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N122" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B123" s="10">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D123" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="E123" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="E123" s="10" t="s">
-        <v>310</v>
-      </c>
       <c r="F123" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G123" s="12"/>
-      <c r="H123" s="12"/>
-      <c r="I123" s="12"/>
+      <c r="G123" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H123" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I123" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="J123" s="11" t="s">
         <v>48</v>
       </c>
@@ -11142,31 +11096,41 @@
       <c r="L123" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M123" s="12"/>
-      <c r="N123" s="12"/>
+      <c r="M123" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N123" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B124" s="10">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D124" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="E124" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="E124" s="10" t="s">
-        <v>312</v>
-      </c>
       <c r="F124" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G124" s="12"/>
-      <c r="H124" s="12"/>
-      <c r="I124" s="12"/>
+      <c r="G124" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H124" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I124" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="J124" s="11" t="s">
         <v>48</v>
       </c>
@@ -11176,31 +11140,41 @@
       <c r="L124" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M124" s="12"/>
-      <c r="N124" s="12"/>
+      <c r="M124" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N124" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B125" s="10">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D125" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="E125" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="E125" s="10" t="s">
-        <v>314</v>
-      </c>
       <c r="F125" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G125" s="12"/>
-      <c r="H125" s="12"/>
-      <c r="I125" s="12"/>
+      <c r="G125" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H125" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I125" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="J125" s="11" t="s">
         <v>48</v>
       </c>
@@ -11210,25 +11184,29 @@
       <c r="L125" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M125" s="12"/>
-      <c r="N125" s="12"/>
+      <c r="M125" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N125" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B126" s="10">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D126" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="E126" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="E126" s="10" t="s">
-        <v>316</v>
-      </c>
       <c r="F126" s="11" t="s">
         <v>48</v>
       </c>
@@ -11253,24 +11231,26 @@
       <c r="M126" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="N126" s="12"/>
+      <c r="N126" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B127" s="10">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D127" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="E127" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="E127" s="10" t="s">
-        <v>318</v>
-      </c>
       <c r="F127" s="11" t="s">
         <v>48</v>
       </c>
@@ -11295,1153 +11275,15 @@
       <c r="M127" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="N127" s="12"/>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A128" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B128" s="10">
-        <v>21</v>
-      </c>
-      <c r="C128" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D128" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="E128" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="F128" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G128" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H128" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I128" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J128" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K128" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L128" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M128" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N128" s="12"/>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A129" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B129" s="10">
-        <v>21</v>
-      </c>
-      <c r="C129" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D129" s="10" t="s">
-        <v>321</v>
-      </c>
-      <c r="E129" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="F129" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G129" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H129" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I129" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J129" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K129" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L129" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M129" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N129" s="12"/>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A130" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B130" s="10">
-        <v>22</v>
-      </c>
-      <c r="C130" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D130" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="E130" s="10" t="s">
-        <v>324</v>
-      </c>
-      <c r="F130" s="12"/>
-      <c r="G130" s="12"/>
-      <c r="H130" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="I130" s="12"/>
-      <c r="J130" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K130" s="11"/>
-      <c r="L130" s="12"/>
-      <c r="M130" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N130" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A131" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B131" s="10">
-        <v>23</v>
-      </c>
-      <c r="C131" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D131" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="E131" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="F131" s="12"/>
-      <c r="G131" s="12"/>
-      <c r="H131" s="12"/>
-      <c r="I131" s="12"/>
-      <c r="J131" s="12"/>
-      <c r="K131" s="12"/>
-      <c r="L131" s="12"/>
-      <c r="M131" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N131" s="12"/>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A132" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B132" s="10">
-        <v>23</v>
-      </c>
-      <c r="C132" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D132" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="E132" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="F132" s="12"/>
-      <c r="G132" s="12"/>
-      <c r="H132" s="12"/>
-      <c r="I132" s="12"/>
-      <c r="J132" s="12"/>
-      <c r="K132" s="12"/>
-      <c r="L132" s="12"/>
-      <c r="M132" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N132" s="12"/>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A133" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B133" s="10">
-        <v>24</v>
-      </c>
-      <c r="C133" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D133" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="E133" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="F133" s="12"/>
-      <c r="G133" s="12"/>
-      <c r="H133" s="12"/>
-      <c r="I133" s="12"/>
-      <c r="J133" s="12"/>
-      <c r="K133" s="12"/>
-      <c r="L133" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M133" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N133" s="12"/>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A134" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B134" s="10">
-        <v>25</v>
-      </c>
-      <c r="C134" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D134" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="E134" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="F134" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G134" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H134" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I134" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J134" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K134" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L134" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M134" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N134" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A135" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B135" s="10">
-        <v>25</v>
-      </c>
-      <c r="C135" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D135" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="E135" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="F135" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G135" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H135" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I135" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J135" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K135" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L135" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M135" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N135" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A136" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B136" s="10">
-        <v>25</v>
-      </c>
-      <c r="C136" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D136" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="E136" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="F136" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G136" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H136" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I136" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J136" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K136" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L136" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M136" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N136" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A137" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B137" s="10">
-        <v>25</v>
-      </c>
-      <c r="C137" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D137" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="E137" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="F137" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G137" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H137" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I137" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J137" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K137" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L137" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M137" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N137" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A138" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B138" s="10">
-        <v>25</v>
-      </c>
-      <c r="C138" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D138" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="E138" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="F138" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G138" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H138" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I138" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J138" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K138" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L138" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M138" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N138" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A139" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B139" s="10">
-        <v>25</v>
-      </c>
-      <c r="C139" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D139" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="E139" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="F139" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G139" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H139" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I139" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J139" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K139" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L139" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M139" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N139" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A140" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B140" s="10">
-        <v>26</v>
-      </c>
-      <c r="C140" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D140" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="E140" s="10"/>
-      <c r="F140" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G140" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H140" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I140" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J140" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K140" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L140" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M140" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N140" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A141" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B141" s="10">
-        <v>27</v>
-      </c>
-      <c r="C141" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D141" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="E141" s="10"/>
-      <c r="F141" s="12"/>
-      <c r="G141" s="12"/>
-      <c r="H141" s="12"/>
-      <c r="I141" s="12"/>
-      <c r="J141" s="12"/>
-      <c r="K141" s="12"/>
-      <c r="L141" s="12"/>
-      <c r="M141" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N141" s="12"/>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A142" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B142" s="10">
-        <v>28</v>
-      </c>
-      <c r="C142" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D142" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="E142" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="F142" s="12"/>
-      <c r="G142" s="12"/>
-      <c r="H142" s="12"/>
-      <c r="I142" s="12"/>
-      <c r="J142" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K142" s="11"/>
-      <c r="L142" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M142" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N142" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A143" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B143" s="10">
-        <v>29</v>
-      </c>
-      <c r="C143" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D143" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="E143" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="F143" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G143" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H143" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I143" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J143" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K143" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L143" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M143" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N143" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A144" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B144" s="10">
-        <v>29</v>
-      </c>
-      <c r="C144" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D144" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="E144" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="F144" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G144" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H144" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I144" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J144" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K144" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L144" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M144" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N144" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A145" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B145" s="10">
-        <v>29</v>
-      </c>
-      <c r="C145" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D145" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="E145" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="F145" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G145" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H145" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I145" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J145" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K145" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L145" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M145" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N145" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A146" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B146" s="10">
-        <v>29</v>
-      </c>
-      <c r="C146" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D146" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="E146" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="F146" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G146" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H146" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I146" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J146" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K146" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L146" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M146" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N146" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A147" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B147" s="10">
-        <v>29</v>
-      </c>
-      <c r="C147" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D147" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="E147" s="10" t="s">
-        <v>351</v>
-      </c>
-      <c r="F147" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G147" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H147" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I147" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J147" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K147" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L147" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M147" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N147" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A148" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B148" s="10">
-        <v>29</v>
-      </c>
-      <c r="C148" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D148" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="E148" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="F148" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G148" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H148" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I148" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J148" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K148" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L148" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M148" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N148" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A149" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B149" s="10">
-        <v>29</v>
-      </c>
-      <c r="C149" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D149" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="E149" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="F149" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G149" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H149" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I149" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J149" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K149" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L149" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M149" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N149" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A150" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B150" s="10">
-        <v>29</v>
-      </c>
-      <c r="C150" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D150" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="E150" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="F150" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G150" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H150" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I150" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J150" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K150" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L150" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M150" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N150" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A151" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B151" s="10">
-        <v>29</v>
-      </c>
-      <c r="C151" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D151" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="E151" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="F151" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G151" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H151" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I151" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J151" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K151" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L151" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M151" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N151" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A152" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B152" s="10">
-        <v>29</v>
-      </c>
-      <c r="C152" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D152" s="10" t="s">
-        <v>360</v>
-      </c>
-      <c r="E152" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="F152" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G152" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H152" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I152" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J152" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K152" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L152" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M152" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N152" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A153" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B153" s="10">
-        <v>29</v>
-      </c>
-      <c r="C153" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D153" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="E153" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="F153" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G153" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H153" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I153" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J153" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K153" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L153" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M153" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N153" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A154" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B154" s="10">
-        <v>29</v>
-      </c>
-      <c r="C154" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D154" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="E154" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="F154" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G154" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H154" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I154" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J154" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K154" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L154" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M154" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N154" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A155" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B155" s="10">
-        <v>29</v>
-      </c>
-      <c r="C155" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D155" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="E155" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="F155" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G155" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H155" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I155" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J155" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K155" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L155" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M155" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N155" s="11" t="s">
+      <c r="N127" s="11" t="s">
         <v>48</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N127"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -12456,3509 +11298,3510 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>367</v>
+        <v>321</v>
       </c>
       <c r="B1" t="s">
-        <v>368</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>369</v>
+        <v>323</v>
       </c>
       <c r="B2" t="s">
-        <v>370</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>371</v>
+        <v>325</v>
       </c>
       <c r="B3" t="s">
-        <v>370</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>372</v>
+        <v>326</v>
       </c>
       <c r="B4" t="s">
-        <v>373</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>374</v>
+        <v>328</v>
       </c>
       <c r="B5" t="s">
-        <v>375</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>376</v>
+        <v>330</v>
       </c>
       <c r="B6" t="s">
-        <v>377</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>378</v>
+        <v>332</v>
       </c>
       <c r="B7" t="s">
-        <v>379</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>380</v>
+        <v>334</v>
       </c>
       <c r="B8" t="s">
-        <v>381</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>382</v>
+        <v>336</v>
       </c>
       <c r="B9" t="s">
-        <v>383</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="B10" t="s">
-        <v>385</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>386</v>
+        <v>340</v>
       </c>
       <c r="B11" t="s">
-        <v>387</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>388</v>
+        <v>342</v>
       </c>
       <c r="B12" t="s">
-        <v>389</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>390</v>
+        <v>344</v>
       </c>
       <c r="B13" t="s">
-        <v>391</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>392</v>
+        <v>346</v>
       </c>
       <c r="B14" t="s">
-        <v>393</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>394</v>
+        <v>348</v>
       </c>
       <c r="B15" t="s">
-        <v>395</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>396</v>
+        <v>350</v>
       </c>
       <c r="B16" t="s">
-        <v>397</v>
+        <v>351</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>398</v>
+        <v>352</v>
       </c>
       <c r="B17" t="s">
-        <v>399</v>
+        <v>353</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>400</v>
+        <v>354</v>
       </c>
       <c r="B18" t="s">
-        <v>401</v>
+        <v>355</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>402</v>
+        <v>356</v>
       </c>
       <c r="B19" t="s">
-        <v>403</v>
+        <v>357</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>404</v>
+        <v>358</v>
       </c>
       <c r="B20" t="s">
-        <v>405</v>
+        <v>359</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>406</v>
+        <v>360</v>
       </c>
       <c r="B21" t="s">
-        <v>407</v>
+        <v>361</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>408</v>
+        <v>362</v>
       </c>
       <c r="B22" t="s">
-        <v>409</v>
+        <v>363</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>410</v>
+        <v>364</v>
       </c>
       <c r="B23" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>412</v>
+        <v>366</v>
       </c>
       <c r="B24" t="s">
-        <v>413</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>414</v>
+        <v>368</v>
       </c>
       <c r="B25" t="s">
-        <v>415</v>
+        <v>369</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>416</v>
+        <v>370</v>
       </c>
       <c r="B26" t="s">
-        <v>417</v>
+        <v>371</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>418</v>
+        <v>372</v>
       </c>
       <c r="B27" t="s">
-        <v>419</v>
+        <v>373</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>420</v>
+        <v>374</v>
       </c>
       <c r="B28" t="s">
-        <v>421</v>
+        <v>375</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>422</v>
+        <v>376</v>
       </c>
       <c r="B29" t="s">
-        <v>423</v>
+        <v>377</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>424</v>
+        <v>378</v>
       </c>
       <c r="B30" t="s">
-        <v>425</v>
+        <v>379</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>426</v>
+        <v>380</v>
       </c>
       <c r="B31" t="s">
-        <v>427</v>
+        <v>381</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>428</v>
+        <v>382</v>
       </c>
       <c r="B32" t="s">
-        <v>429</v>
+        <v>383</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>430</v>
+        <v>384</v>
       </c>
       <c r="B33" t="s">
-        <v>431</v>
+        <v>385</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>432</v>
+        <v>386</v>
       </c>
       <c r="B34" t="s">
-        <v>433</v>
+        <v>387</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>434</v>
+        <v>388</v>
       </c>
       <c r="B35" t="s">
-        <v>435</v>
+        <v>389</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>436</v>
+        <v>390</v>
       </c>
       <c r="B36" t="s">
-        <v>437</v>
+        <v>391</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>438</v>
+        <v>392</v>
       </c>
       <c r="B37" t="s">
-        <v>439</v>
+        <v>393</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>440</v>
+        <v>394</v>
       </c>
       <c r="B38" t="s">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>442</v>
+        <v>396</v>
       </c>
       <c r="B39" t="s">
-        <v>443</v>
+        <v>397</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>444</v>
+        <v>398</v>
       </c>
       <c r="B40" t="s">
-        <v>445</v>
+        <v>399</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>446</v>
+        <v>400</v>
       </c>
       <c r="B41" t="s">
-        <v>447</v>
+        <v>401</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>448</v>
+        <v>402</v>
       </c>
       <c r="B42" t="s">
-        <v>449</v>
+        <v>403</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>450</v>
+        <v>404</v>
       </c>
       <c r="B43" t="s">
-        <v>451</v>
+        <v>405</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>452</v>
+        <v>406</v>
       </c>
       <c r="B44" t="s">
-        <v>453</v>
+        <v>407</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>454</v>
+        <v>408</v>
       </c>
       <c r="B45" t="s">
-        <v>455</v>
+        <v>409</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>456</v>
+        <v>410</v>
       </c>
       <c r="B46" t="s">
-        <v>457</v>
+        <v>411</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>458</v>
+        <v>412</v>
       </c>
       <c r="B47" t="s">
-        <v>459</v>
+        <v>413</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>460</v>
+        <v>414</v>
       </c>
       <c r="B48" t="s">
-        <v>459</v>
+        <v>413</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>461</v>
+        <v>415</v>
       </c>
       <c r="B49" t="s">
-        <v>462</v>
+        <v>416</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>463</v>
+        <v>417</v>
       </c>
       <c r="B50" t="s">
-        <v>464</v>
+        <v>418</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>465</v>
+        <v>419</v>
       </c>
       <c r="B51" t="s">
-        <v>466</v>
+        <v>420</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>467</v>
+        <v>421</v>
       </c>
       <c r="B52" t="s">
-        <v>468</v>
+        <v>422</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>469</v>
+        <v>423</v>
       </c>
       <c r="B53" t="s">
-        <v>470</v>
+        <v>424</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>471</v>
+        <v>425</v>
       </c>
       <c r="B54" t="s">
-        <v>472</v>
+        <v>426</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>473</v>
+        <v>427</v>
       </c>
       <c r="B55" t="s">
-        <v>474</v>
+        <v>428</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>475</v>
+        <v>429</v>
       </c>
       <c r="B56" t="s">
-        <v>476</v>
+        <v>430</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>477</v>
+        <v>431</v>
       </c>
       <c r="B57" t="s">
-        <v>478</v>
+        <v>432</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>479</v>
+        <v>433</v>
       </c>
       <c r="B58" t="s">
-        <v>480</v>
+        <v>434</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>481</v>
+        <v>435</v>
       </c>
       <c r="B59" t="s">
-        <v>482</v>
+        <v>436</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>483</v>
+        <v>437</v>
       </c>
       <c r="B60" t="s">
-        <v>484</v>
+        <v>438</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>485</v>
+        <v>439</v>
       </c>
       <c r="B61" t="s">
-        <v>486</v>
+        <v>440</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>487</v>
+        <v>441</v>
       </c>
       <c r="B62" t="s">
-        <v>486</v>
+        <v>440</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>488</v>
+        <v>442</v>
       </c>
       <c r="B63" t="s">
-        <v>489</v>
+        <v>443</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>490</v>
+        <v>444</v>
       </c>
       <c r="B64" t="s">
-        <v>489</v>
+        <v>443</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>491</v>
+        <v>445</v>
       </c>
       <c r="B65" t="s">
-        <v>492</v>
+        <v>446</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>493</v>
+        <v>447</v>
       </c>
       <c r="B66" t="s">
-        <v>492</v>
+        <v>446</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>494</v>
+        <v>448</v>
       </c>
       <c r="B67" t="s">
-        <v>495</v>
+        <v>449</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>496</v>
+        <v>450</v>
       </c>
       <c r="B68" t="s">
-        <v>495</v>
+        <v>449</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>497</v>
+        <v>451</v>
       </c>
       <c r="B69" t="s">
-        <v>498</v>
+        <v>452</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>499</v>
+        <v>453</v>
       </c>
       <c r="B70" t="s">
-        <v>500</v>
+        <v>454</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>501</v>
+        <v>455</v>
       </c>
       <c r="B71" t="s">
-        <v>502</v>
+        <v>456</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>503</v>
+        <v>457</v>
       </c>
       <c r="B72" t="s">
-        <v>504</v>
+        <v>458</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>505</v>
+        <v>459</v>
       </c>
       <c r="B73" t="s">
-        <v>506</v>
+        <v>460</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>507</v>
+        <v>461</v>
       </c>
       <c r="B74" t="s">
-        <v>508</v>
+        <v>462</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>509</v>
+        <v>463</v>
       </c>
       <c r="B75" t="s">
-        <v>510</v>
+        <v>464</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>511</v>
+        <v>465</v>
       </c>
       <c r="B76" t="s">
-        <v>510</v>
+        <v>464</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>512</v>
+        <v>466</v>
       </c>
       <c r="B77" t="s">
-        <v>513</v>
+        <v>467</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>514</v>
+        <v>468</v>
       </c>
       <c r="B78" t="s">
-        <v>515</v>
+        <v>469</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>516</v>
+        <v>470</v>
       </c>
       <c r="B79" t="s">
-        <v>515</v>
+        <v>469</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>517</v>
+        <v>471</v>
       </c>
       <c r="B80" t="s">
-        <v>518</v>
+        <v>472</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>519</v>
+        <v>473</v>
       </c>
       <c r="B81" t="s">
-        <v>520</v>
+        <v>474</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>521</v>
+        <v>475</v>
       </c>
       <c r="B82" t="s">
-        <v>520</v>
+        <v>474</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>522</v>
+        <v>476</v>
       </c>
       <c r="B83" t="s">
-        <v>523</v>
+        <v>477</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>524</v>
+        <v>478</v>
       </c>
       <c r="B84" t="s">
-        <v>523</v>
+        <v>477</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>525</v>
+        <v>479</v>
       </c>
       <c r="B85" t="s">
-        <v>526</v>
+        <v>480</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>527</v>
+        <v>481</v>
       </c>
       <c r="B86" t="s">
-        <v>526</v>
+        <v>480</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>528</v>
+        <v>482</v>
       </c>
       <c r="B87" t="s">
-        <v>526</v>
+        <v>480</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>529</v>
+        <v>483</v>
       </c>
       <c r="B88" t="s">
-        <v>530</v>
+        <v>484</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>531</v>
+        <v>485</v>
       </c>
       <c r="B89" t="s">
-        <v>532</v>
+        <v>486</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>533</v>
+        <v>487</v>
       </c>
       <c r="B90" t="s">
-        <v>532</v>
+        <v>486</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>534</v>
+        <v>488</v>
       </c>
       <c r="B91" t="s">
-        <v>535</v>
+        <v>489</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>536</v>
+        <v>490</v>
       </c>
       <c r="B92" t="s">
-        <v>537</v>
+        <v>491</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>538</v>
+        <v>492</v>
       </c>
       <c r="B93" t="s">
-        <v>537</v>
+        <v>491</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>539</v>
+        <v>493</v>
       </c>
       <c r="B94" t="s">
-        <v>537</v>
+        <v>491</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>540</v>
+        <v>494</v>
       </c>
       <c r="B95" t="s">
-        <v>541</v>
+        <v>495</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>542</v>
+        <v>496</v>
       </c>
       <c r="B96" t="s">
-        <v>543</v>
+        <v>497</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>544</v>
+        <v>498</v>
       </c>
       <c r="B97" t="s">
-        <v>545</v>
+        <v>499</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>546</v>
+        <v>500</v>
       </c>
       <c r="B98" t="s">
-        <v>547</v>
+        <v>501</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>548</v>
+        <v>502</v>
       </c>
       <c r="B99" t="s">
-        <v>549</v>
+        <v>503</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>550</v>
+        <v>504</v>
       </c>
       <c r="B100" t="s">
-        <v>551</v>
+        <v>505</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>552</v>
+        <v>506</v>
       </c>
       <c r="B101" t="s">
-        <v>553</v>
+        <v>507</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>554</v>
+        <v>508</v>
       </c>
       <c r="B102" t="s">
-        <v>555</v>
+        <v>509</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>556</v>
+        <v>510</v>
       </c>
       <c r="B103" t="s">
-        <v>557</v>
+        <v>511</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>558</v>
+        <v>512</v>
       </c>
       <c r="B104" t="s">
-        <v>559</v>
+        <v>513</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>560</v>
+        <v>514</v>
       </c>
       <c r="B105" t="s">
-        <v>561</v>
+        <v>515</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>562</v>
+        <v>516</v>
       </c>
       <c r="B106" t="s">
-        <v>563</v>
+        <v>517</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>564</v>
+        <v>518</v>
       </c>
       <c r="B107" t="s">
-        <v>565</v>
+        <v>519</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>566</v>
+        <v>520</v>
       </c>
       <c r="B108" t="s">
-        <v>565</v>
+        <v>519</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>567</v>
+        <v>521</v>
       </c>
       <c r="B109" t="s">
-        <v>568</v>
+        <v>522</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>569</v>
+        <v>523</v>
       </c>
       <c r="B110" t="s">
-        <v>570</v>
+        <v>524</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>571</v>
+        <v>525</v>
       </c>
       <c r="B111" t="s">
-        <v>572</v>
+        <v>526</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>573</v>
+        <v>527</v>
       </c>
       <c r="B112" t="s">
-        <v>574</v>
+        <v>528</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>575</v>
+        <v>529</v>
       </c>
       <c r="B113" t="s">
-        <v>576</v>
+        <v>530</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>577</v>
+        <v>531</v>
       </c>
       <c r="B114" t="s">
-        <v>578</v>
+        <v>532</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>579</v>
+        <v>533</v>
       </c>
       <c r="B115" t="s">
-        <v>580</v>
+        <v>534</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>581</v>
+        <v>535</v>
       </c>
       <c r="B116" t="s">
-        <v>582</v>
+        <v>536</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>583</v>
+        <v>537</v>
       </c>
       <c r="B117" t="s">
-        <v>584</v>
+        <v>538</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>585</v>
+        <v>539</v>
       </c>
       <c r="B118" t="s">
-        <v>586</v>
+        <v>540</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>587</v>
+        <v>541</v>
       </c>
       <c r="B119" t="s">
-        <v>588</v>
+        <v>542</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>589</v>
+        <v>543</v>
       </c>
       <c r="B120" t="s">
-        <v>590</v>
+        <v>544</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>591</v>
+        <v>545</v>
       </c>
       <c r="B121" t="s">
-        <v>592</v>
+        <v>546</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>593</v>
+        <v>547</v>
       </c>
       <c r="B122" t="s">
-        <v>594</v>
+        <v>548</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>595</v>
+        <v>549</v>
       </c>
       <c r="B123" t="s">
-        <v>596</v>
+        <v>550</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>597</v>
+        <v>551</v>
       </c>
       <c r="B124" t="s">
-        <v>598</v>
+        <v>552</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>599</v>
+        <v>553</v>
       </c>
       <c r="B125" t="s">
-        <v>600</v>
+        <v>554</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>601</v>
+        <v>555</v>
       </c>
       <c r="B126" t="s">
-        <v>602</v>
+        <v>556</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>603</v>
+        <v>557</v>
       </c>
       <c r="B127" t="s">
-        <v>602</v>
+        <v>556</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>604</v>
+        <v>558</v>
       </c>
       <c r="B128" t="s">
-        <v>605</v>
+        <v>559</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>606</v>
+        <v>560</v>
       </c>
       <c r="B129" t="s">
-        <v>605</v>
+        <v>559</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>607</v>
+        <v>561</v>
       </c>
       <c r="B130" t="s">
-        <v>608</v>
+        <v>562</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>609</v>
+        <v>563</v>
       </c>
       <c r="B131" t="s">
-        <v>610</v>
+        <v>564</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>611</v>
+        <v>565</v>
       </c>
       <c r="B132" t="s">
-        <v>612</v>
+        <v>566</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>613</v>
+        <v>567</v>
       </c>
       <c r="B133" t="s">
-        <v>614</v>
+        <v>568</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>615</v>
+        <v>569</v>
       </c>
       <c r="B134" t="s">
-        <v>616</v>
+        <v>570</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>617</v>
+        <v>571</v>
       </c>
       <c r="B135" t="s">
-        <v>618</v>
+        <v>572</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>617</v>
+        <v>571</v>
       </c>
       <c r="B136" t="s">
-        <v>619</v>
+        <v>573</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>620</v>
+        <v>574</v>
       </c>
       <c r="B137" t="s">
-        <v>621</v>
+        <v>575</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>622</v>
+        <v>576</v>
       </c>
       <c r="B138" t="s">
-        <v>623</v>
+        <v>577</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>624</v>
+        <v>578</v>
       </c>
       <c r="B139" t="s">
-        <v>625</v>
+        <v>579</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>624</v>
+        <v>578</v>
       </c>
       <c r="B140" t="s">
-        <v>626</v>
+        <v>580</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>627</v>
+        <v>581</v>
       </c>
       <c r="B141" t="s">
-        <v>628</v>
+        <v>582</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>629</v>
+        <v>583</v>
       </c>
       <c r="B142" t="s">
-        <v>630</v>
+        <v>584</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>629</v>
+        <v>583</v>
       </c>
       <c r="B143" t="s">
-        <v>631</v>
+        <v>585</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>632</v>
+        <v>586</v>
       </c>
       <c r="B144" t="s">
-        <v>633</v>
+        <v>587</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>634</v>
+        <v>588</v>
       </c>
       <c r="B145" t="s">
-        <v>635</v>
+        <v>589</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>636</v>
+        <v>590</v>
       </c>
       <c r="B146" t="s">
-        <v>637</v>
+        <v>591</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>638</v>
+        <v>592</v>
       </c>
       <c r="B147" t="s">
-        <v>639</v>
+        <v>593</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>640</v>
+        <v>594</v>
       </c>
       <c r="B148" t="s">
-        <v>641</v>
+        <v>595</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>642</v>
+        <v>596</v>
       </c>
       <c r="B149" t="s">
-        <v>643</v>
+        <v>597</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>644</v>
+        <v>598</v>
       </c>
       <c r="B150" t="s">
-        <v>645</v>
+        <v>599</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>646</v>
+        <v>600</v>
       </c>
       <c r="B151" t="s">
-        <v>647</v>
+        <v>601</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>646</v>
+        <v>600</v>
       </c>
       <c r="B152" t="s">
-        <v>648</v>
+        <v>602</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>649</v>
+        <v>603</v>
       </c>
       <c r="B153" t="s">
-        <v>650</v>
+        <v>604</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>651</v>
+        <v>605</v>
       </c>
       <c r="B154" t="s">
-        <v>314</v>
+        <v>276</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>652</v>
+        <v>606</v>
       </c>
       <c r="B155" t="s">
-        <v>653</v>
+        <v>607</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>654</v>
+        <v>608</v>
       </c>
       <c r="B156" t="s">
-        <v>655</v>
+        <v>609</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>654</v>
+        <v>608</v>
       </c>
       <c r="B157" t="s">
-        <v>656</v>
+        <v>610</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>654</v>
+        <v>608</v>
       </c>
       <c r="B158" t="s">
-        <v>657</v>
+        <v>611</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>654</v>
+        <v>608</v>
       </c>
       <c r="B159" t="s">
-        <v>658</v>
+        <v>612</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>654</v>
+        <v>608</v>
       </c>
       <c r="B160" t="s">
-        <v>659</v>
+        <v>613</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>660</v>
+        <v>614</v>
       </c>
       <c r="B161" t="s">
-        <v>661</v>
+        <v>615</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>660</v>
+        <v>614</v>
       </c>
       <c r="B162" t="s">
-        <v>662</v>
+        <v>616</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>663</v>
+        <v>617</v>
       </c>
       <c r="B163" t="s">
-        <v>664</v>
+        <v>618</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>663</v>
+        <v>617</v>
       </c>
       <c r="B164" t="s">
-        <v>665</v>
+        <v>619</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>663</v>
+        <v>617</v>
       </c>
       <c r="B165" t="s">
-        <v>666</v>
+        <v>620</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>667</v>
+        <v>621</v>
       </c>
       <c r="B166" t="s">
-        <v>668</v>
+        <v>622</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>667</v>
+        <v>621</v>
       </c>
       <c r="B167" t="s">
-        <v>669</v>
+        <v>623</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>667</v>
+        <v>621</v>
       </c>
       <c r="B168" t="s">
-        <v>670</v>
+        <v>624</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>671</v>
+        <v>625</v>
       </c>
       <c r="B169" t="s">
-        <v>672</v>
+        <v>626</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>671</v>
+        <v>625</v>
       </c>
       <c r="B170" t="s">
-        <v>673</v>
+        <v>627</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>671</v>
+        <v>625</v>
       </c>
       <c r="B171" t="s">
-        <v>674</v>
+        <v>628</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>675</v>
+        <v>629</v>
       </c>
       <c r="B172" t="s">
-        <v>676</v>
+        <v>630</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>677</v>
+        <v>631</v>
       </c>
       <c r="B173" t="s">
-        <v>678</v>
+        <v>632</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>677</v>
+        <v>631</v>
       </c>
       <c r="B174" t="s">
-        <v>679</v>
+        <v>633</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>677</v>
+        <v>631</v>
       </c>
       <c r="B175" t="s">
-        <v>680</v>
+        <v>634</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>677</v>
+        <v>631</v>
       </c>
       <c r="B176" t="s">
-        <v>681</v>
+        <v>635</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>677</v>
+        <v>631</v>
       </c>
       <c r="B177" t="s">
-        <v>682</v>
+        <v>636</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>677</v>
+        <v>631</v>
       </c>
       <c r="B178" t="s">
-        <v>683</v>
+        <v>637</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>677</v>
+        <v>631</v>
       </c>
       <c r="B179" t="s">
-        <v>684</v>
+        <v>638</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>677</v>
+        <v>631</v>
       </c>
       <c r="B180" t="s">
-        <v>685</v>
+        <v>639</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>677</v>
+        <v>631</v>
       </c>
       <c r="B181" t="s">
-        <v>686</v>
+        <v>640</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>687</v>
+        <v>641</v>
       </c>
       <c r="B182" t="s">
-        <v>688</v>
+        <v>642</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>687</v>
+        <v>641</v>
       </c>
       <c r="B183" t="s">
-        <v>689</v>
+        <v>643</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>687</v>
+        <v>641</v>
       </c>
       <c r="B184" t="s">
-        <v>690</v>
+        <v>644</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>687</v>
+        <v>641</v>
       </c>
       <c r="B185" t="s">
-        <v>691</v>
+        <v>645</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>687</v>
+        <v>641</v>
       </c>
       <c r="B186" t="s">
-        <v>692</v>
+        <v>646</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>687</v>
+        <v>641</v>
       </c>
       <c r="B187" t="s">
-        <v>693</v>
+        <v>647</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>694</v>
+        <v>648</v>
       </c>
       <c r="B188" t="s">
-        <v>695</v>
+        <v>649</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>696</v>
+        <v>650</v>
       </c>
       <c r="B189" t="s">
-        <v>697</v>
+        <v>651</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>696</v>
+        <v>650</v>
       </c>
       <c r="B190" t="s">
-        <v>698</v>
+        <v>652</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>696</v>
+        <v>650</v>
       </c>
       <c r="B191" t="s">
-        <v>699</v>
+        <v>653</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>700</v>
+        <v>654</v>
       </c>
       <c r="B192" t="s">
-        <v>701</v>
+        <v>655</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>700</v>
+        <v>654</v>
       </c>
       <c r="B193" t="s">
-        <v>702</v>
+        <v>656</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>700</v>
+        <v>654</v>
       </c>
       <c r="B194" t="s">
-        <v>703</v>
+        <v>657</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>700</v>
+        <v>654</v>
       </c>
       <c r="B195" t="s">
-        <v>704</v>
+        <v>658</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>705</v>
+        <v>659</v>
       </c>
       <c r="B196" t="s">
-        <v>706</v>
+        <v>660</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>707</v>
+        <v>661</v>
       </c>
       <c r="B197" t="s">
-        <v>708</v>
+        <v>662</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>709</v>
+        <v>663</v>
       </c>
       <c r="B198" t="s">
-        <v>710</v>
+        <v>664</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>711</v>
+        <v>665</v>
       </c>
       <c r="B199" t="s">
-        <v>712</v>
+        <v>666</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>713</v>
+        <v>667</v>
       </c>
       <c r="B200" t="s">
-        <v>714</v>
+        <v>668</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>713</v>
+        <v>667</v>
       </c>
       <c r="B201" t="s">
-        <v>715</v>
+        <v>669</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>713</v>
+        <v>667</v>
       </c>
       <c r="B202" t="s">
-        <v>716</v>
+        <v>670</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>717</v>
+        <v>671</v>
       </c>
       <c r="B203" t="s">
-        <v>718</v>
+        <v>672</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>717</v>
+        <v>671</v>
       </c>
       <c r="B204" t="s">
-        <v>719</v>
+        <v>673</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>717</v>
+        <v>671</v>
       </c>
       <c r="B205" t="s">
-        <v>720</v>
+        <v>674</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>717</v>
+        <v>671</v>
       </c>
       <c r="B206" t="s">
-        <v>721</v>
+        <v>675</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>717</v>
+        <v>671</v>
       </c>
       <c r="B207" t="s">
-        <v>722</v>
+        <v>676</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>723</v>
+        <v>677</v>
       </c>
       <c r="B208" t="s">
-        <v>724</v>
+        <v>678</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>723</v>
+        <v>677</v>
       </c>
       <c r="B209" t="s">
-        <v>725</v>
+        <v>679</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>726</v>
+        <v>680</v>
       </c>
       <c r="B210" t="s">
-        <v>727</v>
+        <v>681</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>726</v>
+        <v>680</v>
       </c>
       <c r="B211" t="s">
-        <v>728</v>
+        <v>682</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>726</v>
+        <v>680</v>
       </c>
       <c r="B212" t="s">
-        <v>729</v>
+        <v>683</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>730</v>
+        <v>684</v>
       </c>
       <c r="B213" t="s">
-        <v>731</v>
+        <v>685</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>730</v>
+        <v>684</v>
       </c>
       <c r="B214" t="s">
-        <v>732</v>
+        <v>686</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>730</v>
+        <v>684</v>
       </c>
       <c r="B215" t="s">
-        <v>733</v>
+        <v>687</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>734</v>
+        <v>688</v>
       </c>
       <c r="B216" t="s">
-        <v>735</v>
+        <v>689</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>736</v>
+        <v>690</v>
       </c>
       <c r="B217" t="s">
-        <v>737</v>
+        <v>691</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>736</v>
+        <v>690</v>
       </c>
       <c r="B218" t="s">
-        <v>738</v>
+        <v>692</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>739</v>
+        <v>693</v>
       </c>
       <c r="B219" t="s">
-        <v>740</v>
+        <v>694</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>741</v>
+        <v>695</v>
       </c>
       <c r="B220" t="s">
-        <v>742</v>
+        <v>696</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>743</v>
+        <v>697</v>
       </c>
       <c r="B221" t="s">
-        <v>744</v>
+        <v>698</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>743</v>
+        <v>697</v>
       </c>
       <c r="B222" t="s">
-        <v>745</v>
+        <v>699</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>746</v>
+        <v>700</v>
       </c>
       <c r="B223" t="s">
-        <v>747</v>
+        <v>701</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>748</v>
+        <v>702</v>
       </c>
       <c r="B224" t="s">
-        <v>749</v>
+        <v>703</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>750</v>
+        <v>704</v>
       </c>
       <c r="B225" t="s">
-        <v>751</v>
+        <v>705</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>752</v>
+        <v>706</v>
       </c>
       <c r="B226" t="s">
-        <v>753</v>
+        <v>707</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>754</v>
+        <v>708</v>
       </c>
       <c r="B227" t="s">
-        <v>755</v>
+        <v>709</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>756</v>
+        <v>710</v>
       </c>
       <c r="B228" t="s">
-        <v>757</v>
+        <v>711</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>756</v>
+        <v>710</v>
       </c>
       <c r="B229" t="s">
-        <v>758</v>
+        <v>712</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>759</v>
+        <v>713</v>
       </c>
       <c r="B230" t="s">
-        <v>760</v>
+        <v>714</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>759</v>
+        <v>713</v>
       </c>
       <c r="B231" t="s">
-        <v>761</v>
+        <v>715</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>759</v>
+        <v>713</v>
       </c>
       <c r="B232" t="s">
-        <v>762</v>
+        <v>716</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>759</v>
+        <v>713</v>
       </c>
       <c r="B233" t="s">
-        <v>763</v>
+        <v>717</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>759</v>
+        <v>713</v>
       </c>
       <c r="B234" t="s">
-        <v>764</v>
+        <v>718</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>765</v>
+        <v>719</v>
       </c>
       <c r="B235" t="s">
-        <v>766</v>
+        <v>720</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>767</v>
+        <v>721</v>
       </c>
       <c r="B236" t="s">
-        <v>353</v>
+        <v>307</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>768</v>
+        <v>722</v>
       </c>
       <c r="B237" t="s">
-        <v>769</v>
+        <v>723</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>770</v>
+        <v>724</v>
       </c>
       <c r="B238" t="s">
-        <v>351</v>
+        <v>306</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>771</v>
+        <v>725</v>
       </c>
       <c r="B239" t="s">
-        <v>772</v>
+        <v>726</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>342</v>
+        <v>300</v>
       </c>
       <c r="B240" t="s">
-        <v>363</v>
+        <v>317</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>362</v>
+        <v>316</v>
       </c>
       <c r="B241" t="s">
-        <v>773</v>
+        <v>727</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>774</v>
+        <v>728</v>
       </c>
       <c r="B242" t="s">
-        <v>775</v>
+        <v>729</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>776</v>
+        <v>730</v>
       </c>
       <c r="B243" t="s">
-        <v>775</v>
+        <v>729</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>777</v>
+        <v>731</v>
       </c>
       <c r="B244" t="s">
-        <v>365</v>
+        <v>319</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>366</v>
+        <v>320</v>
       </c>
       <c r="B245" t="s">
-        <v>365</v>
+        <v>319</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>364</v>
+        <v>318</v>
       </c>
       <c r="B246" t="s">
-        <v>778</v>
+        <v>732</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>779</v>
+        <v>733</v>
       </c>
       <c r="B247" t="s">
-        <v>780</v>
+        <v>734</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>781</v>
+        <v>735</v>
       </c>
       <c r="B248" t="s">
-        <v>780</v>
+        <v>734</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>782</v>
+        <v>736</v>
       </c>
       <c r="B249" t="s">
-        <v>783</v>
+        <v>737</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>784</v>
+        <v>738</v>
       </c>
       <c r="B250" t="s">
-        <v>785</v>
+        <v>739</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>786</v>
+        <v>740</v>
       </c>
       <c r="B251" t="s">
-        <v>787</v>
+        <v>741</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>788</v>
+        <v>742</v>
       </c>
       <c r="B252" t="s">
-        <v>789</v>
+        <v>743</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>788</v>
+        <v>742</v>
       </c>
       <c r="B253" t="s">
-        <v>790</v>
+        <v>744</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>791</v>
+        <v>745</v>
       </c>
       <c r="B254" t="s">
-        <v>792</v>
+        <v>746</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>793</v>
+        <v>747</v>
       </c>
       <c r="B255" t="s">
-        <v>792</v>
+        <v>746</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>794</v>
+        <v>748</v>
       </c>
       <c r="B256" t="s">
-        <v>792</v>
+        <v>746</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>795</v>
+        <v>749</v>
       </c>
       <c r="B257" t="s">
-        <v>796</v>
+        <v>750</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>797</v>
+        <v>751</v>
       </c>
       <c r="B258" t="s">
-        <v>798</v>
+        <v>752</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>799</v>
+        <v>753</v>
       </c>
       <c r="B259" t="s">
-        <v>800</v>
+        <v>754</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>801</v>
+        <v>755</v>
       </c>
       <c r="B260" t="s">
-        <v>802</v>
+        <v>756</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>803</v>
+        <v>757</v>
       </c>
       <c r="B261" t="s">
-        <v>804</v>
+        <v>758</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>805</v>
+        <v>759</v>
       </c>
       <c r="B262" t="s">
-        <v>806</v>
+        <v>760</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>807</v>
+        <v>761</v>
       </c>
       <c r="B263" t="s">
-        <v>808</v>
+        <v>762</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>809</v>
+        <v>763</v>
       </c>
       <c r="B264" t="s">
-        <v>810</v>
+        <v>764</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>811</v>
+        <v>765</v>
       </c>
       <c r="B265" t="s">
-        <v>812</v>
+        <v>766</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>813</v>
+        <v>767</v>
       </c>
       <c r="B266" t="s">
-        <v>812</v>
+        <v>766</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>814</v>
+        <v>768</v>
       </c>
       <c r="B267" t="s">
-        <v>815</v>
+        <v>769</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>816</v>
+        <v>770</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>817</v>
+        <v>771</v>
       </c>
       <c r="B269" t="s">
-        <v>818</v>
+        <v>772</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>819</v>
+        <v>773</v>
       </c>
       <c r="B270" t="s">
-        <v>820</v>
+        <v>774</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>821</v>
+        <v>775</v>
       </c>
       <c r="B271" t="s">
-        <v>822</v>
+        <v>776</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>823</v>
+        <v>777</v>
       </c>
       <c r="B272" t="s">
-        <v>824</v>
+        <v>778</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>825</v>
+        <v>779</v>
       </c>
       <c r="B273" t="s">
-        <v>826</v>
+        <v>780</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>827</v>
+        <v>781</v>
       </c>
       <c r="B274" t="s">
-        <v>828</v>
+        <v>782</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>829</v>
+        <v>783</v>
       </c>
       <c r="B275" t="s">
-        <v>830</v>
+        <v>784</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>831</v>
+        <v>785</v>
       </c>
       <c r="B276" t="s">
-        <v>832</v>
+        <v>786</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>833</v>
+        <v>787</v>
       </c>
       <c r="B277" t="s">
-        <v>834</v>
+        <v>788</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>835</v>
+        <v>789</v>
       </c>
       <c r="B278" t="s">
-        <v>836</v>
+        <v>790</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>837</v>
+        <v>791</v>
       </c>
       <c r="B279" t="s">
-        <v>836</v>
+        <v>790</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>838</v>
+        <v>792</v>
       </c>
       <c r="B280" t="s">
-        <v>836</v>
+        <v>790</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>839</v>
+        <v>793</v>
       </c>
       <c r="B281" t="s">
-        <v>836</v>
+        <v>790</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>840</v>
+        <v>794</v>
       </c>
       <c r="B282" t="s">
-        <v>836</v>
+        <v>790</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>841</v>
+        <v>795</v>
       </c>
       <c r="B283" t="s">
-        <v>842</v>
+        <v>796</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>843</v>
+        <v>797</v>
       </c>
       <c r="B284" t="s">
-        <v>844</v>
+        <v>798</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>843</v>
+        <v>797</v>
       </c>
       <c r="B285" t="s">
-        <v>845</v>
+        <v>799</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>846</v>
+        <v>800</v>
       </c>
       <c r="B286" t="s">
-        <v>847</v>
+        <v>801</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>846</v>
+        <v>800</v>
       </c>
       <c r="B287" t="s">
-        <v>848</v>
+        <v>802</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>846</v>
+        <v>800</v>
       </c>
       <c r="B288" t="s">
-        <v>849</v>
+        <v>803</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>850</v>
+        <v>804</v>
       </c>
       <c r="B289" t="s">
-        <v>851</v>
+        <v>805</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>850</v>
+        <v>804</v>
       </c>
       <c r="B290" t="s">
-        <v>852</v>
+        <v>806</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>850</v>
+        <v>804</v>
       </c>
       <c r="B291" t="s">
-        <v>853</v>
+        <v>807</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>854</v>
+        <v>808</v>
       </c>
       <c r="B292" t="s">
-        <v>855</v>
+        <v>809</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>854</v>
+        <v>808</v>
       </c>
       <c r="B293" t="s">
-        <v>856</v>
+        <v>810</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>857</v>
+        <v>811</v>
       </c>
       <c r="B294" t="s">
-        <v>858</v>
+        <v>812</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>857</v>
+        <v>811</v>
       </c>
       <c r="B295" t="s">
-        <v>859</v>
+        <v>813</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>857</v>
+        <v>811</v>
       </c>
       <c r="B296" t="s">
-        <v>860</v>
+        <v>814</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>861</v>
+        <v>815</v>
       </c>
       <c r="B297" t="s">
-        <v>862</v>
+        <v>816</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>861</v>
+        <v>815</v>
       </c>
       <c r="B298" t="s">
-        <v>863</v>
+        <v>817</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>861</v>
+        <v>815</v>
       </c>
       <c r="B299" t="s">
-        <v>864</v>
+        <v>818</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>861</v>
+        <v>815</v>
       </c>
       <c r="B300" t="s">
-        <v>865</v>
+        <v>819</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>861</v>
+        <v>815</v>
       </c>
       <c r="B301" t="s">
-        <v>866</v>
+        <v>820</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>867</v>
+        <v>821</v>
       </c>
       <c r="B302" t="s">
-        <v>868</v>
+        <v>822</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>869</v>
+        <v>823</v>
       </c>
       <c r="B303" t="s">
-        <v>870</v>
+        <v>824</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>871</v>
+        <v>825</v>
       </c>
       <c r="B304" t="s">
-        <v>872</v>
+        <v>826</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>873</v>
+        <v>827</v>
       </c>
       <c r="B305" t="s">
-        <v>874</v>
+        <v>828</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>875</v>
+        <v>829</v>
       </c>
       <c r="B306" t="s">
-        <v>876</v>
+        <v>830</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>877</v>
+        <v>831</v>
       </c>
       <c r="B307" t="s">
-        <v>878</v>
+        <v>832</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>879</v>
+        <v>833</v>
       </c>
       <c r="B308" t="s">
-        <v>878</v>
+        <v>832</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>880</v>
+        <v>834</v>
       </c>
       <c r="B309" t="s">
-        <v>878</v>
+        <v>832</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>881</v>
+        <v>835</v>
       </c>
       <c r="B310" t="s">
-        <v>882</v>
+        <v>836</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>883</v>
+        <v>837</v>
       </c>
       <c r="B311" t="s">
-        <v>884</v>
+        <v>838</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>885</v>
+        <v>839</v>
       </c>
       <c r="B312" t="s">
-        <v>886</v>
+        <v>840</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>887</v>
+        <v>841</v>
       </c>
       <c r="B313" t="s">
-        <v>888</v>
+        <v>842</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>889</v>
+        <v>843</v>
       </c>
       <c r="B314" t="s">
-        <v>890</v>
+        <v>844</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>891</v>
+        <v>845</v>
       </c>
       <c r="B315" t="s">
-        <v>892</v>
+        <v>846</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>893</v>
+        <v>847</v>
       </c>
       <c r="B316" t="s">
-        <v>894</v>
+        <v>848</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>895</v>
+        <v>849</v>
       </c>
       <c r="B317" t="s">
-        <v>896</v>
+        <v>850</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>897</v>
+        <v>851</v>
       </c>
       <c r="B318" t="s">
-        <v>898</v>
+        <v>852</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>899</v>
+        <v>853</v>
       </c>
       <c r="B319" t="s">
-        <v>900</v>
+        <v>854</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>901</v>
+        <v>855</v>
       </c>
       <c r="B320" t="s">
-        <v>902</v>
+        <v>856</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>903</v>
+        <v>857</v>
       </c>
       <c r="B321" t="s">
-        <v>904</v>
+        <v>858</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>905</v>
+        <v>859</v>
       </c>
       <c r="B322" t="s">
-        <v>906</v>
+        <v>860</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>907</v>
+        <v>861</v>
       </c>
       <c r="B323" t="s">
-        <v>908</v>
+        <v>862</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>909</v>
+        <v>863</v>
       </c>
       <c r="B324" t="s">
-        <v>910</v>
+        <v>864</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>911</v>
+        <v>865</v>
       </c>
       <c r="B325" t="s">
-        <v>912</v>
+        <v>866</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>913</v>
+        <v>867</v>
       </c>
       <c r="B326" t="s">
-        <v>914</v>
+        <v>868</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>915</v>
+        <v>869</v>
       </c>
       <c r="B327" t="s">
-        <v>916</v>
+        <v>870</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>917</v>
+        <v>871</v>
       </c>
       <c r="B328" t="s">
-        <v>918</v>
+        <v>872</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>919</v>
+        <v>873</v>
       </c>
       <c r="B329" t="s">
-        <v>920</v>
+        <v>874</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>921</v>
+        <v>875</v>
       </c>
       <c r="B330" t="s">
-        <v>922</v>
+        <v>876</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>923</v>
+        <v>877</v>
       </c>
       <c r="B331" t="s">
-        <v>924</v>
+        <v>878</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>925</v>
+        <v>879</v>
       </c>
       <c r="B332" t="s">
-        <v>926</v>
+        <v>880</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>927</v>
+        <v>881</v>
       </c>
       <c r="B333" t="s">
-        <v>928</v>
+        <v>882</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>927</v>
+        <v>881</v>
       </c>
       <c r="B334" t="s">
-        <v>929</v>
+        <v>883</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>930</v>
+        <v>884</v>
       </c>
       <c r="B335" t="s">
-        <v>931</v>
+        <v>885</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>932</v>
+        <v>886</v>
       </c>
       <c r="B336" t="s">
-        <v>933</v>
+        <v>887</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>934</v>
+        <v>888</v>
       </c>
       <c r="B337" t="s">
-        <v>935</v>
+        <v>889</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>934</v>
+        <v>888</v>
       </c>
       <c r="B338" t="s">
-        <v>936</v>
+        <v>890</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>934</v>
+        <v>888</v>
       </c>
       <c r="B339" t="s">
-        <v>937</v>
+        <v>891</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>938</v>
+        <v>892</v>
       </c>
       <c r="B340" t="s">
-        <v>939</v>
+        <v>893</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>938</v>
+        <v>892</v>
       </c>
       <c r="B341" t="s">
-        <v>940</v>
+        <v>894</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>941</v>
+        <v>895</v>
       </c>
       <c r="B342" t="s">
-        <v>942</v>
+        <v>896</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>943</v>
+        <v>897</v>
       </c>
       <c r="B343" t="s">
-        <v>944</v>
+        <v>898</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>945</v>
+        <v>899</v>
       </c>
       <c r="B344" t="s">
-        <v>946</v>
+        <v>900</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>947</v>
+        <v>901</v>
       </c>
       <c r="B345" t="s">
-        <v>948</v>
+        <v>902</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>947</v>
+        <v>901</v>
       </c>
       <c r="B346" t="s">
-        <v>949</v>
+        <v>903</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>947</v>
+        <v>901</v>
       </c>
       <c r="B347" t="s">
-        <v>950</v>
+        <v>904</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>951</v>
+        <v>905</v>
       </c>
       <c r="B348" t="s">
-        <v>952</v>
+        <v>906</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>951</v>
+        <v>905</v>
       </c>
       <c r="B349" t="s">
-        <v>953</v>
+        <v>907</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>951</v>
+        <v>905</v>
       </c>
       <c r="B350" t="s">
-        <v>954</v>
+        <v>908</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>955</v>
+        <v>909</v>
       </c>
       <c r="B351" t="s">
-        <v>956</v>
+        <v>910</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>955</v>
+        <v>909</v>
       </c>
       <c r="B352" t="s">
-        <v>957</v>
+        <v>911</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>958</v>
+        <v>912</v>
       </c>
       <c r="B353" t="s">
-        <v>959</v>
+        <v>913</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>960</v>
+        <v>914</v>
       </c>
       <c r="B354" t="s">
-        <v>961</v>
+        <v>915</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>962</v>
+        <v>916</v>
       </c>
       <c r="B355" t="s">
-        <v>963</v>
+        <v>917</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>962</v>
+        <v>916</v>
       </c>
       <c r="B356" t="s">
-        <v>964</v>
+        <v>918</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>965</v>
+        <v>919</v>
       </c>
       <c r="B357" t="s">
-        <v>966</v>
+        <v>920</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>965</v>
+        <v>919</v>
       </c>
       <c r="B358" t="s">
-        <v>967</v>
+        <v>921</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>968</v>
+        <v>922</v>
       </c>
       <c r="B359" t="s">
-        <v>969</v>
+        <v>923</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>968</v>
+        <v>922</v>
       </c>
       <c r="B360" t="s">
-        <v>970</v>
+        <v>924</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>971</v>
+        <v>925</v>
       </c>
       <c r="B361" t="s">
-        <v>972</v>
+        <v>926</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>971</v>
+        <v>925</v>
       </c>
       <c r="B362" t="s">
-        <v>973</v>
+        <v>927</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>974</v>
+        <v>928</v>
       </c>
       <c r="B363" t="s">
-        <v>975</v>
+        <v>929</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>976</v>
+        <v>930</v>
       </c>
       <c r="B364" t="s">
-        <v>977</v>
+        <v>931</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>976</v>
+        <v>930</v>
       </c>
       <c r="B365" t="s">
-        <v>978</v>
+        <v>932</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>979</v>
+        <v>933</v>
       </c>
       <c r="B366" t="s">
-        <v>980</v>
+        <v>934</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>979</v>
+        <v>933</v>
       </c>
       <c r="B367" t="s">
-        <v>981</v>
+        <v>935</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>982</v>
+        <v>936</v>
       </c>
       <c r="B368" t="s">
-        <v>983</v>
+        <v>937</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>982</v>
+        <v>936</v>
       </c>
       <c r="B369" t="s">
-        <v>984</v>
+        <v>938</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>985</v>
+        <v>939</v>
       </c>
       <c r="B370" t="s">
-        <v>986</v>
+        <v>940</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>987</v>
+        <v>941</v>
       </c>
       <c r="B371" t="s">
-        <v>988</v>
+        <v>942</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>989</v>
+        <v>943</v>
       </c>
       <c r="B372" t="s">
-        <v>990</v>
+        <v>944</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>989</v>
+        <v>943</v>
       </c>
       <c r="B373" t="s">
-        <v>991</v>
+        <v>945</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>992</v>
+        <v>946</v>
       </c>
       <c r="B374" t="s">
-        <v>993</v>
+        <v>947</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>992</v>
+        <v>946</v>
       </c>
       <c r="B375" t="s">
-        <v>994</v>
+        <v>948</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>992</v>
+        <v>946</v>
       </c>
       <c r="B376" t="s">
-        <v>995</v>
+        <v>949</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>992</v>
+        <v>946</v>
       </c>
       <c r="B377" t="s">
-        <v>996</v>
+        <v>950</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>997</v>
+        <v>951</v>
       </c>
       <c r="B378" t="s">
-        <v>998</v>
+        <v>952</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>997</v>
+        <v>951</v>
       </c>
       <c r="B379" t="s">
-        <v>999</v>
+        <v>953</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>1000</v>
+        <v>954</v>
       </c>
       <c r="B380" t="s">
-        <v>1001</v>
+        <v>955</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>1002</v>
+        <v>956</v>
       </c>
       <c r="B381" t="s">
-        <v>1003</v>
+        <v>957</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>1004</v>
+        <v>958</v>
       </c>
       <c r="B382" t="s">
-        <v>1005</v>
+        <v>959</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>1006</v>
+        <v>960</v>
       </c>
       <c r="B383" t="s">
-        <v>1007</v>
+        <v>961</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>1008</v>
+        <v>962</v>
       </c>
       <c r="B384" t="s">
-        <v>1009</v>
+        <v>963</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>1010</v>
+        <v>964</v>
       </c>
       <c r="B385" t="s">
-        <v>1009</v>
+        <v>963</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>1011</v>
+        <v>965</v>
       </c>
       <c r="B386" t="s">
-        <v>1012</v>
+        <v>966</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>1013</v>
+        <v>967</v>
       </c>
       <c r="B387" t="s">
-        <v>1014</v>
+        <v>968</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>1015</v>
+        <v>969</v>
       </c>
       <c r="B388" t="s">
-        <v>1016</v>
+        <v>970</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>1017</v>
+        <v>971</v>
       </c>
       <c r="B389" t="s">
-        <v>1018</v>
+        <v>972</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>1019</v>
+        <v>973</v>
       </c>
       <c r="B390" t="s">
-        <v>1018</v>
+        <v>972</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>1020</v>
+        <v>974</v>
       </c>
       <c r="B391" t="s">
-        <v>1021</v>
+        <v>975</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>1022</v>
+        <v>976</v>
       </c>
       <c r="B392" t="s">
-        <v>1021</v>
+        <v>975</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>339</v>
+        <v>298</v>
       </c>
       <c r="B393" t="s">
-        <v>340</v>
+        <v>299</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>1023</v>
+        <v>977</v>
       </c>
       <c r="B394" t="s">
-        <v>1024</v>
+        <v>978</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>1025</v>
+        <v>979</v>
       </c>
       <c r="B395" t="s">
-        <v>1024</v>
+        <v>978</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>1026</v>
+        <v>980</v>
       </c>
       <c r="B396" t="s">
-        <v>1027</v>
+        <v>981</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>1028</v>
+        <v>982</v>
       </c>
       <c r="B397" t="s">
-        <v>1027</v>
+        <v>981</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>1029</v>
+        <v>983</v>
       </c>
       <c r="B398" t="s">
-        <v>1030</v>
+        <v>984</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>1031</v>
+        <v>985</v>
       </c>
       <c r="B399" t="s">
-        <v>1030</v>
+        <v>984</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>1032</v>
+        <v>986</v>
       </c>
       <c r="B400" t="s">
-        <v>1033</v>
+        <v>987</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>1034</v>
+        <v>988</v>
       </c>
       <c r="B401" t="s">
-        <v>1035</v>
+        <v>989</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>1036</v>
+        <v>990</v>
       </c>
       <c r="B402" t="s">
-        <v>1037</v>
+        <v>991</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>1038</v>
+        <v>992</v>
       </c>
       <c r="B403" t="s">
-        <v>1037</v>
+        <v>991</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>1039</v>
+        <v>993</v>
       </c>
       <c r="B404" t="s">
-        <v>1040</v>
+        <v>994</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>1041</v>
+        <v>995</v>
       </c>
       <c r="B405" t="s">
-        <v>1042</v>
+        <v>996</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>1043</v>
+        <v>997</v>
       </c>
       <c r="B406" t="s">
-        <v>1044</v>
+        <v>998</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>1045</v>
+        <v>999</v>
       </c>
       <c r="B407" t="s">
-        <v>1044</v>
+        <v>998</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>1046</v>
+        <v>1000</v>
       </c>
       <c r="B408" t="s">
-        <v>1047</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>1048</v>
+        <v>1002</v>
       </c>
       <c r="B409" t="s">
-        <v>1047</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>1049</v>
+        <v>1003</v>
       </c>
       <c r="B410" t="s">
-        <v>1050</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>1051</v>
+        <v>1005</v>
       </c>
       <c r="B411" t="s">
-        <v>1052</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>1053</v>
+        <v>1007</v>
       </c>
       <c r="B412" t="s">
-        <v>1054</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>1055</v>
+        <v>1009</v>
       </c>
       <c r="B413" t="s">
-        <v>1056</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>1057</v>
+        <v>1011</v>
       </c>
       <c r="B414" t="s">
-        <v>1058</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>1059</v>
+        <v>1013</v>
       </c>
       <c r="B415" t="s">
-        <v>1060</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>1059</v>
+        <v>1013</v>
       </c>
       <c r="B416" t="s">
-        <v>1061</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>1059</v>
+        <v>1013</v>
       </c>
       <c r="B417" t="s">
-        <v>1062</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>1063</v>
+        <v>1017</v>
       </c>
       <c r="B418" t="s">
-        <v>1064</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>1063</v>
+        <v>1017</v>
       </c>
       <c r="B419" t="s">
-        <v>1065</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>1066</v>
+        <v>1020</v>
       </c>
       <c r="B420" t="s">
-        <v>1067</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>1068</v>
+        <v>1022</v>
       </c>
       <c r="B421" t="s">
-        <v>1069</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>1068</v>
+        <v>1022</v>
       </c>
       <c r="B422" t="s">
-        <v>1070</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>1068</v>
+        <v>1022</v>
       </c>
       <c r="B423" t="s">
-        <v>1071</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>1072</v>
+        <v>1026</v>
       </c>
       <c r="B424" t="s">
-        <v>1073</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>1072</v>
+        <v>1026</v>
       </c>
       <c r="B425" t="s">
-        <v>1074</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>1075</v>
+        <v>1029</v>
       </c>
       <c r="B426" t="s">
-        <v>1076</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>1075</v>
+        <v>1029</v>
       </c>
       <c r="B427" t="s">
-        <v>1077</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>1078</v>
+        <v>1032</v>
       </c>
       <c r="B428" t="s">
-        <v>1079</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>1078</v>
+        <v>1032</v>
       </c>
       <c r="B429" t="s">
-        <v>1080</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>1081</v>
+        <v>1035</v>
       </c>
       <c r="B430" t="s">
-        <v>1082</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>1081</v>
+        <v>1035</v>
       </c>
       <c r="B431" t="s">
-        <v>1083</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>1084</v>
+        <v>1038</v>
       </c>
       <c r="B432" t="s">
-        <v>1085</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>1084</v>
+        <v>1038</v>
       </c>
       <c r="B433" t="s">
-        <v>1086</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>1084</v>
+        <v>1038</v>
       </c>
       <c r="B434" t="s">
-        <v>1087</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>1088</v>
+        <v>1042</v>
       </c>
       <c r="B435" t="s">
-        <v>1089</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>1088</v>
+        <v>1042</v>
       </c>
       <c r="B436" t="s">
-        <v>1090</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>1091</v>
+        <v>1045</v>
       </c>
       <c r="B437" t="s">
-        <v>1092</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>1093</v>
+        <v>1047</v>
       </c>
       <c r="B438" t="s">
-        <v>1094</v>
+        <v>1048</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B438"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15978,16 +14821,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
-        <v>1107</v>
+        <v>1061</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>1106</v>
+        <v>1060</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1105</v>
+        <v>1059</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1104</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -15995,13 +14838,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>1103</v>
+        <v>1057</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>1099</v>
+        <v>1053</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>359</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -16009,13 +14852,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1102</v>
+        <v>1056</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>1099</v>
+        <v>1053</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>361</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -16023,13 +14866,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1103</v>
+        <v>1057</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>1098</v>
+        <v>1052</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>359</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -16037,13 +14880,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>1102</v>
+        <v>1056</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>1098</v>
+        <v>1052</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>361</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -16051,13 +14894,13 @@
         <v>3</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>1103</v>
+        <v>1057</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>1100</v>
+        <v>1054</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>359</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -16065,13 +14908,13 @@
         <v>3</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1102</v>
+        <v>1056</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>1100</v>
+        <v>1054</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>361</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -16079,13 +14922,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1103</v>
+        <v>1057</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>1095</v>
+        <v>1049</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>359</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -16093,13 +14936,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>1102</v>
+        <v>1056</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>1095</v>
+        <v>1049</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>361</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -16107,13 +14950,13 @@
         <v>5</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>348</v>
+        <v>305</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>1099</v>
+        <v>1053</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>1101</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -16121,13 +14964,13 @@
         <v>6</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>348</v>
+        <v>305</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>1098</v>
+        <v>1052</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>1101</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -16135,13 +14978,13 @@
         <v>7</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>348</v>
+        <v>305</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>1095</v>
+        <v>1049</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>1101</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -16149,13 +14992,13 @@
         <v>8</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>342</v>
+        <v>300</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>1099</v>
+        <v>1053</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>363</v>
+        <v>317</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -16163,13 +15006,13 @@
         <v>9</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>342</v>
+        <v>300</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>1100</v>
+        <v>1054</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>363</v>
+        <v>317</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -16177,13 +15020,13 @@
         <v>10</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>342</v>
+        <v>300</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>1098</v>
+        <v>1052</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>363</v>
+        <v>317</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -16191,13 +15034,13 @@
         <v>11</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>342</v>
+        <v>300</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>1095</v>
+        <v>1049</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>363</v>
+        <v>317</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -16205,13 +15048,13 @@
         <v>12</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>1097</v>
+        <v>1051</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>1099</v>
+        <v>1053</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>355</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -16219,13 +15062,13 @@
         <v>12</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>1096</v>
+        <v>1050</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>1099</v>
+        <v>1053</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>357</v>
+        <v>311</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -16233,13 +15076,13 @@
         <v>13</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>1097</v>
+        <v>1051</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>1098</v>
+        <v>1052</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>355</v>
+        <v>309</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -16247,13 +15090,13 @@
         <v>13</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>1096</v>
+        <v>1050</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>1098</v>
+        <v>1052</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>357</v>
+        <v>311</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -16261,13 +15104,13 @@
         <v>14</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>1097</v>
+        <v>1051</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>1095</v>
+        <v>1049</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>355</v>
+        <v>309</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -16275,13 +15118,13 @@
         <v>14</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>1096</v>
+        <v>1050</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>1095</v>
+        <v>1049</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>357</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>

--- a/품목마스터/마감작업자별 생산가능품목_코드목록_v2.xlsx
+++ b/품목마스터/마감작업자별 생산가능품목_코드목록_v2.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16440" windowHeight="8655" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16440" windowHeight="8655" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2564" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2576" uniqueCount="1074">
   <si>
     <t>마감작업자 생산가능품목</t>
   </si>
@@ -3241,6 +3241,29 @@
   </si>
   <si>
     <t>폴디</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAXXZ003</t>
+  </si>
+  <si>
+    <t>L735</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[저품질] 사티 1인 (우)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[저품질] 사티 1인 (좌)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAXXZ002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L730</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3369,7 +3392,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3407,6 +3430,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -14809,13 +14835,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="13"/>
     <col min="2" max="2" width="18.125" style="13" customWidth="1"/>
     <col min="3" max="3" width="12" style="13" customWidth="1"/>
-    <col min="4" max="4" width="25.375" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.625" style="13" customWidth="1"/>
     <col min="5" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
@@ -14861,43 +14887,71 @@
         <v>315</v>
       </c>
     </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="13">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>313</v>
+      </c>
+    </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="13">
         <v>2</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>1052</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="13" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
+        <v>3</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>1056</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>1052</v>
-      </c>
-      <c r="D6" s="13" t="s">
+      <c r="C7" s="13" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>1057</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>313</v>
@@ -14905,226 +14959,254 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>1056</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>315</v>
       </c>
     </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
+        <v>5</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>1055</v>
+      </c>
+    </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1057</v>
+        <v>305</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>313</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>1056</v>
+        <v>305</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>1049</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>315</v>
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
+        <v>8</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>1055</v>
+        <v>317</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>1052</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>1055</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>1049</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>1055</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>300</v>
+        <v>1051</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>1053</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>300</v>
+        <v>1050</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>300</v>
+        <v>1051</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>1052</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>300</v>
+        <v>1050</v>
       </c>
       <c r="C20" s="13" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>1049</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>317</v>
+      <c r="D21" s="13" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
-        <v>12</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>1050</v>
+        <v>15</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>1068</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>311</v>
+        <v>1069</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="13">
+        <v>15</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>1071</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="13">
-        <v>13</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>1051</v>
+        <v>16</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>1068</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>1052</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>309</v>
+        <v>1073</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>1070</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
-        <v>13</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>1050</v>
+        <v>16</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>1072</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>1052</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="13">
-        <v>14</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="13">
-        <v>14</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>1050</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>311</v>
+        <v>1073</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>1071</v>
       </c>
     </row>
   </sheetData>

--- a/품목마스터/마감작업자별 생산가능품목_코드목록_v2.xlsx
+++ b/품목마스터/마감작업자별 생산가능품목_코드목록_v2.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3649" uniqueCount="1072">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3638" uniqueCount="1072">
   <si>
     <t>NO</t>
   </si>
@@ -9705,9 +9705,7 @@
       <c r="H106" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="I106" s="10" t="s">
-        <v>46</v>
-      </c>
+      <c r="I106" s="11"/>
       <c r="J106" s="10" t="s">
         <v>46</v>
       </c>
@@ -9745,9 +9743,7 @@
       <c r="H107" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="I107" s="10" t="s">
-        <v>46</v>
-      </c>
+      <c r="I107" s="11"/>
       <c r="J107" s="10" t="s">
         <v>46</v>
       </c>
@@ -9785,9 +9781,7 @@
       <c r="H108" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="I108" s="10" t="s">
-        <v>46</v>
-      </c>
+      <c r="I108" s="11"/>
       <c r="J108" s="10" t="s">
         <v>46</v>
       </c>
@@ -9825,9 +9819,7 @@
       <c r="H109" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="I109" s="10" t="s">
-        <v>46</v>
-      </c>
+      <c r="I109" s="11"/>
       <c r="J109" s="10" t="s">
         <v>46</v>
       </c>
@@ -10122,27 +10114,13 @@
       <c r="E117" s="9" t="s">
         <v>1064</v>
       </c>
-      <c r="F117" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G117" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="I117" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J117" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="K117" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="L117" s="10" t="s">
-        <v>46</v>
-      </c>
+      <c r="F117" s="11"/>
+      <c r="G117" s="11"/>
+      <c r="H117" s="11"/>
+      <c r="I117" s="11"/>
+      <c r="J117" s="11"/>
+      <c r="K117" s="11"/>
+      <c r="L117" s="11"/>
       <c r="M117" s="10" t="s">
         <v>46</v>
       </c>

--- a/품목마스터/마감작업자별 생산가능품목_코드목록_v2.xlsx
+++ b/품목마스터/마감작업자별 생산가능품목_코드목록_v2.xlsx
@@ -24,12 +24,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'특정라인 지정'!$A$1:$B$438</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">품목군코드상세!$A$1:$N$127</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3638" uniqueCount="1072">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3644" uniqueCount="1074">
   <si>
     <t>NO</t>
   </si>
@@ -3259,6 +3259,14 @@
   </si>
   <si>
     <t>L730</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데스커</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSSCAY070</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3334,7 +3342,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -3372,13 +3380,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3420,6 +3439,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -5913,7 +5933,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N127"/>
+  <dimension ref="A1:N128"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" style="7" customWidth="1"/>
@@ -10409,6 +10429,29 @@
         <v>46</v>
       </c>
       <c r="N127" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A128" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B128" s="15">
+        <v>30</v>
+      </c>
+      <c r="C128" s="15" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D128" s="15" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E128" s="15" t="s">
+        <v>1072</v>
+      </c>
+      <c r="M128" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N128" s="10" t="s">
         <v>46</v>
       </c>
     </row>

--- a/품목마스터/마감작업자별 생산가능품목_코드목록_v2.xlsx
+++ b/품목마스터/마감작업자별 생산가능품목_코드목록_v2.xlsx
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">원본!$A$1:$N$127</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'특정라인 지정'!$A$1:$B$438</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'특정라인 지정'!$A$1:$B$436</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">품목군코드상세!$A$1:$N$127</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3644" uniqueCount="1074">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3646" uniqueCount="1071">
   <si>
     <t>NO</t>
   </si>
@@ -2327,15 +2327,6 @@
   </si>
   <si>
     <t>WDWW164957-R000</t>
-  </si>
-  <si>
-    <t>HCS8101N</t>
-  </si>
-  <si>
-    <t>볼케S(P가죽,전동)</t>
-  </si>
-  <si>
-    <t>볼케S(가죽,전동)</t>
   </si>
   <si>
     <t>OPFW005622-R000</t>
@@ -6956,7 +6947,9 @@
       <c r="E27" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="F27" s="11"/>
+      <c r="F27" s="10" t="s">
+        <v>46</v>
+      </c>
       <c r="G27" s="10" t="s">
         <v>46</v>
       </c>
@@ -6990,7 +6983,9 @@
       <c r="E28" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="F28" s="11"/>
+      <c r="F28" s="10" t="s">
+        <v>46</v>
+      </c>
       <c r="G28" s="10" t="s">
         <v>46</v>
       </c>
@@ -9583,7 +9578,9 @@
       <c r="F102" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="G102" s="11"/>
+      <c r="G102" s="10" t="s">
+        <v>46</v>
+      </c>
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
       <c r="J102" s="10" t="s">
@@ -9617,7 +9614,9 @@
       <c r="F103" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="G103" s="11"/>
+      <c r="G103" s="10" t="s">
+        <v>46</v>
+      </c>
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
       <c r="J103" s="10" t="s">
@@ -9651,7 +9650,9 @@
       <c r="F104" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="G104" s="11"/>
+      <c r="G104" s="10" t="s">
+        <v>46</v>
+      </c>
       <c r="H104" s="11"/>
       <c r="I104" s="11"/>
       <c r="J104" s="10" t="s">
@@ -9685,7 +9686,9 @@
       <c r="F105" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="G105" s="11"/>
+      <c r="G105" s="10" t="s">
+        <v>46</v>
+      </c>
       <c r="H105" s="11"/>
       <c r="I105" s="11"/>
       <c r="J105" s="10" t="s">
@@ -10129,10 +10132,10 @@
         <v>32</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="F117" s="11"/>
       <c r="G117" s="11"/>
@@ -10159,10 +10162,10 @@
         <v>34</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="F118" s="11"/>
       <c r="G118" s="11"/>
@@ -10190,7 +10193,7 @@
         <v>298</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="F119" s="11"/>
       <c r="G119" s="11"/>
@@ -10276,7 +10279,7 @@
         <v>303</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="F122" s="11"/>
       <c r="G122" s="11"/>
@@ -10440,13 +10443,13 @@
         <v>30</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="D128" s="15" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="E128" s="15" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="M128" s="10" t="s">
         <v>46</v>
@@ -10465,7 +10468,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B438"/>
+  <dimension ref="A1:B436"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -12610,82 +12613,82 @@
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>264</v>
+        <v>768</v>
       </c>
       <c r="B268" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B269" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B270" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B271" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B272" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B273" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B274" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B275" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B276" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
+        <v>786</v>
+      </c>
+      <c r="B277" t="s">
         <v>785</v>
-      </c>
-      <c r="B277" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
@@ -12693,31 +12696,31 @@
         <v>787</v>
       </c>
       <c r="B278" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B279" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B280" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
+        <v>790</v>
+      </c>
+      <c r="B281" t="s">
         <v>791</v>
-      </c>
-      <c r="B281" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.3">
@@ -12725,12 +12728,12 @@
         <v>792</v>
       </c>
       <c r="B282" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B283" t="s">
         <v>794</v>
@@ -12754,15 +12757,15 @@
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
+        <v>795</v>
+      </c>
+      <c r="B286" t="s">
         <v>798</v>
-      </c>
-      <c r="B286" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B287" t="s">
         <v>800</v>
@@ -12770,7 +12773,7 @@
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B288" t="s">
         <v>801</v>
@@ -12778,15 +12781,15 @@
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
+        <v>799</v>
+      </c>
+      <c r="B289" t="s">
         <v>802</v>
-      </c>
-      <c r="B289" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B290" t="s">
         <v>804</v>
@@ -12794,7 +12797,7 @@
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B291" t="s">
         <v>805</v>
@@ -12818,15 +12821,15 @@
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
+        <v>806</v>
+      </c>
+      <c r="B294" t="s">
         <v>809</v>
-      </c>
-      <c r="B294" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B295" t="s">
         <v>811</v>
@@ -12834,7 +12837,7 @@
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B296" t="s">
         <v>812</v>
@@ -12842,31 +12845,31 @@
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
+        <v>810</v>
+      </c>
+      <c r="B297" t="s">
         <v>813</v>
-      </c>
-      <c r="B297" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="B298" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="B299" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="B300" t="s">
         <v>817</v>
@@ -12874,50 +12877,50 @@
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="B301" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B302" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B303" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B304" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B305" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
+        <v>828</v>
+      </c>
+      <c r="B306" t="s">
         <v>827</v>
-      </c>
-      <c r="B306" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.3">
@@ -12925,15 +12928,15 @@
         <v>829</v>
       </c>
       <c r="B307" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
+        <v>830</v>
+      </c>
+      <c r="B308" t="s">
         <v>831</v>
-      </c>
-      <c r="B308" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.3">
@@ -12941,188 +12944,188 @@
         <v>832</v>
       </c>
       <c r="B309" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B310" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B311" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B312" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B313" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B314" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B315" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B316" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B317" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B318" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B319" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B320" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B321" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B322" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B323" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B324" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B325" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B326" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B327" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B328" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B329" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B330" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B331" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B332" t="s">
         <v>878</v>
@@ -13138,23 +13141,23 @@
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B334" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B335" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B336" t="s">
         <v>885</v>
@@ -13162,15 +13165,15 @@
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
+        <v>883</v>
+      </c>
+      <c r="B337" t="s">
         <v>886</v>
-      </c>
-      <c r="B337" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B338" t="s">
         <v>888</v>
@@ -13178,7 +13181,7 @@
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B339" t="s">
         <v>889</v>
@@ -13194,31 +13197,31 @@
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B341" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B342" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B343" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B344" t="s">
         <v>898</v>
@@ -13226,15 +13229,15 @@
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
+        <v>896</v>
+      </c>
+      <c r="B345" t="s">
         <v>899</v>
-      </c>
-      <c r="B345" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B346" t="s">
         <v>901</v>
@@ -13242,7 +13245,7 @@
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B347" t="s">
         <v>902</v>
@@ -13250,15 +13253,15 @@
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
+        <v>900</v>
+      </c>
+      <c r="B348" t="s">
         <v>903</v>
-      </c>
-      <c r="B348" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B349" t="s">
         <v>905</v>
@@ -13266,7 +13269,7 @@
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B350" t="s">
         <v>906</v>
@@ -13282,23 +13285,23 @@
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B352" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B353" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B354" t="s">
         <v>913</v>
@@ -13362,15 +13365,15 @@
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="B362" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B363" t="s">
         <v>927</v>
@@ -13418,23 +13421,23 @@
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B369" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B370" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B371" t="s">
         <v>940</v>
@@ -13458,23 +13461,23 @@
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
+        <v>941</v>
+      </c>
+      <c r="B374" t="s">
         <v>944</v>
-      </c>
-      <c r="B374" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="B375" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B376" t="s">
         <v>947</v>
@@ -13482,7 +13485,7 @@
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B377" t="s">
         <v>948</v>
@@ -13498,42 +13501,42 @@
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="B379" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B380" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B381" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B382" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
+        <v>959</v>
+      </c>
+      <c r="B383" t="s">
         <v>958</v>
-      </c>
-      <c r="B383" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.3">
@@ -13549,31 +13552,31 @@
         <v>962</v>
       </c>
       <c r="B385" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B386" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B387" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
+        <v>968</v>
+      </c>
+      <c r="B388" t="s">
         <v>967</v>
-      </c>
-      <c r="B388" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.3">
@@ -13594,15 +13597,15 @@
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>972</v>
+        <v>296</v>
       </c>
       <c r="B391" t="s">
-        <v>973</v>
+        <v>297</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B392" t="s">
         <v>973</v>
@@ -13610,10 +13613,10 @@
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>296</v>
+        <v>974</v>
       </c>
       <c r="B393" t="s">
-        <v>297</v>
+        <v>973</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.3">
@@ -13661,23 +13664,23 @@
         <v>983</v>
       </c>
       <c r="B399" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B400" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
+        <v>987</v>
+      </c>
+      <c r="B401" t="s">
         <v>986</v>
-      </c>
-      <c r="B401" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.3">
@@ -13693,23 +13696,23 @@
         <v>990</v>
       </c>
       <c r="B403" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B404" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
+        <v>994</v>
+      </c>
+      <c r="B405" t="s">
         <v>993</v>
-      </c>
-      <c r="B405" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.3">
@@ -13741,44 +13744,44 @@
         <v>1000</v>
       </c>
       <c r="B409" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B410" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B411" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B412" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B413" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B414" t="s">
         <v>1010</v>
@@ -13786,15 +13789,15 @@
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B415" t="s">
         <v>1011</v>
-      </c>
-      <c r="B415" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B416" t="s">
         <v>1013</v>
@@ -13802,7 +13805,7 @@
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B417" t="s">
         <v>1014</v>
@@ -13818,15 +13821,15 @@
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="B419" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B420" t="s">
         <v>1019</v>
@@ -13834,15 +13837,15 @@
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B421" t="s">
         <v>1020</v>
-      </c>
-      <c r="B421" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B422" t="s">
         <v>1022</v>
@@ -13850,7 +13853,7 @@
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B423" t="s">
         <v>1023</v>
@@ -13922,15 +13925,15 @@
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B432" t="s">
         <v>1036</v>
-      </c>
-      <c r="B432" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B433" t="s">
         <v>1038</v>
@@ -13938,7 +13941,7 @@
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B434" t="s">
         <v>1039</v>
@@ -13954,30 +13957,14 @@
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B436" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A437" t="s">
         <v>1043</v>
       </c>
-      <c r="B437" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A438" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B438" t="s">
-        <v>1046</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B438"/>
+  <autoFilter ref="A1:B436"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13997,16 +13984,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -14014,10 +14001,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>311</v>
@@ -14028,10 +14015,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>313</v>
@@ -14042,10 +14029,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>311</v>
@@ -14056,10 +14043,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>313</v>
@@ -14070,10 +14057,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>311</v>
@@ -14084,10 +14071,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>313</v>
@@ -14098,10 +14085,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>311</v>
@@ -14112,10 +14099,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>313</v>
@@ -14129,10 +14116,10 @@
         <v>303</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -14143,10 +14130,10 @@
         <v>303</v>
       </c>
       <c r="C11" s="12" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>1050</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -14157,10 +14144,10 @@
         <v>303</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -14171,7 +14158,7 @@
         <v>298</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>315</v>
@@ -14185,7 +14172,7 @@
         <v>298</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>315</v>
@@ -14199,7 +14186,7 @@
         <v>298</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>315</v>
@@ -14213,7 +14200,7 @@
         <v>298</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>315</v>
@@ -14224,10 +14211,10 @@
         <v>12</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>307</v>
@@ -14238,10 +14225,10 @@
         <v>12</v>
       </c>
       <c r="B18" s="12" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>1048</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>1051</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>309</v>
@@ -14252,10 +14239,10 @@
         <v>13</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>307</v>
@@ -14266,10 +14253,10 @@
         <v>13</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>309</v>
@@ -14280,10 +14267,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>307</v>
@@ -14294,10 +14281,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>309</v>
@@ -14308,13 +14295,13 @@
         <v>15</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -14322,13 +14309,13 @@
         <v>15</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -14336,13 +14323,13 @@
         <v>16</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -14350,13 +14337,13 @@
         <v>16</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
     </row>
   </sheetData>
@@ -18719,10 +18706,10 @@
         <v>32</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>46</v>
@@ -18763,10 +18750,10 @@
         <v>34</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="F118" s="11"/>
       <c r="G118" s="11"/>
@@ -18794,7 +18781,7 @@
         <v>298</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>46</v>
@@ -18926,7 +18913,7 @@
         <v>303</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="F122" s="10" t="s">
         <v>46</v>
